--- a/diseases/d050/2010-2014.xlsx
+++ b/diseases/d050/2010-2014.xlsx
@@ -773,6 +773,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO2" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -918,6 +923,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO3" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1063,6 +1073,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO4" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1208,6 +1223,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO5" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1353,6 +1373,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO6" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1498,6 +1523,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO7" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1643,6 +1673,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO8" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1788,6 +1823,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO9" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1933,6 +1973,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO10" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2078,6 +2123,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO11" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2223,6 +2273,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO12" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2368,6 +2423,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO13" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2513,6 +2573,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO14" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2658,6 +2723,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO15" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2803,6 +2873,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO16" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2948,6 +3023,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO17" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3093,6 +3173,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO18" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3238,6 +3323,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO19" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3383,6 +3473,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO20" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3528,6 +3623,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO21" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3673,6 +3773,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO22" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4262,6 +4367,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO26" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4999,6 +5109,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO31" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5884,6 +5999,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO37" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6621,6 +6741,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO42" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7506,6 +7631,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO48" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8243,6 +8373,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO53" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8980,6 +9115,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO58" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9717,6 +9857,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO63" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -10602,6 +10747,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA69" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO69" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -11339,6 +11489,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA74" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO74" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -12076,6 +12231,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA79" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO79" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -12961,6 +13121,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA85" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO85" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -13698,6 +13863,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA90" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO90" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -14583,6 +14753,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA96" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO96" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -15320,6 +15495,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA101" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO101" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -16057,6 +16237,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA106" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO106" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -16942,6 +17127,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA112" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO112" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -17679,6 +17869,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA117" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO117" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -18416,6 +18611,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA122" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO122" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -19153,6 +19353,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA127" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO127" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -20038,6 +20243,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA133" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO133" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -20775,6 +20985,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA138" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO138" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -21660,6 +21875,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA144" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO144" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -22397,6 +22617,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA149" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO149" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -23134,6 +23359,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA154" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO154" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -24019,6 +24249,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA160" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO160" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -24754,6 +24989,11 @@
       <c r="S165" t="inlineStr">
         <is>
           <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA165" t="inlineStr">
+        <is>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO165" t="inlineStr">

--- a/diseases/d050/2010-2014.xlsx
+++ b/diseases/d050/2010-2014.xlsx
@@ -3926,28 +3926,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>HOLD_JP_534554c6916adc005164f8ba7945</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR23" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS23" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ23" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS23" t="inlineStr">
+        <is>
+          <t>HOLD_JP_534554c6916adc005164f8ba7945</t>
+        </is>
+      </c>
       <c r="AT23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU23" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV23" t="inlineStr">
@@ -4074,28 +4088,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>HOLD_JP_534554c6916adc005164f8ba7945</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO24" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP24" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR24" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS24" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ24" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS24" t="inlineStr">
+        <is>
+          <t>HOLD_JP_534554c6916adc005164f8ba7945</t>
+        </is>
+      </c>
       <c r="AT24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU24" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV24" t="inlineStr">
@@ -4222,28 +4250,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>HOLD_JP_534554c6916adc005164f8ba7945</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO25" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP25" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR25" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS25" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ25" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS25" t="inlineStr">
+        <is>
+          <t>HOLD_JP_534554c6916adc005164f8ba7945</t>
+        </is>
+      </c>
       <c r="AT25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU25" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV25" t="inlineStr">
@@ -4520,28 +4562,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>HOLD_JP_534554c6916adc005164f8ba7945</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO27" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP27" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR27" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS27" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ27" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS27" t="inlineStr">
+        <is>
+          <t>HOLD_JP_534554c6916adc005164f8ba7945</t>
+        </is>
+      </c>
       <c r="AT27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU27" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV27" t="inlineStr">
@@ -4668,28 +4724,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>HOLD_JP_534554c6916adc005164f8ba7945</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO28" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP28" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR28" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS28" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ28" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS28" t="inlineStr">
+        <is>
+          <t>HOLD_JP_534554c6916adc005164f8ba7945</t>
+        </is>
+      </c>
       <c r="AT28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU28" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV28" t="inlineStr">
@@ -4816,28 +4886,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>HOLD_JP_534554c6916adc005164f8ba7945</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO29" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP29" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR29" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS29" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ29" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS29" t="inlineStr">
+        <is>
+          <t>HOLD_JP_534554c6916adc005164f8ba7945</t>
+        </is>
+      </c>
       <c r="AT29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU29" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV29" t="inlineStr">
@@ -4964,28 +5048,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>HOLD_JP_534554c6916adc005164f8ba7945</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO30" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP30" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR30" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS30" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ30" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS30" t="inlineStr">
+        <is>
+          <t>HOLD_JP_534554c6916adc005164f8ba7945</t>
+        </is>
+      </c>
       <c r="AT30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU30" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV30" t="inlineStr">
@@ -5262,28 +5360,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>HOLD_JP_534554c6916adc005164f8ba7945</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO32" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP32" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR32" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS32" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ32" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS32" t="inlineStr">
+        <is>
+          <t>HOLD_JP_534554c6916adc005164f8ba7945</t>
+        </is>
+      </c>
       <c r="AT32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU32" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV32" t="inlineStr">
@@ -5410,28 +5522,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>HOLD_JP_534554c6916adc005164f8ba7945</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO33" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP33" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR33" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS33" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ33" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS33" t="inlineStr">
+        <is>
+          <t>HOLD_JP_534554c6916adc005164f8ba7945</t>
+        </is>
+      </c>
       <c r="AT33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU33" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV33" t="inlineStr">
@@ -5558,28 +5684,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>HOLD_JP_534554c6916adc005164f8ba7945</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO34" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP34" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR34" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS34" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ34" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS34" t="inlineStr">
+        <is>
+          <t>HOLD_JP_534554c6916adc005164f8ba7945</t>
+        </is>
+      </c>
       <c r="AT34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU34" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV34" t="inlineStr">
@@ -5706,28 +5846,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>HOLD_JP_534554c6916adc005164f8ba7945</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO35" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP35" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR35" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS35" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ35" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS35" t="inlineStr">
+        <is>
+          <t>HOLD_JP_534554c6916adc005164f8ba7945</t>
+        </is>
+      </c>
       <c r="AT35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU35" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV35" t="inlineStr">
@@ -5854,28 +6008,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>HOLD_JP_534554c6916adc005164f8ba7945</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO36" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP36" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR36" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS36" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ36" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS36" t="inlineStr">
+        <is>
+          <t>HOLD_JP_534554c6916adc005164f8ba7945</t>
+        </is>
+      </c>
       <c r="AT36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU36" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV36" t="inlineStr">
@@ -6152,28 +6320,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>HOLD_JP_534554c6916adc005164f8ba7945</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO38" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP38" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR38" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS38" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ38" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS38" t="inlineStr">
+        <is>
+          <t>HOLD_JP_534554c6916adc005164f8ba7945</t>
+        </is>
+      </c>
       <c r="AT38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU38" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV38" t="inlineStr">
@@ -6300,28 +6482,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>HOLD_JP_534554c6916adc005164f8ba7945</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO39" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP39" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR39" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS39" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ39" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS39" t="inlineStr">
+        <is>
+          <t>HOLD_JP_534554c6916adc005164f8ba7945</t>
+        </is>
+      </c>
       <c r="AT39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU39" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV39" t="inlineStr">
@@ -6448,28 +6644,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>HOLD_JP_534554c6916adc005164f8ba7945</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO40" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP40" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR40" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS40" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ40" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS40" t="inlineStr">
+        <is>
+          <t>HOLD_JP_534554c6916adc005164f8ba7945</t>
+        </is>
+      </c>
       <c r="AT40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU40" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV40" t="inlineStr">
@@ -6596,28 +6806,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>HOLD_JP_534554c6916adc005164f8ba7945</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO41" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP41" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR41" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS41" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ41" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS41" t="inlineStr">
+        <is>
+          <t>HOLD_JP_534554c6916adc005164f8ba7945</t>
+        </is>
+      </c>
       <c r="AT41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU41" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV41" t="inlineStr">
@@ -6894,28 +7118,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>HOLD_JP_534554c6916adc005164f8ba7945</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO43" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP43" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR43" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS43" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ43" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS43" t="inlineStr">
+        <is>
+          <t>HOLD_JP_534554c6916adc005164f8ba7945</t>
+        </is>
+      </c>
       <c r="AT43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU43" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV43" t="inlineStr">
@@ -7042,28 +7280,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>HOLD_JP_534554c6916adc005164f8ba7945</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO44" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP44" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR44" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS44" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ44" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS44" t="inlineStr">
+        <is>
+          <t>HOLD_JP_534554c6916adc005164f8ba7945</t>
+        </is>
+      </c>
       <c r="AT44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU44" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV44" t="inlineStr">
@@ -7190,28 +7442,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>HOLD_JP_534554c6916adc005164f8ba7945</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO45" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP45" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR45" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS45" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ45" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS45" t="inlineStr">
+        <is>
+          <t>HOLD_JP_534554c6916adc005164f8ba7945</t>
+        </is>
+      </c>
       <c r="AT45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU45" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV45" t="inlineStr">
@@ -7338,28 +7604,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>HOLD_JP_534554c6916adc005164f8ba7945</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO46" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP46" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR46" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS46" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ46" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS46" t="inlineStr">
+        <is>
+          <t>HOLD_JP_534554c6916adc005164f8ba7945</t>
+        </is>
+      </c>
       <c r="AT46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU46" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV46" t="inlineStr">
@@ -7486,28 +7766,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>HOLD_JP_534554c6916adc005164f8ba7945</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO47" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP47" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR47" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS47" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ47" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS47" t="inlineStr">
+        <is>
+          <t>HOLD_JP_534554c6916adc005164f8ba7945</t>
+        </is>
+      </c>
       <c r="AT47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU47" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV47" t="inlineStr">
@@ -7784,28 +8078,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>HOLD_JP_534554c6916adc005164f8ba7945</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO49" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP49" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR49" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS49" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ49" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS49" t="inlineStr">
+        <is>
+          <t>HOLD_JP_534554c6916adc005164f8ba7945</t>
+        </is>
+      </c>
       <c r="AT49" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU49" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV49" t="inlineStr">
@@ -7932,28 +8240,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>HOLD_JP_534554c6916adc005164f8ba7945</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO50" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP50" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR50" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS50" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ50" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS50" t="inlineStr">
+        <is>
+          <t>HOLD_JP_534554c6916adc005164f8ba7945</t>
+        </is>
+      </c>
       <c r="AT50" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU50" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV50" t="inlineStr">
@@ -8080,28 +8402,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>HOLD_JP_534554c6916adc005164f8ba7945</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO51" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP51" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR51" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS51" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ51" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS51" t="inlineStr">
+        <is>
+          <t>HOLD_JP_534554c6916adc005164f8ba7945</t>
+        </is>
+      </c>
       <c r="AT51" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU51" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV51" t="inlineStr">
@@ -8228,28 +8564,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>HOLD_JP_534554c6916adc005164f8ba7945</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO52" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP52" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR52" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS52" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ52" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS52" t="inlineStr">
+        <is>
+          <t>HOLD_JP_534554c6916adc005164f8ba7945</t>
+        </is>
+      </c>
       <c r="AT52" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU52" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV52" t="inlineStr">
@@ -8526,28 +8876,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>HOLD_JP_534554c6916adc005164f8ba7945</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO54" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP54" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR54" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS54" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ54" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS54" t="inlineStr">
+        <is>
+          <t>HOLD_JP_534554c6916adc005164f8ba7945</t>
+        </is>
+      </c>
       <c r="AT54" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU54" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV54" t="inlineStr">
@@ -8674,28 +9038,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>HOLD_JP_534554c6916adc005164f8ba7945</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO55" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP55" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR55" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS55" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ55" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS55" t="inlineStr">
+        <is>
+          <t>HOLD_JP_534554c6916adc005164f8ba7945</t>
+        </is>
+      </c>
       <c r="AT55" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU55" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV55" t="inlineStr">
@@ -8822,28 +9200,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>HOLD_JP_534554c6916adc005164f8ba7945</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO56" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP56" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR56" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS56" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ56" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS56" t="inlineStr">
+        <is>
+          <t>HOLD_JP_534554c6916adc005164f8ba7945</t>
+        </is>
+      </c>
       <c r="AT56" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU56" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV56" t="inlineStr">
@@ -8970,28 +9362,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>HOLD_JP_534554c6916adc005164f8ba7945</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO57" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP57" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR57" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS57" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ57" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS57" t="inlineStr">
+        <is>
+          <t>HOLD_JP_534554c6916adc005164f8ba7945</t>
+        </is>
+      </c>
       <c r="AT57" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU57" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV57" t="inlineStr">
@@ -9268,28 +9674,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>HOLD_JP_534554c6916adc005164f8ba7945</t>
+        </is>
+      </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO59" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP59" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR59" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS59" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ59" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS59" t="inlineStr">
+        <is>
+          <t>HOLD_JP_534554c6916adc005164f8ba7945</t>
+        </is>
+      </c>
       <c r="AT59" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU59" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV59" t="inlineStr">
@@ -9416,28 +9836,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>HOLD_JP_534554c6916adc005164f8ba7945</t>
+        </is>
+      </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO60" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP60" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR60" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS60" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ60" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS60" t="inlineStr">
+        <is>
+          <t>HOLD_JP_534554c6916adc005164f8ba7945</t>
+        </is>
+      </c>
       <c r="AT60" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU60" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV60" t="inlineStr">
@@ -9564,28 +9998,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>HOLD_JP_534554c6916adc005164f8ba7945</t>
+        </is>
+      </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO61" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP61" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR61" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS61" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ61" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS61" t="inlineStr">
+        <is>
+          <t>HOLD_JP_534554c6916adc005164f8ba7945</t>
+        </is>
+      </c>
       <c r="AT61" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU61" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV61" t="inlineStr">
@@ -9712,28 +10160,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>HOLD_JP_534554c6916adc005164f8ba7945</t>
+        </is>
+      </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO62" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP62" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR62" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS62" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ62" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS62" t="inlineStr">
+        <is>
+          <t>HOLD_JP_534554c6916adc005164f8ba7945</t>
+        </is>
+      </c>
       <c r="AT62" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU62" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV62" t="inlineStr">
@@ -10010,28 +10472,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>HOLD_JP_534554c6916adc005164f8ba7945</t>
+        </is>
+      </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO64" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP64" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR64" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS64" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ64" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS64" t="inlineStr">
+        <is>
+          <t>HOLD_JP_534554c6916adc005164f8ba7945</t>
+        </is>
+      </c>
       <c r="AT64" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU64" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV64" t="inlineStr">
@@ -10158,28 +10634,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>HOLD_JP_534554c6916adc005164f8ba7945</t>
+        </is>
+      </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO65" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP65" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR65" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS65" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ65" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS65" t="inlineStr">
+        <is>
+          <t>HOLD_JP_534554c6916adc005164f8ba7945</t>
+        </is>
+      </c>
       <c r="AT65" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU65" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV65" t="inlineStr">
@@ -10306,28 +10796,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>HOLD_JP_534554c6916adc005164f8ba7945</t>
+        </is>
+      </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO66" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP66" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR66" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS66" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ66" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS66" t="inlineStr">
+        <is>
+          <t>HOLD_JP_534554c6916adc005164f8ba7945</t>
+        </is>
+      </c>
       <c r="AT66" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU66" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV66" t="inlineStr">
@@ -10454,28 +10958,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>HOLD_JP_534554c6916adc005164f8ba7945</t>
+        </is>
+      </c>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO67" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP67" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR67" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS67" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ67" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS67" t="inlineStr">
+        <is>
+          <t>HOLD_JP_534554c6916adc005164f8ba7945</t>
+        </is>
+      </c>
       <c r="AT67" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU67" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV67" t="inlineStr">
@@ -10602,28 +11120,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>HOLD_JP_534554c6916adc005164f8ba7945</t>
+        </is>
+      </c>
+      <c r="AA68" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO68" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP68" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR68" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS68" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ68" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS68" t="inlineStr">
+        <is>
+          <t>HOLD_JP_534554c6916adc005164f8ba7945</t>
+        </is>
+      </c>
       <c r="AT68" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU68" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV68" t="inlineStr">
@@ -10900,28 +11432,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>HOLD_JP_534554c6916adc005164f8ba7945</t>
+        </is>
+      </c>
+      <c r="AA70" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO70" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP70" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR70" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS70" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ70" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS70" t="inlineStr">
+        <is>
+          <t>HOLD_JP_534554c6916adc005164f8ba7945</t>
+        </is>
+      </c>
       <c r="AT70" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU70" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV70" t="inlineStr">
@@ -11048,28 +11594,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>HOLD_JP_534554c6916adc005164f8ba7945</t>
+        </is>
+      </c>
+      <c r="AA71" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO71" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP71" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR71" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS71" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ71" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS71" t="inlineStr">
+        <is>
+          <t>HOLD_JP_534554c6916adc005164f8ba7945</t>
+        </is>
+      </c>
       <c r="AT71" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU71" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV71" t="inlineStr">
@@ -11196,28 +11756,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>HOLD_JP_534554c6916adc005164f8ba7945</t>
+        </is>
+      </c>
+      <c r="AA72" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO72" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP72" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR72" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS72" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ72" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS72" t="inlineStr">
+        <is>
+          <t>HOLD_JP_534554c6916adc005164f8ba7945</t>
+        </is>
+      </c>
       <c r="AT72" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU72" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV72" t="inlineStr">
@@ -11344,28 +11918,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>HOLD_JP_534554c6916adc005164f8ba7945</t>
+        </is>
+      </c>
+      <c r="AA73" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO73" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP73" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR73" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS73" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ73" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS73" t="inlineStr">
+        <is>
+          <t>HOLD_JP_534554c6916adc005164f8ba7945</t>
+        </is>
+      </c>
       <c r="AT73" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU73" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV73" t="inlineStr">
@@ -11642,28 +12230,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U75" t="inlineStr">
+        <is>
+          <t>HOLD_JP_534554c6916adc005164f8ba7945</t>
+        </is>
+      </c>
+      <c r="AA75" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO75" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP75" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR75" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS75" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ75" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS75" t="inlineStr">
+        <is>
+          <t>HOLD_JP_534554c6916adc005164f8ba7945</t>
+        </is>
+      </c>
       <c r="AT75" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU75" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV75" t="inlineStr">
@@ -11790,28 +12392,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U76" t="inlineStr">
+        <is>
+          <t>HOLD_JP_534554c6916adc005164f8ba7945</t>
+        </is>
+      </c>
+      <c r="AA76" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO76" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP76" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR76" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS76" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ76" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS76" t="inlineStr">
+        <is>
+          <t>HOLD_JP_534554c6916adc005164f8ba7945</t>
+        </is>
+      </c>
       <c r="AT76" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU76" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV76" t="inlineStr">
@@ -11938,28 +12554,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U77" t="inlineStr">
+        <is>
+          <t>HOLD_JP_534554c6916adc005164f8ba7945</t>
+        </is>
+      </c>
+      <c r="AA77" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO77" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP77" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR77" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS77" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ77" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS77" t="inlineStr">
+        <is>
+          <t>HOLD_JP_534554c6916adc005164f8ba7945</t>
+        </is>
+      </c>
       <c r="AT77" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU77" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV77" t="inlineStr">
@@ -12086,28 +12716,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U78" t="inlineStr">
+        <is>
+          <t>HOLD_JP_534554c6916adc005164f8ba7945</t>
+        </is>
+      </c>
+      <c r="AA78" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO78" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP78" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR78" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS78" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ78" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS78" t="inlineStr">
+        <is>
+          <t>HOLD_JP_534554c6916adc005164f8ba7945</t>
+        </is>
+      </c>
       <c r="AT78" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU78" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV78" t="inlineStr">
@@ -12384,28 +13028,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U80" t="inlineStr">
+        <is>
+          <t>HOLD_JP_534554c6916adc005164f8ba7945</t>
+        </is>
+      </c>
+      <c r="AA80" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO80" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP80" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR80" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS80" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ80" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS80" t="inlineStr">
+        <is>
+          <t>HOLD_JP_534554c6916adc005164f8ba7945</t>
+        </is>
+      </c>
       <c r="AT80" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU80" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV80" t="inlineStr">
@@ -12532,28 +13190,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U81" t="inlineStr">
+        <is>
+          <t>HOLD_JP_534554c6916adc005164f8ba7945</t>
+        </is>
+      </c>
+      <c r="AA81" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO81" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP81" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR81" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS81" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ81" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS81" t="inlineStr">
+        <is>
+          <t>HOLD_JP_534554c6916adc005164f8ba7945</t>
+        </is>
+      </c>
       <c r="AT81" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU81" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV81" t="inlineStr">
@@ -12680,28 +13352,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U82" t="inlineStr">
+        <is>
+          <t>HOLD_JP_534554c6916adc005164f8ba7945</t>
+        </is>
+      </c>
+      <c r="AA82" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO82" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP82" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR82" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS82" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ82" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS82" t="inlineStr">
+        <is>
+          <t>HOLD_JP_534554c6916adc005164f8ba7945</t>
+        </is>
+      </c>
       <c r="AT82" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU82" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV82" t="inlineStr">
@@ -12828,28 +13514,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U83" t="inlineStr">
+        <is>
+          <t>HOLD_JP_534554c6916adc005164f8ba7945</t>
+        </is>
+      </c>
+      <c r="AA83" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO83" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP83" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR83" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS83" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ83" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS83" t="inlineStr">
+        <is>
+          <t>HOLD_JP_534554c6916adc005164f8ba7945</t>
+        </is>
+      </c>
       <c r="AT83" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU83" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV83" t="inlineStr">
@@ -12976,28 +13676,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U84" t="inlineStr">
+        <is>
+          <t>HOLD_JP_534554c6916adc005164f8ba7945</t>
+        </is>
+      </c>
+      <c r="AA84" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO84" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP84" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR84" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS84" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ84" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS84" t="inlineStr">
+        <is>
+          <t>HOLD_JP_534554c6916adc005164f8ba7945</t>
+        </is>
+      </c>
       <c r="AT84" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU84" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV84" t="inlineStr">
@@ -13274,28 +13988,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U86" t="inlineStr">
+        <is>
+          <t>HOLD_JP_534554c6916adc005164f8ba7945</t>
+        </is>
+      </c>
+      <c r="AA86" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO86" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP86" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR86" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS86" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ86" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS86" t="inlineStr">
+        <is>
+          <t>HOLD_JP_534554c6916adc005164f8ba7945</t>
+        </is>
+      </c>
       <c r="AT86" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU86" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV86" t="inlineStr">
@@ -13422,28 +14150,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U87" t="inlineStr">
+        <is>
+          <t>HOLD_JP_534554c6916adc005164f8ba7945</t>
+        </is>
+      </c>
+      <c r="AA87" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO87" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP87" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR87" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS87" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ87" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS87" t="inlineStr">
+        <is>
+          <t>HOLD_JP_534554c6916adc005164f8ba7945</t>
+        </is>
+      </c>
       <c r="AT87" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU87" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV87" t="inlineStr">
@@ -13570,28 +14312,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U88" t="inlineStr">
+        <is>
+          <t>HOLD_JP_534554c6916adc005164f8ba7945</t>
+        </is>
+      </c>
+      <c r="AA88" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO88" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP88" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR88" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS88" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ88" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS88" t="inlineStr">
+        <is>
+          <t>HOLD_JP_534554c6916adc005164f8ba7945</t>
+        </is>
+      </c>
       <c r="AT88" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU88" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV88" t="inlineStr">
@@ -13718,28 +14474,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U89" t="inlineStr">
+        <is>
+          <t>HOLD_JP_534554c6916adc005164f8ba7945</t>
+        </is>
+      </c>
+      <c r="AA89" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO89" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP89" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR89" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS89" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ89" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS89" t="inlineStr">
+        <is>
+          <t>HOLD_JP_534554c6916adc005164f8ba7945</t>
+        </is>
+      </c>
       <c r="AT89" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU89" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV89" t="inlineStr">
@@ -14016,28 +14786,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U91" t="inlineStr">
+        <is>
+          <t>HOLD_JP_534554c6916adc005164f8ba7945</t>
+        </is>
+      </c>
+      <c r="AA91" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO91" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP91" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR91" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS91" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ91" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS91" t="inlineStr">
+        <is>
+          <t>HOLD_JP_534554c6916adc005164f8ba7945</t>
+        </is>
+      </c>
       <c r="AT91" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU91" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV91" t="inlineStr">
@@ -14164,28 +14948,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U92" t="inlineStr">
+        <is>
+          <t>HOLD_JP_534554c6916adc005164f8ba7945</t>
+        </is>
+      </c>
+      <c r="AA92" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO92" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP92" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR92" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS92" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ92" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS92" t="inlineStr">
+        <is>
+          <t>HOLD_JP_534554c6916adc005164f8ba7945</t>
+        </is>
+      </c>
       <c r="AT92" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU92" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV92" t="inlineStr">
@@ -14312,28 +15110,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U93" t="inlineStr">
+        <is>
+          <t>HOLD_JP_534554c6916adc005164f8ba7945</t>
+        </is>
+      </c>
+      <c r="AA93" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO93" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP93" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR93" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS93" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ93" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS93" t="inlineStr">
+        <is>
+          <t>HOLD_JP_534554c6916adc005164f8ba7945</t>
+        </is>
+      </c>
       <c r="AT93" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU93" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV93" t="inlineStr">
@@ -14460,28 +15272,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U94" t="inlineStr">
+        <is>
+          <t>HOLD_JP_534554c6916adc005164f8ba7945</t>
+        </is>
+      </c>
+      <c r="AA94" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO94" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP94" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR94" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS94" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ94" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS94" t="inlineStr">
+        <is>
+          <t>HOLD_JP_534554c6916adc005164f8ba7945</t>
+        </is>
+      </c>
       <c r="AT94" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU94" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV94" t="inlineStr">
@@ -14608,28 +15434,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U95" t="inlineStr">
+        <is>
+          <t>HOLD_JP_534554c6916adc005164f8ba7945</t>
+        </is>
+      </c>
+      <c r="AA95" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO95" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP95" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR95" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS95" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ95" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS95" t="inlineStr">
+        <is>
+          <t>HOLD_JP_534554c6916adc005164f8ba7945</t>
+        </is>
+      </c>
       <c r="AT95" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU95" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV95" t="inlineStr">
@@ -14906,28 +15746,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U97" t="inlineStr">
+        <is>
+          <t>HOLD_JP_534554c6916adc005164f8ba7945</t>
+        </is>
+      </c>
+      <c r="AA97" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO97" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP97" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR97" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS97" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ97" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS97" t="inlineStr">
+        <is>
+          <t>HOLD_JP_534554c6916adc005164f8ba7945</t>
+        </is>
+      </c>
       <c r="AT97" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU97" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV97" t="inlineStr">
@@ -15054,28 +15908,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U98" t="inlineStr">
+        <is>
+          <t>HOLD_JP_534554c6916adc005164f8ba7945</t>
+        </is>
+      </c>
+      <c r="AA98" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO98" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP98" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR98" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS98" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ98" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS98" t="inlineStr">
+        <is>
+          <t>HOLD_JP_534554c6916adc005164f8ba7945</t>
+        </is>
+      </c>
       <c r="AT98" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU98" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV98" t="inlineStr">
@@ -15202,28 +16070,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U99" t="inlineStr">
+        <is>
+          <t>HOLD_JP_534554c6916adc005164f8ba7945</t>
+        </is>
+      </c>
+      <c r="AA99" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO99" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP99" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR99" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS99" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ99" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS99" t="inlineStr">
+        <is>
+          <t>HOLD_JP_534554c6916adc005164f8ba7945</t>
+        </is>
+      </c>
       <c r="AT99" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU99" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV99" t="inlineStr">
@@ -15350,28 +16232,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U100" t="inlineStr">
+        <is>
+          <t>HOLD_JP_534554c6916adc005164f8ba7945</t>
+        </is>
+      </c>
+      <c r="AA100" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO100" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP100" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR100" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS100" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ100" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS100" t="inlineStr">
+        <is>
+          <t>HOLD_JP_534554c6916adc005164f8ba7945</t>
+        </is>
+      </c>
       <c r="AT100" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU100" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV100" t="inlineStr">
@@ -15648,28 +16544,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U102" t="inlineStr">
+        <is>
+          <t>HOLD_JP_534554c6916adc005164f8ba7945</t>
+        </is>
+      </c>
+      <c r="AA102" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO102" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP102" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR102" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS102" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ102" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS102" t="inlineStr">
+        <is>
+          <t>HOLD_JP_534554c6916adc005164f8ba7945</t>
+        </is>
+      </c>
       <c r="AT102" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU102" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV102" t="inlineStr">
@@ -15796,28 +16706,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U103" t="inlineStr">
+        <is>
+          <t>HOLD_JP_534554c6916adc005164f8ba7945</t>
+        </is>
+      </c>
+      <c r="AA103" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO103" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP103" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR103" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS103" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ103" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS103" t="inlineStr">
+        <is>
+          <t>HOLD_JP_534554c6916adc005164f8ba7945</t>
+        </is>
+      </c>
       <c r="AT103" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU103" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV103" t="inlineStr">
@@ -15944,28 +16868,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U104" t="inlineStr">
+        <is>
+          <t>HOLD_JP_534554c6916adc005164f8ba7945</t>
+        </is>
+      </c>
+      <c r="AA104" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO104" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP104" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR104" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS104" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ104" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS104" t="inlineStr">
+        <is>
+          <t>HOLD_JP_534554c6916adc005164f8ba7945</t>
+        </is>
+      </c>
       <c r="AT104" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU104" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV104" t="inlineStr">
@@ -16092,28 +17030,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U105" t="inlineStr">
+        <is>
+          <t>HOLD_JP_534554c6916adc005164f8ba7945</t>
+        </is>
+      </c>
+      <c r="AA105" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO105" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP105" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR105" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS105" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ105" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS105" t="inlineStr">
+        <is>
+          <t>HOLD_JP_534554c6916adc005164f8ba7945</t>
+        </is>
+      </c>
       <c r="AT105" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU105" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV105" t="inlineStr">
@@ -16390,28 +17342,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U107" t="inlineStr">
+        <is>
+          <t>HOLD_JP_534554c6916adc005164f8ba7945</t>
+        </is>
+      </c>
+      <c r="AA107" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO107" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP107" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR107" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS107" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ107" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS107" t="inlineStr">
+        <is>
+          <t>HOLD_JP_534554c6916adc005164f8ba7945</t>
+        </is>
+      </c>
       <c r="AT107" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU107" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV107" t="inlineStr">
@@ -16538,28 +17504,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U108" t="inlineStr">
+        <is>
+          <t>HOLD_JP_534554c6916adc005164f8ba7945</t>
+        </is>
+      </c>
+      <c r="AA108" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO108" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP108" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR108" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS108" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ108" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS108" t="inlineStr">
+        <is>
+          <t>HOLD_JP_534554c6916adc005164f8ba7945</t>
+        </is>
+      </c>
       <c r="AT108" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU108" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV108" t="inlineStr">
@@ -16686,28 +17666,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U109" t="inlineStr">
+        <is>
+          <t>HOLD_JP_534554c6916adc005164f8ba7945</t>
+        </is>
+      </c>
+      <c r="AA109" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO109" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP109" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR109" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS109" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ109" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS109" t="inlineStr">
+        <is>
+          <t>HOLD_JP_534554c6916adc005164f8ba7945</t>
+        </is>
+      </c>
       <c r="AT109" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU109" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV109" t="inlineStr">
@@ -16834,28 +17828,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U110" t="inlineStr">
+        <is>
+          <t>HOLD_JP_534554c6916adc005164f8ba7945</t>
+        </is>
+      </c>
+      <c r="AA110" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO110" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP110" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR110" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS110" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ110" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS110" t="inlineStr">
+        <is>
+          <t>HOLD_JP_534554c6916adc005164f8ba7945</t>
+        </is>
+      </c>
       <c r="AT110" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU110" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV110" t="inlineStr">
@@ -16982,28 +17990,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U111" t="inlineStr">
+        <is>
+          <t>HOLD_JP_534554c6916adc005164f8ba7945</t>
+        </is>
+      </c>
+      <c r="AA111" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO111" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP111" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR111" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS111" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ111" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS111" t="inlineStr">
+        <is>
+          <t>HOLD_JP_534554c6916adc005164f8ba7945</t>
+        </is>
+      </c>
       <c r="AT111" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU111" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV111" t="inlineStr">
@@ -17280,28 +18302,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U113" t="inlineStr">
+        <is>
+          <t>HOLD_JP_534554c6916adc005164f8ba7945</t>
+        </is>
+      </c>
+      <c r="AA113" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO113" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP113" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR113" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS113" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ113" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS113" t="inlineStr">
+        <is>
+          <t>HOLD_JP_534554c6916adc005164f8ba7945</t>
+        </is>
+      </c>
       <c r="AT113" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU113" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV113" t="inlineStr">
@@ -17428,28 +18464,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U114" t="inlineStr">
+        <is>
+          <t>HOLD_JP_534554c6916adc005164f8ba7945</t>
+        </is>
+      </c>
+      <c r="AA114" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO114" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP114" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR114" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS114" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ114" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS114" t="inlineStr">
+        <is>
+          <t>HOLD_JP_534554c6916adc005164f8ba7945</t>
+        </is>
+      </c>
       <c r="AT114" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU114" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV114" t="inlineStr">
@@ -17576,28 +18626,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U115" t="inlineStr">
+        <is>
+          <t>HOLD_JP_534554c6916adc005164f8ba7945</t>
+        </is>
+      </c>
+      <c r="AA115" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO115" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP115" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR115" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS115" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ115" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS115" t="inlineStr">
+        <is>
+          <t>HOLD_JP_534554c6916adc005164f8ba7945</t>
+        </is>
+      </c>
       <c r="AT115" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU115" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV115" t="inlineStr">
@@ -17724,28 +18788,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U116" t="inlineStr">
+        <is>
+          <t>HOLD_JP_534554c6916adc005164f8ba7945</t>
+        </is>
+      </c>
+      <c r="AA116" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO116" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP116" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR116" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS116" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ116" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS116" t="inlineStr">
+        <is>
+          <t>HOLD_JP_534554c6916adc005164f8ba7945</t>
+        </is>
+      </c>
       <c r="AT116" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU116" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV116" t="inlineStr">
@@ -18022,28 +19100,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U118" t="inlineStr">
+        <is>
+          <t>HOLD_JP_534554c6916adc005164f8ba7945</t>
+        </is>
+      </c>
+      <c r="AA118" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO118" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP118" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR118" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS118" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ118" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS118" t="inlineStr">
+        <is>
+          <t>HOLD_JP_534554c6916adc005164f8ba7945</t>
+        </is>
+      </c>
       <c r="AT118" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU118" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV118" t="inlineStr">
@@ -18170,28 +19262,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U119" t="inlineStr">
+        <is>
+          <t>HOLD_JP_534554c6916adc005164f8ba7945</t>
+        </is>
+      </c>
+      <c r="AA119" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO119" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP119" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR119" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS119" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ119" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS119" t="inlineStr">
+        <is>
+          <t>HOLD_JP_534554c6916adc005164f8ba7945</t>
+        </is>
+      </c>
       <c r="AT119" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU119" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV119" t="inlineStr">
@@ -18318,28 +19424,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U120" t="inlineStr">
+        <is>
+          <t>HOLD_JP_534554c6916adc005164f8ba7945</t>
+        </is>
+      </c>
+      <c r="AA120" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO120" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP120" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR120" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS120" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ120" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS120" t="inlineStr">
+        <is>
+          <t>HOLD_JP_534554c6916adc005164f8ba7945</t>
+        </is>
+      </c>
       <c r="AT120" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU120" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV120" t="inlineStr">
@@ -18466,28 +19586,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U121" t="inlineStr">
+        <is>
+          <t>HOLD_JP_534554c6916adc005164f8ba7945</t>
+        </is>
+      </c>
+      <c r="AA121" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO121" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP121" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR121" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS121" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ121" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS121" t="inlineStr">
+        <is>
+          <t>HOLD_JP_534554c6916adc005164f8ba7945</t>
+        </is>
+      </c>
       <c r="AT121" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU121" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV121" t="inlineStr">
@@ -18764,28 +19898,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U123" t="inlineStr">
+        <is>
+          <t>HOLD_JP_534554c6916adc005164f8ba7945</t>
+        </is>
+      </c>
+      <c r="AA123" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO123" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP123" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR123" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS123" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ123" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS123" t="inlineStr">
+        <is>
+          <t>HOLD_JP_534554c6916adc005164f8ba7945</t>
+        </is>
+      </c>
       <c r="AT123" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU123" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV123" t="inlineStr">
@@ -18912,28 +20060,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U124" t="inlineStr">
+        <is>
+          <t>HOLD_JP_534554c6916adc005164f8ba7945</t>
+        </is>
+      </c>
+      <c r="AA124" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO124" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP124" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR124" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS124" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ124" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS124" t="inlineStr">
+        <is>
+          <t>HOLD_JP_534554c6916adc005164f8ba7945</t>
+        </is>
+      </c>
       <c r="AT124" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU124" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV124" t="inlineStr">
@@ -19060,28 +20222,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U125" t="inlineStr">
+        <is>
+          <t>HOLD_JP_534554c6916adc005164f8ba7945</t>
+        </is>
+      </c>
+      <c r="AA125" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO125" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP125" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR125" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS125" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ125" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS125" t="inlineStr">
+        <is>
+          <t>HOLD_JP_534554c6916adc005164f8ba7945</t>
+        </is>
+      </c>
       <c r="AT125" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU125" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV125" t="inlineStr">
@@ -19208,28 +20384,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U126" t="inlineStr">
+        <is>
+          <t>HOLD_JP_534554c6916adc005164f8ba7945</t>
+        </is>
+      </c>
+      <c r="AA126" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO126" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP126" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR126" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS126" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ126" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS126" t="inlineStr">
+        <is>
+          <t>HOLD_JP_534554c6916adc005164f8ba7945</t>
+        </is>
+      </c>
       <c r="AT126" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU126" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV126" t="inlineStr">
@@ -19506,28 +20696,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U128" t="inlineStr">
+        <is>
+          <t>HOLD_JP_534554c6916adc005164f8ba7945</t>
+        </is>
+      </c>
+      <c r="AA128" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO128" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP128" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR128" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS128" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ128" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS128" t="inlineStr">
+        <is>
+          <t>HOLD_JP_534554c6916adc005164f8ba7945</t>
+        </is>
+      </c>
       <c r="AT128" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU128" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV128" t="inlineStr">
@@ -19654,28 +20858,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U129" t="inlineStr">
+        <is>
+          <t>HOLD_JP_534554c6916adc005164f8ba7945</t>
+        </is>
+      </c>
+      <c r="AA129" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO129" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP129" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR129" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS129" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ129" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS129" t="inlineStr">
+        <is>
+          <t>HOLD_JP_534554c6916adc005164f8ba7945</t>
+        </is>
+      </c>
       <c r="AT129" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU129" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV129" t="inlineStr">
@@ -19802,28 +21020,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U130" t="inlineStr">
+        <is>
+          <t>HOLD_JP_534554c6916adc005164f8ba7945</t>
+        </is>
+      </c>
+      <c r="AA130" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO130" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP130" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR130" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS130" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ130" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS130" t="inlineStr">
+        <is>
+          <t>HOLD_JP_534554c6916adc005164f8ba7945</t>
+        </is>
+      </c>
       <c r="AT130" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU130" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV130" t="inlineStr">
@@ -19950,28 +21182,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U131" t="inlineStr">
+        <is>
+          <t>HOLD_JP_534554c6916adc005164f8ba7945</t>
+        </is>
+      </c>
+      <c r="AA131" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO131" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP131" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR131" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS131" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ131" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS131" t="inlineStr">
+        <is>
+          <t>HOLD_JP_534554c6916adc005164f8ba7945</t>
+        </is>
+      </c>
       <c r="AT131" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU131" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV131" t="inlineStr">
@@ -20098,28 +21344,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U132" t="inlineStr">
+        <is>
+          <t>HOLD_JP_534554c6916adc005164f8ba7945</t>
+        </is>
+      </c>
+      <c r="AA132" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO132" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP132" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR132" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS132" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ132" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS132" t="inlineStr">
+        <is>
+          <t>HOLD_JP_534554c6916adc005164f8ba7945</t>
+        </is>
+      </c>
       <c r="AT132" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU132" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV132" t="inlineStr">
@@ -20396,28 +21656,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U134" t="inlineStr">
+        <is>
+          <t>HOLD_JP_534554c6916adc005164f8ba7945</t>
+        </is>
+      </c>
+      <c r="AA134" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO134" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP134" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR134" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS134" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ134" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS134" t="inlineStr">
+        <is>
+          <t>HOLD_JP_534554c6916adc005164f8ba7945</t>
+        </is>
+      </c>
       <c r="AT134" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU134" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV134" t="inlineStr">
@@ -20544,28 +21818,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U135" t="inlineStr">
+        <is>
+          <t>HOLD_JP_534554c6916adc005164f8ba7945</t>
+        </is>
+      </c>
+      <c r="AA135" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO135" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP135" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR135" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS135" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ135" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS135" t="inlineStr">
+        <is>
+          <t>HOLD_JP_534554c6916adc005164f8ba7945</t>
+        </is>
+      </c>
       <c r="AT135" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU135" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV135" t="inlineStr">
@@ -20692,28 +21980,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U136" t="inlineStr">
+        <is>
+          <t>HOLD_JP_534554c6916adc005164f8ba7945</t>
+        </is>
+      </c>
+      <c r="AA136" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO136" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP136" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR136" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS136" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ136" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS136" t="inlineStr">
+        <is>
+          <t>HOLD_JP_534554c6916adc005164f8ba7945</t>
+        </is>
+      </c>
       <c r="AT136" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU136" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV136" t="inlineStr">
@@ -20840,28 +22142,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U137" t="inlineStr">
+        <is>
+          <t>HOLD_JP_534554c6916adc005164f8ba7945</t>
+        </is>
+      </c>
+      <c r="AA137" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO137" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP137" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR137" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS137" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ137" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS137" t="inlineStr">
+        <is>
+          <t>HOLD_JP_534554c6916adc005164f8ba7945</t>
+        </is>
+      </c>
       <c r="AT137" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU137" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV137" t="inlineStr">
@@ -21138,28 +22454,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U139" t="inlineStr">
+        <is>
+          <t>HOLD_JP_534554c6916adc005164f8ba7945</t>
+        </is>
+      </c>
+      <c r="AA139" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO139" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP139" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR139" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS139" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ139" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS139" t="inlineStr">
+        <is>
+          <t>HOLD_JP_534554c6916adc005164f8ba7945</t>
+        </is>
+      </c>
       <c r="AT139" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU139" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV139" t="inlineStr">
@@ -21286,28 +22616,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U140" t="inlineStr">
+        <is>
+          <t>HOLD_JP_534554c6916adc005164f8ba7945</t>
+        </is>
+      </c>
+      <c r="AA140" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO140" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP140" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR140" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS140" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ140" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS140" t="inlineStr">
+        <is>
+          <t>HOLD_JP_534554c6916adc005164f8ba7945</t>
+        </is>
+      </c>
       <c r="AT140" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU140" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV140" t="inlineStr">
@@ -21434,28 +22778,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U141" t="inlineStr">
+        <is>
+          <t>HOLD_JP_534554c6916adc005164f8ba7945</t>
+        </is>
+      </c>
+      <c r="AA141" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO141" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP141" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR141" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS141" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ141" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS141" t="inlineStr">
+        <is>
+          <t>HOLD_JP_534554c6916adc005164f8ba7945</t>
+        </is>
+      </c>
       <c r="AT141" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU141" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV141" t="inlineStr">
@@ -21582,28 +22940,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U142" t="inlineStr">
+        <is>
+          <t>HOLD_JP_534554c6916adc005164f8ba7945</t>
+        </is>
+      </c>
+      <c r="AA142" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO142" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP142" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR142" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS142" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ142" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS142" t="inlineStr">
+        <is>
+          <t>HOLD_JP_534554c6916adc005164f8ba7945</t>
+        </is>
+      </c>
       <c r="AT142" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU142" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV142" t="inlineStr">
@@ -21730,28 +23102,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U143" t="inlineStr">
+        <is>
+          <t>HOLD_JP_534554c6916adc005164f8ba7945</t>
+        </is>
+      </c>
+      <c r="AA143" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO143" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP143" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR143" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS143" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ143" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS143" t="inlineStr">
+        <is>
+          <t>HOLD_JP_534554c6916adc005164f8ba7945</t>
+        </is>
+      </c>
       <c r="AT143" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU143" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV143" t="inlineStr">
@@ -22028,28 +23414,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U145" t="inlineStr">
+        <is>
+          <t>HOLD_JP_534554c6916adc005164f8ba7945</t>
+        </is>
+      </c>
+      <c r="AA145" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO145" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP145" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR145" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS145" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ145" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS145" t="inlineStr">
+        <is>
+          <t>HOLD_JP_534554c6916adc005164f8ba7945</t>
+        </is>
+      </c>
       <c r="AT145" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU145" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV145" t="inlineStr">
@@ -22176,28 +23576,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U146" t="inlineStr">
+        <is>
+          <t>HOLD_JP_534554c6916adc005164f8ba7945</t>
+        </is>
+      </c>
+      <c r="AA146" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO146" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP146" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR146" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS146" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ146" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS146" t="inlineStr">
+        <is>
+          <t>HOLD_JP_534554c6916adc005164f8ba7945</t>
+        </is>
+      </c>
       <c r="AT146" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU146" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV146" t="inlineStr">
@@ -22324,28 +23738,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U147" t="inlineStr">
+        <is>
+          <t>HOLD_JP_534554c6916adc005164f8ba7945</t>
+        </is>
+      </c>
+      <c r="AA147" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO147" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP147" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR147" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS147" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ147" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS147" t="inlineStr">
+        <is>
+          <t>HOLD_JP_534554c6916adc005164f8ba7945</t>
+        </is>
+      </c>
       <c r="AT147" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU147" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV147" t="inlineStr">
@@ -22472,28 +23900,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U148" t="inlineStr">
+        <is>
+          <t>HOLD_JP_534554c6916adc005164f8ba7945</t>
+        </is>
+      </c>
+      <c r="AA148" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO148" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP148" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR148" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS148" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ148" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS148" t="inlineStr">
+        <is>
+          <t>HOLD_JP_534554c6916adc005164f8ba7945</t>
+        </is>
+      </c>
       <c r="AT148" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU148" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV148" t="inlineStr">
@@ -22770,28 +24212,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U150" t="inlineStr">
+        <is>
+          <t>HOLD_JP_534554c6916adc005164f8ba7945</t>
+        </is>
+      </c>
+      <c r="AA150" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO150" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP150" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR150" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS150" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ150" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS150" t="inlineStr">
+        <is>
+          <t>HOLD_JP_534554c6916adc005164f8ba7945</t>
+        </is>
+      </c>
       <c r="AT150" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU150" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV150" t="inlineStr">
@@ -26831,28 +28287,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U168" t="inlineStr">
+        <is>
+          <t>HOLD_JP_534554c6916adc005164f8ba7945</t>
+        </is>
+      </c>
+      <c r="AA168" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO168" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP168" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR168" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS168" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ168" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS168" t="inlineStr">
+        <is>
+          <t>HOLD_JP_534554c6916adc005164f8ba7945</t>
+        </is>
+      </c>
       <c r="AT168" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU168" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV168" t="inlineStr">
@@ -26979,28 +28449,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U169" t="inlineStr">
+        <is>
+          <t>HOLD_JP_534554c6916adc005164f8ba7945</t>
+        </is>
+      </c>
+      <c r="AA169" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO169" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP169" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR169" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS169" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ169" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS169" t="inlineStr">
+        <is>
+          <t>HOLD_JP_534554c6916adc005164f8ba7945</t>
+        </is>
+      </c>
       <c r="AT169" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU169" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV169" t="inlineStr">
@@ -27127,28 +28611,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U170" t="inlineStr">
+        <is>
+          <t>HOLD_JP_534554c6916adc005164f8ba7945</t>
+        </is>
+      </c>
+      <c r="AA170" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO170" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP170" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR170" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS170" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ170" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS170" t="inlineStr">
+        <is>
+          <t>HOLD_JP_534554c6916adc005164f8ba7945</t>
+        </is>
+      </c>
       <c r="AT170" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU170" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV170" t="inlineStr">
@@ -31338,28 +32836,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U189" t="inlineStr">
+        <is>
+          <t>HOLD_JP_534554c6916adc005164f8ba7945</t>
+        </is>
+      </c>
+      <c r="AA189" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO189" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP189" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR189" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS189" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ189" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS189" t="inlineStr">
+        <is>
+          <t>HOLD_JP_534554c6916adc005164f8ba7945</t>
+        </is>
+      </c>
       <c r="AT189" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU189" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV189" t="inlineStr">
@@ -35399,28 +36911,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U207" t="inlineStr">
+        <is>
+          <t>HOLD_JP_534554c6916adc005164f8ba7945</t>
+        </is>
+      </c>
+      <c r="AA207" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO207" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP207" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR207" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS207" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ207" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS207" t="inlineStr">
+        <is>
+          <t>HOLD_JP_534554c6916adc005164f8ba7945</t>
+        </is>
+      </c>
       <c r="AT207" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU207" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV207" t="inlineStr">
@@ -35547,28 +37073,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U208" t="inlineStr">
+        <is>
+          <t>HOLD_JP_534554c6916adc005164f8ba7945</t>
+        </is>
+      </c>
+      <c r="AA208" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO208" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP208" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR208" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS208" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ208" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS208" t="inlineStr">
+        <is>
+          <t>HOLD_JP_534554c6916adc005164f8ba7945</t>
+        </is>
+      </c>
       <c r="AT208" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU208" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV208" t="inlineStr">
@@ -35695,28 +37235,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U209" t="inlineStr">
+        <is>
+          <t>HOLD_JP_534554c6916adc005164f8ba7945</t>
+        </is>
+      </c>
+      <c r="AA209" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO209" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP209" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR209" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS209" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ209" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS209" t="inlineStr">
+        <is>
+          <t>HOLD_JP_534554c6916adc005164f8ba7945</t>
+        </is>
+      </c>
       <c r="AT209" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU209" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV209" t="inlineStr">
@@ -35843,28 +37397,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U210" t="inlineStr">
+        <is>
+          <t>HOLD_JP_534554c6916adc005164f8ba7945</t>
+        </is>
+      </c>
+      <c r="AA210" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO210" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP210" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR210" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS210" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ210" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS210" t="inlineStr">
+        <is>
+          <t>HOLD_JP_534554c6916adc005164f8ba7945</t>
+        </is>
+      </c>
       <c r="AT210" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU210" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV210" t="inlineStr">
@@ -36141,28 +37709,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U212" t="inlineStr">
+        <is>
+          <t>HOLD_JP_534554c6916adc005164f8ba7945</t>
+        </is>
+      </c>
+      <c r="AA212" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO212" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP212" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR212" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS212" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ212" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS212" t="inlineStr">
+        <is>
+          <t>HOLD_JP_534554c6916adc005164f8ba7945</t>
+        </is>
+      </c>
       <c r="AT212" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU212" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV212" t="inlineStr">
@@ -36289,28 +37871,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U213" t="inlineStr">
+        <is>
+          <t>HOLD_JP_534554c6916adc005164f8ba7945</t>
+        </is>
+      </c>
+      <c r="AA213" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO213" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP213" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR213" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS213" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ213" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS213" t="inlineStr">
+        <is>
+          <t>HOLD_JP_534554c6916adc005164f8ba7945</t>
+        </is>
+      </c>
       <c r="AT213" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU213" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV213" t="inlineStr">
@@ -36437,28 +38033,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U214" t="inlineStr">
+        <is>
+          <t>HOLD_JP_534554c6916adc005164f8ba7945</t>
+        </is>
+      </c>
+      <c r="AA214" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO214" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP214" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR214" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS214" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ214" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS214" t="inlineStr">
+        <is>
+          <t>HOLD_JP_534554c6916adc005164f8ba7945</t>
+        </is>
+      </c>
       <c r="AT214" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU214" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV214" t="inlineStr">
@@ -36585,28 +38195,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U215" t="inlineStr">
+        <is>
+          <t>HOLD_JP_534554c6916adc005164f8ba7945</t>
+        </is>
+      </c>
+      <c r="AA215" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO215" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP215" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR215" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS215" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ215" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS215" t="inlineStr">
+        <is>
+          <t>HOLD_JP_534554c6916adc005164f8ba7945</t>
+        </is>
+      </c>
       <c r="AT215" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU215" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV215" t="inlineStr">
@@ -36883,28 +38507,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U217" t="inlineStr">
+        <is>
+          <t>HOLD_JP_534554c6916adc005164f8ba7945</t>
+        </is>
+      </c>
+      <c r="AA217" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO217" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP217" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR217" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS217" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ217" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS217" t="inlineStr">
+        <is>
+          <t>HOLD_JP_534554c6916adc005164f8ba7945</t>
+        </is>
+      </c>
       <c r="AT217" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU217" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV217" t="inlineStr">
@@ -37031,28 +38669,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U218" t="inlineStr">
+        <is>
+          <t>HOLD_JP_534554c6916adc005164f8ba7945</t>
+        </is>
+      </c>
+      <c r="AA218" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO218" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP218" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR218" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS218" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ218" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS218" t="inlineStr">
+        <is>
+          <t>HOLD_JP_534554c6916adc005164f8ba7945</t>
+        </is>
+      </c>
       <c r="AT218" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU218" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV218" t="inlineStr">
@@ -37179,28 +38831,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U219" t="inlineStr">
+        <is>
+          <t>HOLD_JP_534554c6916adc005164f8ba7945</t>
+        </is>
+      </c>
+      <c r="AA219" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO219" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP219" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR219" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS219" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ219" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS219" t="inlineStr">
+        <is>
+          <t>HOLD_JP_534554c6916adc005164f8ba7945</t>
+        </is>
+      </c>
       <c r="AT219" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU219" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV219" t="inlineStr">
@@ -37327,28 +38993,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U220" t="inlineStr">
+        <is>
+          <t>HOLD_JP_534554c6916adc005164f8ba7945</t>
+        </is>
+      </c>
+      <c r="AA220" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO220" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP220" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR220" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS220" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ220" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS220" t="inlineStr">
+        <is>
+          <t>HOLD_JP_534554c6916adc005164f8ba7945</t>
+        </is>
+      </c>
       <c r="AT220" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU220" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV220" t="inlineStr">

--- a/diseases/d050/2010-2014.xlsx
+++ b/diseases/d050/2010-2014.xlsx
@@ -768,11 +768,6 @@
       <c r="R2" t="n">
         <v>0</v>
       </c>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -785,22 +780,12 @@
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR2" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr"/>
       <c r="AT2" t="n">
         <v>0</v>
-      </c>
-      <c r="AU2" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV2" t="inlineStr">
         <is>
@@ -918,11 +903,6 @@
       <c r="R3" t="n">
         <v>0</v>
       </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -935,22 +915,12 @@
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR3" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr"/>
       <c r="AT3" t="n">
         <v>0</v>
-      </c>
-      <c r="AU3" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV3" t="inlineStr">
         <is>
@@ -1068,11 +1038,6 @@
       <c r="R4" t="n">
         <v>0</v>
       </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1085,22 +1050,12 @@
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR4" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr"/>
       <c r="AT4" t="n">
         <v>0</v>
-      </c>
-      <c r="AU4" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV4" t="inlineStr">
         <is>
@@ -1218,11 +1173,6 @@
       <c r="R5" t="n">
         <v>0</v>
       </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1235,22 +1185,12 @@
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR5" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr"/>
       <c r="AT5" t="n">
         <v>0</v>
-      </c>
-      <c r="AU5" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV5" t="inlineStr">
         <is>
@@ -1368,11 +1308,6 @@
       <c r="R6" t="n">
         <v>0</v>
       </c>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1385,22 +1320,12 @@
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR6" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr"/>
       <c r="AT6" t="n">
         <v>0</v>
-      </c>
-      <c r="AU6" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV6" t="inlineStr">
         <is>
@@ -1518,11 +1443,6 @@
       <c r="R7" t="n">
         <v>0</v>
       </c>
-      <c r="S7" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1535,22 +1455,12 @@
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR7" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr"/>
       <c r="AT7" t="n">
         <v>0</v>
-      </c>
-      <c r="AU7" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV7" t="inlineStr">
         <is>
@@ -1668,11 +1578,6 @@
       <c r="R8" t="n">
         <v>0</v>
       </c>
-      <c r="S8" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1685,22 +1590,12 @@
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR8" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr"/>
       <c r="AT8" t="n">
         <v>0</v>
-      </c>
-      <c r="AU8" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV8" t="inlineStr">
         <is>
@@ -1818,11 +1713,6 @@
       <c r="R9" t="n">
         <v>0</v>
       </c>
-      <c r="S9" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1835,22 +1725,12 @@
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR9" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr"/>
       <c r="AT9" t="n">
         <v>0</v>
-      </c>
-      <c r="AU9" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV9" t="inlineStr">
         <is>
@@ -1968,11 +1848,6 @@
       <c r="R10" t="n">
         <v>0</v>
       </c>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1985,22 +1860,12 @@
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR10" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr"/>
       <c r="AT10" t="n">
         <v>0</v>
-      </c>
-      <c r="AU10" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV10" t="inlineStr">
         <is>
@@ -2118,11 +1983,6 @@
       <c r="R11" t="n">
         <v>0</v>
       </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2135,22 +1995,12 @@
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR11" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr"/>
       <c r="AT11" t="n">
         <v>0</v>
-      </c>
-      <c r="AU11" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV11" t="inlineStr">
         <is>
@@ -2268,11 +2118,6 @@
       <c r="R12" t="n">
         <v>0</v>
       </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2285,22 +2130,12 @@
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR12" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr"/>
       <c r="AT12" t="n">
         <v>0</v>
-      </c>
-      <c r="AU12" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV12" t="inlineStr">
         <is>
@@ -2418,11 +2253,6 @@
       <c r="R13" t="n">
         <v>0</v>
       </c>
-      <c r="S13" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2435,22 +2265,12 @@
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR13" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr"/>
       <c r="AT13" t="n">
         <v>0</v>
-      </c>
-      <c r="AU13" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV13" t="inlineStr">
         <is>
@@ -2568,11 +2388,6 @@
       <c r="R14" t="n">
         <v>0</v>
       </c>
-      <c r="S14" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2585,22 +2400,12 @@
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR14" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr"/>
       <c r="AT14" t="n">
         <v>0</v>
-      </c>
-      <c r="AU14" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV14" t="inlineStr">
         <is>
@@ -2718,11 +2523,6 @@
       <c r="R15" t="n">
         <v>0</v>
       </c>
-      <c r="S15" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2735,22 +2535,12 @@
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR15" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr"/>
       <c r="AT15" t="n">
         <v>0</v>
-      </c>
-      <c r="AU15" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV15" t="inlineStr">
         <is>
@@ -2868,11 +2658,6 @@
       <c r="R16" t="n">
         <v>0</v>
       </c>
-      <c r="S16" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2885,22 +2670,12 @@
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR16" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr"/>
       <c r="AT16" t="n">
         <v>0</v>
-      </c>
-      <c r="AU16" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV16" t="inlineStr">
         <is>
@@ -3018,11 +2793,6 @@
       <c r="R17" t="n">
         <v>0</v>
       </c>
-      <c r="S17" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3035,22 +2805,12 @@
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR17" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr"/>
       <c r="AT17" t="n">
         <v>0</v>
-      </c>
-      <c r="AU17" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV17" t="inlineStr">
         <is>
@@ -3168,11 +2928,6 @@
       <c r="R18" t="n">
         <v>0</v>
       </c>
-      <c r="S18" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3185,22 +2940,12 @@
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR18" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr"/>
       <c r="AT18" t="n">
         <v>0</v>
-      </c>
-      <c r="AU18" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV18" t="inlineStr">
         <is>
@@ -3318,11 +3063,6 @@
       <c r="R19" t="n">
         <v>0</v>
       </c>
-      <c r="S19" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3335,22 +3075,12 @@
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR19" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr"/>
       <c r="AT19" t="n">
         <v>0</v>
-      </c>
-      <c r="AU19" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV19" t="inlineStr">
         <is>
@@ -3468,11 +3198,6 @@
       <c r="R20" t="n">
         <v>0</v>
       </c>
-      <c r="S20" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3485,22 +3210,12 @@
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR20" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr"/>
       <c r="AT20" t="n">
         <v>0</v>
-      </c>
-      <c r="AU20" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV20" t="inlineStr">
         <is>
@@ -3618,11 +3333,6 @@
       <c r="R21" t="n">
         <v>0</v>
       </c>
-      <c r="S21" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3635,22 +3345,12 @@
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR21" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr"/>
       <c r="AT21" t="n">
         <v>0</v>
-      </c>
-      <c r="AU21" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV21" t="inlineStr">
         <is>
@@ -3768,11 +3468,6 @@
       <c r="R22" t="n">
         <v>0</v>
       </c>
-      <c r="S22" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3785,22 +3480,12 @@
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR22" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr"/>
       <c r="AT22" t="n">
         <v>0</v>
-      </c>
-      <c r="AU22" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV22" t="inlineStr">
         <is>
@@ -4404,11 +4089,6 @@
       <c r="R26" t="n">
         <v>0</v>
       </c>
-      <c r="S26" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -4421,22 +4101,12 @@
       </c>
       <c r="AP26" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR26" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS26" t="inlineStr"/>
       <c r="AT26" t="n">
         <v>0</v>
-      </c>
-      <c r="AU26" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV26" t="inlineStr">
         <is>
@@ -5202,11 +4872,6 @@
       <c r="R31" t="n">
         <v>0</v>
       </c>
-      <c r="S31" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -5219,22 +4884,12 @@
       </c>
       <c r="AP31" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR31" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS31" t="inlineStr"/>
       <c r="AT31" t="n">
         <v>0</v>
-      </c>
-      <c r="AU31" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV31" t="inlineStr">
         <is>
@@ -6162,11 +5817,6 @@
       <c r="R37" t="n">
         <v>0</v>
       </c>
-      <c r="S37" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -6179,22 +5829,12 @@
       </c>
       <c r="AP37" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR37" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS37" t="inlineStr"/>
       <c r="AT37" t="n">
         <v>0</v>
-      </c>
-      <c r="AU37" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV37" t="inlineStr">
         <is>
@@ -6960,11 +6600,6 @@
       <c r="R42" t="n">
         <v>0</v>
       </c>
-      <c r="S42" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -6977,22 +6612,12 @@
       </c>
       <c r="AP42" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR42" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS42" t="inlineStr"/>
       <c r="AT42" t="n">
         <v>0</v>
-      </c>
-      <c r="AU42" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV42" t="inlineStr">
         <is>
@@ -7920,11 +7545,6 @@
       <c r="R48" t="n">
         <v>0</v>
       </c>
-      <c r="S48" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA48" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -7937,22 +7557,12 @@
       </c>
       <c r="AP48" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR48" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS48" t="inlineStr"/>
       <c r="AT48" t="n">
         <v>0</v>
-      </c>
-      <c r="AU48" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV48" t="inlineStr">
         <is>
@@ -8718,11 +8328,6 @@
       <c r="R53" t="n">
         <v>0</v>
       </c>
-      <c r="S53" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA53" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -8735,22 +8340,12 @@
       </c>
       <c r="AP53" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR53" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS53" t="inlineStr"/>
       <c r="AT53" t="n">
         <v>0</v>
-      </c>
-      <c r="AU53" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV53" t="inlineStr">
         <is>
@@ -9516,11 +9111,6 @@
       <c r="R58" t="n">
         <v>0</v>
       </c>
-      <c r="S58" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA58" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -9533,22 +9123,12 @@
       </c>
       <c r="AP58" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR58" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS58" t="inlineStr"/>
       <c r="AT58" t="n">
         <v>0</v>
-      </c>
-      <c r="AU58" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV58" t="inlineStr">
         <is>
@@ -10314,11 +9894,6 @@
       <c r="R63" t="n">
         <v>0</v>
       </c>
-      <c r="S63" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA63" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -10331,22 +9906,12 @@
       </c>
       <c r="AP63" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR63" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS63" t="inlineStr"/>
       <c r="AT63" t="n">
         <v>0</v>
-      </c>
-      <c r="AU63" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV63" t="inlineStr">
         <is>
@@ -11274,11 +10839,6 @@
       <c r="R69" t="n">
         <v>0</v>
       </c>
-      <c r="S69" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA69" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -11291,22 +10851,12 @@
       </c>
       <c r="AP69" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR69" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS69" t="inlineStr"/>
       <c r="AT69" t="n">
         <v>0</v>
-      </c>
-      <c r="AU69" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV69" t="inlineStr">
         <is>
@@ -12072,11 +11622,6 @@
       <c r="R74" t="n">
         <v>0</v>
       </c>
-      <c r="S74" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA74" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -12089,22 +11634,12 @@
       </c>
       <c r="AP74" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR74" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS74" t="inlineStr"/>
       <c r="AT74" t="n">
         <v>0</v>
-      </c>
-      <c r="AU74" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV74" t="inlineStr">
         <is>
@@ -12870,11 +12405,6 @@
       <c r="R79" t="n">
         <v>0</v>
       </c>
-      <c r="S79" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA79" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -12887,22 +12417,12 @@
       </c>
       <c r="AP79" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR79" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS79" t="inlineStr"/>
       <c r="AT79" t="n">
         <v>0</v>
-      </c>
-      <c r="AU79" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV79" t="inlineStr">
         <is>
@@ -13830,11 +13350,6 @@
       <c r="R85" t="n">
         <v>0</v>
       </c>
-      <c r="S85" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA85" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -13847,22 +13362,12 @@
       </c>
       <c r="AP85" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR85" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS85" t="inlineStr"/>
       <c r="AT85" t="n">
         <v>0</v>
-      </c>
-      <c r="AU85" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV85" t="inlineStr">
         <is>
@@ -14628,11 +14133,6 @@
       <c r="R90" t="n">
         <v>0</v>
       </c>
-      <c r="S90" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA90" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -14645,22 +14145,12 @@
       </c>
       <c r="AP90" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR90" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS90" t="inlineStr"/>
       <c r="AT90" t="n">
         <v>0</v>
-      </c>
-      <c r="AU90" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV90" t="inlineStr">
         <is>
@@ -15588,11 +15078,6 @@
       <c r="R96" t="n">
         <v>0</v>
       </c>
-      <c r="S96" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA96" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -15605,22 +15090,12 @@
       </c>
       <c r="AP96" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR96" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS96" t="inlineStr"/>
       <c r="AT96" t="n">
         <v>0</v>
-      </c>
-      <c r="AU96" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV96" t="inlineStr">
         <is>
@@ -16386,11 +15861,6 @@
       <c r="R101" t="n">
         <v>0</v>
       </c>
-      <c r="S101" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA101" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -16403,22 +15873,12 @@
       </c>
       <c r="AP101" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR101" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS101" t="inlineStr"/>
       <c r="AT101" t="n">
         <v>0</v>
-      </c>
-      <c r="AU101" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV101" t="inlineStr">
         <is>
@@ -17184,11 +16644,6 @@
       <c r="R106" t="n">
         <v>0</v>
       </c>
-      <c r="S106" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA106" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -17201,22 +16656,12 @@
       </c>
       <c r="AP106" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR106" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS106" t="inlineStr"/>
       <c r="AT106" t="n">
         <v>0</v>
-      </c>
-      <c r="AU106" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV106" t="inlineStr">
         <is>
@@ -18144,11 +17589,6 @@
       <c r="R112" t="n">
         <v>0</v>
       </c>
-      <c r="S112" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA112" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -18161,22 +17601,12 @@
       </c>
       <c r="AP112" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR112" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS112" t="inlineStr"/>
       <c r="AT112" t="n">
         <v>0</v>
-      </c>
-      <c r="AU112" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV112" t="inlineStr">
         <is>
@@ -18942,11 +18372,6 @@
       <c r="R117" t="n">
         <v>0</v>
       </c>
-      <c r="S117" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA117" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -18959,22 +18384,12 @@
       </c>
       <c r="AP117" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR117" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS117" t="inlineStr"/>
       <c r="AT117" t="n">
         <v>0</v>
-      </c>
-      <c r="AU117" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV117" t="inlineStr">
         <is>
@@ -19740,11 +19155,6 @@
       <c r="R122" t="n">
         <v>0</v>
       </c>
-      <c r="S122" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA122" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -19757,22 +19167,12 @@
       </c>
       <c r="AP122" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR122" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS122" t="inlineStr"/>
       <c r="AT122" t="n">
         <v>0</v>
-      </c>
-      <c r="AU122" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV122" t="inlineStr">
         <is>
@@ -20538,11 +19938,6 @@
       <c r="R127" t="n">
         <v>0</v>
       </c>
-      <c r="S127" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA127" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -20555,22 +19950,12 @@
       </c>
       <c r="AP127" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR127" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS127" t="inlineStr"/>
       <c r="AT127" t="n">
         <v>0</v>
-      </c>
-      <c r="AU127" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV127" t="inlineStr">
         <is>
@@ -21498,11 +20883,6 @@
       <c r="R133" t="n">
         <v>0</v>
       </c>
-      <c r="S133" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA133" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -21515,22 +20895,12 @@
       </c>
       <c r="AP133" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR133" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS133" t="inlineStr"/>
       <c r="AT133" t="n">
         <v>0</v>
-      </c>
-      <c r="AU133" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV133" t="inlineStr">
         <is>
@@ -22296,11 +21666,6 @@
       <c r="R138" t="n">
         <v>0</v>
       </c>
-      <c r="S138" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA138" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -22313,22 +21678,12 @@
       </c>
       <c r="AP138" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR138" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS138" t="inlineStr"/>
       <c r="AT138" t="n">
         <v>0</v>
-      </c>
-      <c r="AU138" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV138" t="inlineStr">
         <is>
@@ -23256,11 +22611,6 @@
       <c r="R144" t="n">
         <v>0</v>
       </c>
-      <c r="S144" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA144" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -23273,22 +22623,12 @@
       </c>
       <c r="AP144" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR144" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS144" t="inlineStr"/>
       <c r="AT144" t="n">
         <v>0</v>
-      </c>
-      <c r="AU144" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV144" t="inlineStr">
         <is>
@@ -24054,11 +23394,6 @@
       <c r="R149" t="n">
         <v>0</v>
       </c>
-      <c r="S149" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA149" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -24071,22 +23406,12 @@
       </c>
       <c r="AP149" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR149" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS149" t="inlineStr"/>
       <c r="AT149" t="n">
         <v>0</v>
-      </c>
-      <c r="AU149" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV149" t="inlineStr">
         <is>
@@ -24314,17 +23639,17 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>DE-HH</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>Hamburg, Germany</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
@@ -24363,126 +23688,34 @@
       <c r="O151" t="n">
         <v>1</v>
       </c>
-      <c r="P151" t="n">
+      <c r="U151" t="inlineStr">
+        <is>
+          <t>HOLD_DE_a46d3e1400ce8c779c6fd41d7e0c</t>
+        </is>
+      </c>
+      <c r="AA151" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AO151" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP151" t="inlineStr">
+        <is>
+          <t>published_series</t>
+        </is>
+      </c>
+      <c r="AS151" t="inlineStr">
+        <is>
+          <t>HOLD_DE_a46d3e1400ce8c779c6fd41d7e0c</t>
+        </is>
+      </c>
+      <c r="AT151" t="n">
         <v>1</v>
       </c>
-      <c r="U151" t="inlineStr">
-        <is>
-          <t>SER_DE_RKI_SURVSTAT_SOURCE_NATIVE</t>
-        </is>
-      </c>
-      <c r="V151" t="inlineStr">
-        <is>
-          <t>SER_DE_RKI_SURVSTAT_SOURCE_NATIVE</t>
-        </is>
-      </c>
-      <c r="W151" t="inlineStr">
-        <is>
-          <t>SRC_DE_RKI_SURVSTAT</t>
-        </is>
-      </c>
-      <c r="X151" t="inlineStr">
-        <is>
-          <t>__source_native__</t>
-        </is>
-      </c>
-      <c r="Y151" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z151" t="inlineStr">
-        <is>
-          <t>national_ifsG_notification_registry</t>
-        </is>
-      </c>
-      <c r="AA151" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
-      <c r="AB151" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC151" t="inlineStr">
-        <is>
-          <t>country:DE:national</t>
-        </is>
-      </c>
-      <c r="AD151" t="inlineStr">
-        <is>
-          <t>sha256:d93dc9dc4f6141dbe5cd43d9314d102c906ca0e9ca38d971733bac05e6076158</t>
-        </is>
-      </c>
-      <c r="AE151" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF151" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG151" t="inlineStr">
-        <is>
-          <t>direct_only</t>
-        </is>
-      </c>
-      <c r="AH151" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI151" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ151" t="inlineStr">
-        <is>
-          <t>DE_RKI_SURVSTAT_source_native</t>
-        </is>
-      </c>
-      <c r="AK151" t="inlineStr">
-        <is>
-          <t>Source-native RKI SurvStat category. The original pathogen/category is retained in dimensions and is not automatically rolled up.</t>
-        </is>
-      </c>
-      <c r="AM151" t="inlineStr">
-        <is>
-          <t>raw</t>
-        </is>
-      </c>
-      <c r="AN151" t="b">
-        <v>0</v>
-      </c>
-      <c r="AO151" t="inlineStr">
-        <is>
-          <t>source_observations_only</t>
-        </is>
-      </c>
-      <c r="AP151" t="inlineStr">
-        <is>
-          <t>no_eligible_public_projection</t>
-        </is>
-      </c>
-      <c r="AQ151" t="inlineStr">
-        <is>
-          <t>source_observations_only</t>
-        </is>
-      </c>
-      <c r="AS151" t="inlineStr"/>
-      <c r="AT151" t="n">
-        <v>2</v>
-      </c>
-      <c r="AU151" t="inlineStr">
-        <is>
-          <t>Registered source observations are retained for provenance and downloads, but their measure is not eligible for the public cases curve.</t>
-        </is>
-      </c>
       <c r="AV151" t="inlineStr">
         <is>
           <t>rki_survstat</t>
@@ -24495,12 +23728,12 @@
       </c>
       <c r="AX151" t="inlineStr">
         <is>
-          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
+          <t>https://survstat.rki.de/Content/Query/Main.aspx</t>
         </is>
       </c>
       <c r="AY151" t="inlineStr">
         <is>
-          <t>official_webforms_csv_export</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ151" t="inlineStr">
@@ -24515,12 +23748,12 @@
       </c>
       <c r="BB151" t="inlineStr">
         <is>
-          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
+          <t>https://survstat.rki.de/Content/Query/Main.aspx</t>
         </is>
       </c>
       <c r="BC151" t="inlineStr">
         <is>
-          <t>official_webforms_csv_export</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -24552,12 +23785,12 @@
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>DE-HH</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Hamburg, Germany</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
@@ -24582,7 +23815,7 @@
       </c>
       <c r="L152" t="inlineStr">
         <is>
-          <t>2014-09-08</t>
+          <t>2014-09-12</t>
         </is>
       </c>
       <c r="M152" t="inlineStr">
@@ -24591,19 +23824,25 @@
         </is>
       </c>
       <c r="N152" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O152" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="Q152" t="n">
+        <v>0</v>
+      </c>
+      <c r="R152" t="n">
+        <v>0</v>
       </c>
       <c r="S152" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="U152" t="inlineStr">
         <is>
-          <t>HOLD_DE_a46d3e1400ce8c779c6fd41d7e0c</t>
+          <t>HOLD_JP_534554c6916adc005164f8ba7945</t>
         </is>
       </c>
       <c r="AA152" t="inlineStr">
@@ -24613,7 +23852,7 @@
       </c>
       <c r="AO152" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP152" t="inlineStr">
@@ -24623,12 +23862,12 @@
       </c>
       <c r="AQ152" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill</t>
         </is>
       </c>
       <c r="AS152" t="inlineStr">
         <is>
-          <t>HOLD_DE_a46d3e1400ce8c779c6fd41d7e0c</t>
+          <t>HOLD_JP_534554c6916adc005164f8ba7945</t>
         </is>
       </c>
       <c r="AT152" t="n">
@@ -24636,22 +23875,22 @@
       </c>
       <c r="AU152" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV152" t="inlineStr">
         <is>
-          <t>rki_survstat</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW152" t="inlineStr">
         <is>
-          <t>Germany RKI SurvStat 2.0</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX152" t="inlineStr">
         <is>
-          <t>https://survstat.rki.de/Content/Query/Main.aspx</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY152" t="inlineStr">
@@ -24661,17 +23900,17 @@
       </c>
       <c r="AZ152" t="inlineStr">
         <is>
-          <t>rki_survstat</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA152" t="inlineStr">
         <is>
-          <t>Germany RKI SurvStat 2.0</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB152" t="inlineStr">
         <is>
-          <t>https://survstat.rki.de/Content/Query/Main.aspx</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC152" t="inlineStr">
@@ -24703,17 +23942,17 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>DE-HH</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Hamburg, Germany</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
@@ -24738,7 +23977,7 @@
       </c>
       <c r="L153" t="inlineStr">
         <is>
-          <t>2014-09-08</t>
+          <t>2014-09-19</t>
         </is>
       </c>
       <c r="M153" t="inlineStr">
@@ -24747,39 +23986,25 @@
         </is>
       </c>
       <c r="N153" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O153" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="Q153" t="n">
+        <v>0</v>
+      </c>
+      <c r="R153" t="n">
+        <v>0</v>
+      </c>
+      <c r="S153" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="U153" t="inlineStr">
         <is>
-          <t>HOLD_DE_a46d3e1400ce8c779c6fd41d7e0c</t>
-        </is>
-      </c>
-      <c r="V153" t="inlineStr">
-        <is>
-          <t>ebolafieber</t>
-        </is>
-      </c>
-      <c r="W153" t="inlineStr">
-        <is>
-          <t>SRC_DE_RKI_SURVSTAT</t>
-        </is>
-      </c>
-      <c r="X153" t="inlineStr">
-        <is>
-          <t>Ebolafieber</t>
-        </is>
-      </c>
-      <c r="Y153" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z153" t="inlineStr">
-        <is>
-          <t>notification</t>
+          <t>HOLD_JP_534554c6916adc005164f8ba7945</t>
         </is>
       </c>
       <c r="AA153" t="inlineStr">
@@ -24787,67 +24012,9 @@
           <t>unknown</t>
         </is>
       </c>
-      <c r="AB153" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC153" t="inlineStr">
-        <is>
-          <t>country:DE-HH:national</t>
-        </is>
-      </c>
-      <c r="AD153" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE153" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF153" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG153" t="inlineStr">
-        <is>
-          <t>direct_only</t>
-        </is>
-      </c>
-      <c r="AH153" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI153" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ153" t="inlineStr">
-        <is>
-          <t>source-current</t>
-        </is>
-      </c>
-      <c r="AL153" t="inlineStr">
-        <is>
-          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
-        </is>
-      </c>
-      <c r="AM153" t="inlineStr">
-        <is>
-          <t>raw</t>
-        </is>
-      </c>
-      <c r="AN153" t="b">
-        <v>1</v>
-      </c>
       <c r="AO153" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP153" t="inlineStr">
@@ -24857,12 +24024,12 @@
       </c>
       <c r="AQ153" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill</t>
         </is>
       </c>
       <c r="AS153" t="inlineStr">
         <is>
-          <t>HOLD_DE_a46d3e1400ce8c779c6fd41d7e0c</t>
+          <t>HOLD_JP_534554c6916adc005164f8ba7945</t>
         </is>
       </c>
       <c r="AT153" t="n">
@@ -24870,22 +24037,22 @@
       </c>
       <c r="AU153" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV153" t="inlineStr">
         <is>
-          <t>rki_survstat</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW153" t="inlineStr">
         <is>
-          <t>Germany RKI SurvStat 2.0</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX153" t="inlineStr">
         <is>
-          <t>https://survstat.rki.de/Content/Query/Main.aspx</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY153" t="inlineStr">
@@ -24895,17 +24062,17 @@
       </c>
       <c r="AZ153" t="inlineStr">
         <is>
-          <t>rki_survstat</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA153" t="inlineStr">
         <is>
-          <t>Germany RKI SurvStat 2.0</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB153" t="inlineStr">
         <is>
-          <t>https://survstat.rki.de/Content/Query/Main.aspx</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC153" t="inlineStr">
@@ -24972,7 +24139,7 @@
       </c>
       <c r="L154" t="inlineStr">
         <is>
-          <t>2014-09-12</t>
+          <t>2014-09-26</t>
         </is>
       </c>
       <c r="M154" t="inlineStr">
@@ -25104,12 +24271,12 @@
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>DE-HE</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Hessen, Germany</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
@@ -25134,7 +24301,7 @@
       </c>
       <c r="L155" t="inlineStr">
         <is>
-          <t>2014-09-19</t>
+          <t>2014-09-29</t>
         </is>
       </c>
       <c r="M155" t="inlineStr">
@@ -25143,25 +24310,14 @@
         </is>
       </c>
       <c r="N155" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O155" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q155" t="n">
-        <v>0</v>
-      </c>
-      <c r="R155" t="n">
-        <v>0</v>
-      </c>
-      <c r="S155" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="U155" t="inlineStr">
         <is>
-          <t>HOLD_JP_534554c6916adc005164f8ba7945</t>
+          <t>HOLD_DE_a46d3e1400ce8c779c6fd41d7e0c</t>
         </is>
       </c>
       <c r="AA155" t="inlineStr">
@@ -25171,45 +24327,35 @@
       </c>
       <c r="AO155" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP155" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ155" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS155" t="inlineStr">
         <is>
-          <t>HOLD_JP_534554c6916adc005164f8ba7945</t>
+          <t>HOLD_DE_a46d3e1400ce8c779c6fd41d7e0c</t>
         </is>
       </c>
       <c r="AT155" t="n">
         <v>1</v>
       </c>
-      <c r="AU155" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
-      </c>
       <c r="AV155" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>rki_survstat</t>
         </is>
       </c>
       <c r="AW155" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Germany RKI SurvStat 2.0</t>
         </is>
       </c>
       <c r="AX155" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://survstat.rki.de/Content/Query/Main.aspx</t>
         </is>
       </c>
       <c r="AY155" t="inlineStr">
@@ -25219,17 +24365,17 @@
       </c>
       <c r="AZ155" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>rki_survstat</t>
         </is>
       </c>
       <c r="BA155" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Germany RKI SurvStat 2.0</t>
         </is>
       </c>
       <c r="BB155" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://survstat.rki.de/Content/Query/Main.aspx</t>
         </is>
       </c>
       <c r="BC155" t="inlineStr">
@@ -25266,12 +24412,12 @@
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
@@ -25296,12 +24442,12 @@
       </c>
       <c r="L156" t="inlineStr">
         <is>
-          <t>2014-09-26</t>
+          <t>2014-10-01</t>
         </is>
       </c>
       <c r="M156" t="inlineStr">
         <is>
-          <t>2014-09</t>
+          <t>2014-10</t>
         </is>
       </c>
       <c r="N156" t="n">
@@ -25310,93 +24456,66 @@
       <c r="O156" t="n">
         <v>0</v>
       </c>
-      <c r="Q156" t="n">
-        <v>0</v>
-      </c>
       <c r="R156" t="n">
         <v>0</v>
       </c>
-      <c r="S156" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="U156" t="inlineStr">
-        <is>
-          <t>HOLD_JP_534554c6916adc005164f8ba7945</t>
-        </is>
-      </c>
       <c r="AA156" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO156" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP156" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ156" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
-        </is>
-      </c>
-      <c r="AS156" t="inlineStr">
-        <is>
-          <t>HOLD_JP_534554c6916adc005164f8ba7945</t>
-        </is>
-      </c>
+          <t>published_series</t>
+        </is>
+      </c>
+      <c r="AS156" t="inlineStr"/>
       <c r="AT156" t="n">
-        <v>1</v>
-      </c>
-      <c r="AU156" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
+        <v>0</v>
       </c>
       <c r="AV156" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW156" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX156" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY156" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ156" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA156" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB156" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC156" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -25423,17 +24542,17 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
@@ -25458,178 +24577,107 @@
       </c>
       <c r="L157" t="inlineStr">
         <is>
-          <t>2014-09-29</t>
+          <t>2014-10-03</t>
         </is>
       </c>
       <c r="M157" t="inlineStr">
         <is>
-          <t>2014-09</t>
+          <t>2014-10</t>
         </is>
       </c>
       <c r="N157" t="n">
+        <v>0</v>
+      </c>
+      <c r="O157" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q157" t="n">
+        <v>0</v>
+      </c>
+      <c r="R157" t="n">
+        <v>0</v>
+      </c>
+      <c r="S157" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U157" t="inlineStr">
+        <is>
+          <t>HOLD_JP_534554c6916adc005164f8ba7945</t>
+        </is>
+      </c>
+      <c r="AA157" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AO157" t="inlineStr">
+        <is>
+          <t>mixed</t>
+        </is>
+      </c>
+      <c r="AP157" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ157" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS157" t="inlineStr">
+        <is>
+          <t>HOLD_JP_534554c6916adc005164f8ba7945</t>
+        </is>
+      </c>
+      <c r="AT157" t="n">
         <v>1</v>
       </c>
-      <c r="O157" t="n">
-        <v>1</v>
-      </c>
-      <c r="P157" t="n">
-        <v>1</v>
-      </c>
-      <c r="U157" t="inlineStr">
-        <is>
-          <t>SER_DE_RKI_SURVSTAT_SOURCE_NATIVE</t>
-        </is>
-      </c>
-      <c r="V157" t="inlineStr">
-        <is>
-          <t>SER_DE_RKI_SURVSTAT_SOURCE_NATIVE</t>
-        </is>
-      </c>
-      <c r="W157" t="inlineStr">
-        <is>
-          <t>SRC_DE_RKI_SURVSTAT</t>
-        </is>
-      </c>
-      <c r="X157" t="inlineStr">
-        <is>
-          <t>__source_native__</t>
-        </is>
-      </c>
-      <c r="Y157" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z157" t="inlineStr">
-        <is>
-          <t>national_ifsG_notification_registry</t>
-        </is>
-      </c>
-      <c r="AA157" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
-      <c r="AB157" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC157" t="inlineStr">
-        <is>
-          <t>country:DE:national</t>
-        </is>
-      </c>
-      <c r="AD157" t="inlineStr">
-        <is>
-          <t>sha256:d93dc9dc4f6141dbe5cd43d9314d102c906ca0e9ca38d971733bac05e6076158</t>
-        </is>
-      </c>
-      <c r="AE157" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF157" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG157" t="inlineStr">
-        <is>
-          <t>direct_only</t>
-        </is>
-      </c>
-      <c r="AH157" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI157" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ157" t="inlineStr">
-        <is>
-          <t>DE_RKI_SURVSTAT_source_native</t>
-        </is>
-      </c>
-      <c r="AK157" t="inlineStr">
-        <is>
-          <t>Source-native RKI SurvStat category. The original pathogen/category is retained in dimensions and is not automatically rolled up.</t>
-        </is>
-      </c>
-      <c r="AM157" t="inlineStr">
-        <is>
-          <t>raw</t>
-        </is>
-      </c>
-      <c r="AN157" t="b">
-        <v>0</v>
-      </c>
-      <c r="AO157" t="inlineStr">
-        <is>
-          <t>source_observations_only</t>
-        </is>
-      </c>
-      <c r="AP157" t="inlineStr">
-        <is>
-          <t>no_eligible_public_projection</t>
-        </is>
-      </c>
-      <c r="AQ157" t="inlineStr">
-        <is>
-          <t>source_observations_only</t>
-        </is>
-      </c>
-      <c r="AS157" t="inlineStr"/>
-      <c r="AT157" t="n">
-        <v>2</v>
-      </c>
       <c r="AU157" t="inlineStr">
         <is>
-          <t>Registered source observations are retained for provenance and downloads, but their measure is not eligible for the public cases curve.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV157" t="inlineStr">
         <is>
-          <t>rki_survstat</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW157" t="inlineStr">
         <is>
-          <t>Germany RKI SurvStat 2.0</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX157" t="inlineStr">
         <is>
-          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY157" t="inlineStr">
         <is>
-          <t>official_webforms_csv_export</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ157" t="inlineStr">
         <is>
-          <t>rki_survstat</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA157" t="inlineStr">
         <is>
-          <t>Germany RKI SurvStat 2.0</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB157" t="inlineStr">
         <is>
-          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC157" t="inlineStr">
         <is>
-          <t>official_webforms_csv_export</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -25661,12 +24709,12 @@
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>DE-HE</t>
+          <t>DE-SN</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Hessen, Germany</t>
+          <t>Sachsen, Germany</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
@@ -25691,12 +24739,12 @@
       </c>
       <c r="L158" t="inlineStr">
         <is>
-          <t>2014-09-29</t>
+          <t>2014-10-06</t>
         </is>
       </c>
       <c r="M158" t="inlineStr">
         <is>
-          <t>2014-09</t>
+          <t>2014-10</t>
         </is>
       </c>
       <c r="N158" t="n">
@@ -25705,11 +24753,6 @@
       <c r="O158" t="n">
         <v>1</v>
       </c>
-      <c r="S158" t="inlineStr">
-        <is>
-          <t>missing_population</t>
-        </is>
-      </c>
       <c r="U158" t="inlineStr">
         <is>
           <t>HOLD_DE_a46d3e1400ce8c779c6fd41d7e0c</t>
@@ -25727,12 +24770,7 @@
       </c>
       <c r="AP158" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ158" t="inlineStr">
-        <is>
-          <t>parity</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS158" t="inlineStr">
@@ -25742,11 +24780,6 @@
       </c>
       <c r="AT158" t="n">
         <v>1</v>
-      </c>
-      <c r="AU158" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series.</t>
-        </is>
       </c>
       <c r="AV158" t="inlineStr">
         <is>
@@ -25812,17 +24845,17 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>DE-HE</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Hessen, Germany</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
@@ -25847,48 +24880,34 @@
       </c>
       <c r="L159" t="inlineStr">
         <is>
-          <t>2014-09-29</t>
+          <t>2014-10-10</t>
         </is>
       </c>
       <c r="M159" t="inlineStr">
         <is>
-          <t>2014-09</t>
+          <t>2014-10</t>
         </is>
       </c>
       <c r="N159" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O159" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="Q159" t="n">
+        <v>0</v>
+      </c>
+      <c r="R159" t="n">
+        <v>0</v>
+      </c>
+      <c r="S159" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="U159" t="inlineStr">
         <is>
-          <t>HOLD_DE_a46d3e1400ce8c779c6fd41d7e0c</t>
-        </is>
-      </c>
-      <c r="V159" t="inlineStr">
-        <is>
-          <t>ebolafieber</t>
-        </is>
-      </c>
-      <c r="W159" t="inlineStr">
-        <is>
-          <t>SRC_DE_RKI_SURVSTAT</t>
-        </is>
-      </c>
-      <c r="X159" t="inlineStr">
-        <is>
-          <t>Ebolafieber</t>
-        </is>
-      </c>
-      <c r="Y159" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z159" t="inlineStr">
-        <is>
-          <t>notification</t>
+          <t>HOLD_JP_534554c6916adc005164f8ba7945</t>
         </is>
       </c>
       <c r="AA159" t="inlineStr">
@@ -25896,67 +24915,9 @@
           <t>unknown</t>
         </is>
       </c>
-      <c r="AB159" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC159" t="inlineStr">
-        <is>
-          <t>country:DE-HE:national</t>
-        </is>
-      </c>
-      <c r="AD159" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE159" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF159" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG159" t="inlineStr">
-        <is>
-          <t>direct_only</t>
-        </is>
-      </c>
-      <c r="AH159" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI159" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ159" t="inlineStr">
-        <is>
-          <t>source-current</t>
-        </is>
-      </c>
-      <c r="AL159" t="inlineStr">
-        <is>
-          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
-        </is>
-      </c>
-      <c r="AM159" t="inlineStr">
-        <is>
-          <t>raw</t>
-        </is>
-      </c>
-      <c r="AN159" t="b">
-        <v>1</v>
-      </c>
       <c r="AO159" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP159" t="inlineStr">
@@ -25966,12 +24927,12 @@
       </c>
       <c r="AQ159" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill</t>
         </is>
       </c>
       <c r="AS159" t="inlineStr">
         <is>
-          <t>HOLD_DE_a46d3e1400ce8c779c6fd41d7e0c</t>
+          <t>HOLD_JP_534554c6916adc005164f8ba7945</t>
         </is>
       </c>
       <c r="AT159" t="n">
@@ -25979,22 +24940,22 @@
       </c>
       <c r="AU159" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV159" t="inlineStr">
         <is>
-          <t>rki_survstat</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW159" t="inlineStr">
         <is>
-          <t>Germany RKI SurvStat 2.0</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX159" t="inlineStr">
         <is>
-          <t>https://survstat.rki.de/Content/Query/Main.aspx</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY159" t="inlineStr">
@@ -26004,17 +24965,17 @@
       </c>
       <c r="AZ159" t="inlineStr">
         <is>
-          <t>rki_survstat</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA159" t="inlineStr">
         <is>
-          <t>Germany RKI SurvStat 2.0</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB159" t="inlineStr">
         <is>
-          <t>https://survstat.rki.de/Content/Query/Main.aspx</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC159" t="inlineStr">
@@ -26051,12 +25012,12 @@
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
@@ -26081,7 +25042,7 @@
       </c>
       <c r="L160" t="inlineStr">
         <is>
-          <t>2014-10-01</t>
+          <t>2014-10-17</t>
         </is>
       </c>
       <c r="M160" t="inlineStr">
@@ -26095,6 +25056,9 @@
       <c r="O160" t="n">
         <v>0</v>
       </c>
+      <c r="Q160" t="n">
+        <v>0</v>
+      </c>
       <c r="R160" t="n">
         <v>0</v>
       </c>
@@ -26103,73 +25067,82 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U160" t="inlineStr">
+        <is>
+          <t>HOLD_JP_534554c6916adc005164f8ba7945</t>
+        </is>
+      </c>
       <c r="AA160" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="AO160" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP160" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR160" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS160" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ160" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS160" t="inlineStr">
+        <is>
+          <t>HOLD_JP_534554c6916adc005164f8ba7945</t>
+        </is>
+      </c>
       <c r="AT160" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU160" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV160" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW160" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX160" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY160" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ160" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA160" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB160" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC160" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -26231,7 +25204,7 @@
       </c>
       <c r="L161" t="inlineStr">
         <is>
-          <t>2014-10-03</t>
+          <t>2014-10-24</t>
         </is>
       </c>
       <c r="M161" t="inlineStr">
@@ -26358,17 +25331,17 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
@@ -26393,7 +25366,7 @@
       </c>
       <c r="L162" t="inlineStr">
         <is>
-          <t>2014-10-06</t>
+          <t>2014-10-31</t>
         </is>
       </c>
       <c r="M162" t="inlineStr">
@@ -26402,169 +25375,98 @@
         </is>
       </c>
       <c r="N162" t="n">
+        <v>0</v>
+      </c>
+      <c r="O162" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q162" t="n">
+        <v>0</v>
+      </c>
+      <c r="R162" t="n">
+        <v>0</v>
+      </c>
+      <c r="S162" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U162" t="inlineStr">
+        <is>
+          <t>HOLD_JP_534554c6916adc005164f8ba7945</t>
+        </is>
+      </c>
+      <c r="AA162" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AO162" t="inlineStr">
+        <is>
+          <t>mixed</t>
+        </is>
+      </c>
+      <c r="AP162" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ162" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS162" t="inlineStr">
+        <is>
+          <t>HOLD_JP_534554c6916adc005164f8ba7945</t>
+        </is>
+      </c>
+      <c r="AT162" t="n">
         <v>1</v>
       </c>
-      <c r="O162" t="n">
-        <v>1</v>
-      </c>
-      <c r="P162" t="n">
-        <v>1</v>
-      </c>
-      <c r="U162" t="inlineStr">
-        <is>
-          <t>SER_DE_RKI_SURVSTAT_SOURCE_NATIVE</t>
-        </is>
-      </c>
-      <c r="V162" t="inlineStr">
-        <is>
-          <t>SER_DE_RKI_SURVSTAT_SOURCE_NATIVE</t>
-        </is>
-      </c>
-      <c r="W162" t="inlineStr">
-        <is>
-          <t>SRC_DE_RKI_SURVSTAT</t>
-        </is>
-      </c>
-      <c r="X162" t="inlineStr">
-        <is>
-          <t>__source_native__</t>
-        </is>
-      </c>
-      <c r="Y162" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z162" t="inlineStr">
-        <is>
-          <t>national_ifsG_notification_registry</t>
-        </is>
-      </c>
-      <c r="AA162" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
-      <c r="AB162" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC162" t="inlineStr">
-        <is>
-          <t>country:DE:national</t>
-        </is>
-      </c>
-      <c r="AD162" t="inlineStr">
-        <is>
-          <t>sha256:d93dc9dc4f6141dbe5cd43d9314d102c906ca0e9ca38d971733bac05e6076158</t>
-        </is>
-      </c>
-      <c r="AE162" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF162" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG162" t="inlineStr">
-        <is>
-          <t>direct_only</t>
-        </is>
-      </c>
-      <c r="AH162" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI162" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ162" t="inlineStr">
-        <is>
-          <t>DE_RKI_SURVSTAT_source_native</t>
-        </is>
-      </c>
-      <c r="AK162" t="inlineStr">
-        <is>
-          <t>Source-native RKI SurvStat category. The original pathogen/category is retained in dimensions and is not automatically rolled up.</t>
-        </is>
-      </c>
-      <c r="AM162" t="inlineStr">
-        <is>
-          <t>raw</t>
-        </is>
-      </c>
-      <c r="AN162" t="b">
-        <v>0</v>
-      </c>
-      <c r="AO162" t="inlineStr">
-        <is>
-          <t>source_observations_only</t>
-        </is>
-      </c>
-      <c r="AP162" t="inlineStr">
-        <is>
-          <t>no_eligible_public_projection</t>
-        </is>
-      </c>
-      <c r="AQ162" t="inlineStr">
-        <is>
-          <t>source_observations_only</t>
-        </is>
-      </c>
-      <c r="AS162" t="inlineStr"/>
-      <c r="AT162" t="n">
-        <v>2</v>
-      </c>
       <c r="AU162" t="inlineStr">
         <is>
-          <t>Registered source observations are retained for provenance and downloads, but their measure is not eligible for the public cases curve.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV162" t="inlineStr">
         <is>
-          <t>rki_survstat</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW162" t="inlineStr">
         <is>
-          <t>Germany RKI SurvStat 2.0</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX162" t="inlineStr">
         <is>
-          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY162" t="inlineStr">
         <is>
-          <t>official_webforms_csv_export</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ162" t="inlineStr">
         <is>
-          <t>rki_survstat</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA162" t="inlineStr">
         <is>
-          <t>Germany RKI SurvStat 2.0</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB162" t="inlineStr">
         <is>
-          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC162" t="inlineStr">
         <is>
-          <t>official_webforms_csv_export</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -26596,12 +25498,12 @@
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>DE-SN</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Sachsen, Germany</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
@@ -26626,101 +25528,80 @@
       </c>
       <c r="L163" t="inlineStr">
         <is>
-          <t>2014-10-06</t>
+          <t>2014-11-01</t>
         </is>
       </c>
       <c r="M163" t="inlineStr">
         <is>
-          <t>2014-10</t>
+          <t>2014-11</t>
         </is>
       </c>
       <c r="N163" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O163" t="n">
-        <v>1</v>
-      </c>
-      <c r="S163" t="inlineStr">
-        <is>
-          <t>missing_population</t>
-        </is>
-      </c>
-      <c r="U163" t="inlineStr">
-        <is>
-          <t>HOLD_DE_a46d3e1400ce8c779c6fd41d7e0c</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="R163" t="n">
+        <v>0</v>
       </c>
       <c r="AA163" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO163" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP163" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ163" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS163" t="inlineStr">
-        <is>
-          <t>HOLD_DE_a46d3e1400ce8c779c6fd41d7e0c</t>
-        </is>
-      </c>
+          <t>published_series</t>
+        </is>
+      </c>
+      <c r="AS163" t="inlineStr"/>
       <c r="AT163" t="n">
-        <v>1</v>
-      </c>
-      <c r="AU163" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series.</t>
-        </is>
+        <v>0</v>
       </c>
       <c r="AV163" t="inlineStr">
         <is>
-          <t>rki_survstat</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW163" t="inlineStr">
         <is>
-          <t>Germany RKI SurvStat 2.0</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX163" t="inlineStr">
         <is>
-          <t>https://survstat.rki.de/Content/Query/Main.aspx</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY163" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ163" t="inlineStr">
         <is>
-          <t>rki_survstat</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA163" t="inlineStr">
         <is>
-          <t>Germany RKI SurvStat 2.0</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB163" t="inlineStr">
         <is>
-          <t>https://survstat.rki.de/Content/Query/Main.aspx</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC163" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -26747,17 +25628,17 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>DE-SN</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Sachsen, Germany</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
@@ -26782,48 +25663,34 @@
       </c>
       <c r="L164" t="inlineStr">
         <is>
-          <t>2014-10-06</t>
+          <t>2014-11-07</t>
         </is>
       </c>
       <c r="M164" t="inlineStr">
         <is>
-          <t>2014-10</t>
+          <t>2014-11</t>
         </is>
       </c>
       <c r="N164" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O164" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="Q164" t="n">
+        <v>0</v>
+      </c>
+      <c r="R164" t="n">
+        <v>0</v>
+      </c>
+      <c r="S164" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="U164" t="inlineStr">
         <is>
-          <t>HOLD_DE_a46d3e1400ce8c779c6fd41d7e0c</t>
-        </is>
-      </c>
-      <c r="V164" t="inlineStr">
-        <is>
-          <t>ebolafieber</t>
-        </is>
-      </c>
-      <c r="W164" t="inlineStr">
-        <is>
-          <t>SRC_DE_RKI_SURVSTAT</t>
-        </is>
-      </c>
-      <c r="X164" t="inlineStr">
-        <is>
-          <t>Ebolafieber</t>
-        </is>
-      </c>
-      <c r="Y164" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z164" t="inlineStr">
-        <is>
-          <t>notification</t>
+          <t>HOLD_JP_534554c6916adc005164f8ba7945</t>
         </is>
       </c>
       <c r="AA164" t="inlineStr">
@@ -26831,67 +25698,9 @@
           <t>unknown</t>
         </is>
       </c>
-      <c r="AB164" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC164" t="inlineStr">
-        <is>
-          <t>country:DE-SN:national</t>
-        </is>
-      </c>
-      <c r="AD164" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE164" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF164" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG164" t="inlineStr">
-        <is>
-          <t>direct_only</t>
-        </is>
-      </c>
-      <c r="AH164" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI164" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ164" t="inlineStr">
-        <is>
-          <t>source-current</t>
-        </is>
-      </c>
-      <c r="AL164" t="inlineStr">
-        <is>
-          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
-        </is>
-      </c>
-      <c r="AM164" t="inlineStr">
-        <is>
-          <t>raw</t>
-        </is>
-      </c>
-      <c r="AN164" t="b">
-        <v>1</v>
-      </c>
       <c r="AO164" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP164" t="inlineStr">
@@ -26901,12 +25710,12 @@
       </c>
       <c r="AQ164" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill</t>
         </is>
       </c>
       <c r="AS164" t="inlineStr">
         <is>
-          <t>HOLD_DE_a46d3e1400ce8c779c6fd41d7e0c</t>
+          <t>HOLD_JP_534554c6916adc005164f8ba7945</t>
         </is>
       </c>
       <c r="AT164" t="n">
@@ -26914,22 +25723,22 @@
       </c>
       <c r="AU164" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV164" t="inlineStr">
         <is>
-          <t>rki_survstat</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW164" t="inlineStr">
         <is>
-          <t>Germany RKI SurvStat 2.0</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX164" t="inlineStr">
         <is>
-          <t>https://survstat.rki.de/Content/Query/Main.aspx</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY164" t="inlineStr">
@@ -26939,17 +25748,17 @@
       </c>
       <c r="AZ164" t="inlineStr">
         <is>
-          <t>rki_survstat</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA164" t="inlineStr">
         <is>
-          <t>Germany RKI SurvStat 2.0</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB164" t="inlineStr">
         <is>
-          <t>https://survstat.rki.de/Content/Query/Main.aspx</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC164" t="inlineStr">
@@ -27016,12 +25825,12 @@
       </c>
       <c r="L165" t="inlineStr">
         <is>
-          <t>2014-10-10</t>
+          <t>2014-11-14</t>
         </is>
       </c>
       <c r="M165" t="inlineStr">
         <is>
-          <t>2014-10</t>
+          <t>2014-11</t>
         </is>
       </c>
       <c r="N165" t="n">
@@ -27178,12 +25987,12 @@
       </c>
       <c r="L166" t="inlineStr">
         <is>
-          <t>2014-10-17</t>
+          <t>2014-11-21</t>
         </is>
       </c>
       <c r="M166" t="inlineStr">
         <is>
-          <t>2014-10</t>
+          <t>2014-11</t>
         </is>
       </c>
       <c r="N166" t="n">
@@ -27340,12 +26149,12 @@
       </c>
       <c r="L167" t="inlineStr">
         <is>
-          <t>2014-10-24</t>
+          <t>2014-11-28</t>
         </is>
       </c>
       <c r="M167" t="inlineStr">
         <is>
-          <t>2014-10</t>
+          <t>2014-11</t>
         </is>
       </c>
       <c r="N167" t="n">
@@ -27472,12 +26281,12 @@
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
@@ -27502,12 +26311,12 @@
       </c>
       <c r="L168" t="inlineStr">
         <is>
-          <t>2014-10-31</t>
+          <t>2014-12-01</t>
         </is>
       </c>
       <c r="M168" t="inlineStr">
         <is>
-          <t>2014-10</t>
+          <t>2014-12</t>
         </is>
       </c>
       <c r="N168" t="n">
@@ -27516,93 +26325,66 @@
       <c r="O168" t="n">
         <v>0</v>
       </c>
-      <c r="Q168" t="n">
-        <v>0</v>
-      </c>
       <c r="R168" t="n">
         <v>0</v>
       </c>
-      <c r="S168" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="U168" t="inlineStr">
-        <is>
-          <t>HOLD_JP_534554c6916adc005164f8ba7945</t>
-        </is>
-      </c>
       <c r="AA168" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO168" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP168" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ168" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
-        </is>
-      </c>
-      <c r="AS168" t="inlineStr">
-        <is>
-          <t>HOLD_JP_534554c6916adc005164f8ba7945</t>
-        </is>
-      </c>
+          <t>published_series</t>
+        </is>
+      </c>
+      <c r="AS168" t="inlineStr"/>
       <c r="AT168" t="n">
-        <v>1</v>
-      </c>
-      <c r="AU168" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
+        <v>0</v>
       </c>
       <c r="AV168" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW168" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX168" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY168" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ168" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA168" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB168" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC168" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -27634,12 +26416,12 @@
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
@@ -27664,12 +26446,12 @@
       </c>
       <c r="L169" t="inlineStr">
         <is>
-          <t>2014-11-01</t>
+          <t>2014-12-05</t>
         </is>
       </c>
       <c r="M169" t="inlineStr">
         <is>
-          <t>2014-11</t>
+          <t>2014-12</t>
         </is>
       </c>
       <c r="N169" t="n">
@@ -27678,6 +26460,9 @@
       <c r="O169" t="n">
         <v>0</v>
       </c>
+      <c r="Q169" t="n">
+        <v>0</v>
+      </c>
       <c r="R169" t="n">
         <v>0</v>
       </c>
@@ -27686,73 +26471,82 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U169" t="inlineStr">
+        <is>
+          <t>HOLD_JP_534554c6916adc005164f8ba7945</t>
+        </is>
+      </c>
       <c r="AA169" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="AO169" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP169" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR169" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS169" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ169" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS169" t="inlineStr">
+        <is>
+          <t>HOLD_JP_534554c6916adc005164f8ba7945</t>
+        </is>
+      </c>
       <c r="AT169" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU169" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV169" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW169" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX169" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY169" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ169" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA169" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB169" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC169" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -27814,12 +26608,12 @@
       </c>
       <c r="L170" t="inlineStr">
         <is>
-          <t>2014-11-07</t>
+          <t>2014-12-12</t>
         </is>
       </c>
       <c r="M170" t="inlineStr">
         <is>
-          <t>2014-11</t>
+          <t>2014-12</t>
         </is>
       </c>
       <c r="N170" t="n">
@@ -27976,12 +26770,12 @@
       </c>
       <c r="L171" t="inlineStr">
         <is>
-          <t>2014-11-14</t>
+          <t>2014-12-19</t>
         </is>
       </c>
       <c r="M171" t="inlineStr">
         <is>
-          <t>2014-11</t>
+          <t>2014-12</t>
         </is>
       </c>
       <c r="N171" t="n">
@@ -28138,12 +26932,12 @@
       </c>
       <c r="L172" t="inlineStr">
         <is>
-          <t>2014-11-21</t>
+          <t>2014-12-26</t>
         </is>
       </c>
       <c r="M172" t="inlineStr">
         <is>
-          <t>2014-11</t>
+          <t>2014-12</t>
         </is>
       </c>
       <c r="N172" t="n">
@@ -28237,966 +27031,6 @@
         </is>
       </c>
       <c r="BC172" t="inlineStr">
-        <is>
-          <t>web</t>
-        </is>
-      </c>
-    </row>
-    <row r="173">
-      <c r="A173" t="inlineStr">
-        <is>
-          <t>disease</t>
-        </is>
-      </c>
-      <c r="B173" t="inlineStr">
-        <is>
-          <t>D050</t>
-        </is>
-      </c>
-      <c r="C173" t="inlineStr">
-        <is>
-          <t>ebola</t>
-        </is>
-      </c>
-      <c r="D173" t="inlineStr">
-        <is>
-          <t>Ebola</t>
-        </is>
-      </c>
-      <c r="E173" t="inlineStr">
-        <is>
-          <t>public_projection</t>
-        </is>
-      </c>
-      <c r="F173" t="inlineStr">
-        <is>
-          <t>JP</t>
-        </is>
-      </c>
-      <c r="G173" t="inlineStr">
-        <is>
-          <t>Japan</t>
-        </is>
-      </c>
-      <c r="H173" t="inlineStr">
-        <is>
-          <t>D050</t>
-        </is>
-      </c>
-      <c r="I173" t="inlineStr">
-        <is>
-          <t>Ebola</t>
-        </is>
-      </c>
-      <c r="J173" t="inlineStr">
-        <is>
-          <t>埃博拉出血热</t>
-        </is>
-      </c>
-      <c r="K173" t="inlineStr">
-        <is>
-          <t>Viral</t>
-        </is>
-      </c>
-      <c r="L173" t="inlineStr">
-        <is>
-          <t>2014-11-28</t>
-        </is>
-      </c>
-      <c r="M173" t="inlineStr">
-        <is>
-          <t>2014-11</t>
-        </is>
-      </c>
-      <c r="N173" t="n">
-        <v>0</v>
-      </c>
-      <c r="O173" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q173" t="n">
-        <v>0</v>
-      </c>
-      <c r="R173" t="n">
-        <v>0</v>
-      </c>
-      <c r="S173" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="U173" t="inlineStr">
-        <is>
-          <t>HOLD_JP_534554c6916adc005164f8ba7945</t>
-        </is>
-      </c>
-      <c r="AA173" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AO173" t="inlineStr">
-        <is>
-          <t>mixed</t>
-        </is>
-      </c>
-      <c r="AP173" t="inlineStr">
-        <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ173" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
-        </is>
-      </c>
-      <c r="AS173" t="inlineStr">
-        <is>
-          <t>HOLD_JP_534554c6916adc005164f8ba7945</t>
-        </is>
-      </c>
-      <c r="AT173" t="n">
-        <v>1</v>
-      </c>
-      <c r="AU173" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
-      </c>
-      <c r="AV173" t="inlineStr">
-        <is>
-          <t>jp_weekly</t>
-        </is>
-      </c>
-      <c r="AW173" t="inlineStr">
-        <is>
-          <t>JP NIID Weekly</t>
-        </is>
-      </c>
-      <c r="AX173" t="inlineStr">
-        <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
-        </is>
-      </c>
-      <c r="AY173" t="inlineStr">
-        <is>
-          <t>web</t>
-        </is>
-      </c>
-      <c r="AZ173" t="inlineStr">
-        <is>
-          <t>jp_weekly</t>
-        </is>
-      </c>
-      <c r="BA173" t="inlineStr">
-        <is>
-          <t>JP NIID Weekly</t>
-        </is>
-      </c>
-      <c r="BB173" t="inlineStr">
-        <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
-        </is>
-      </c>
-      <c r="BC173" t="inlineStr">
-        <is>
-          <t>web</t>
-        </is>
-      </c>
-    </row>
-    <row r="174">
-      <c r="A174" t="inlineStr">
-        <is>
-          <t>disease</t>
-        </is>
-      </c>
-      <c r="B174" t="inlineStr">
-        <is>
-          <t>D050</t>
-        </is>
-      </c>
-      <c r="C174" t="inlineStr">
-        <is>
-          <t>ebola</t>
-        </is>
-      </c>
-      <c r="D174" t="inlineStr">
-        <is>
-          <t>Ebola</t>
-        </is>
-      </c>
-      <c r="E174" t="inlineStr">
-        <is>
-          <t>public_projection</t>
-        </is>
-      </c>
-      <c r="F174" t="inlineStr">
-        <is>
-          <t>KR</t>
-        </is>
-      </c>
-      <c r="G174" t="inlineStr">
-        <is>
-          <t>South Korea</t>
-        </is>
-      </c>
-      <c r="H174" t="inlineStr">
-        <is>
-          <t>D050</t>
-        </is>
-      </c>
-      <c r="I174" t="inlineStr">
-        <is>
-          <t>Ebola</t>
-        </is>
-      </c>
-      <c r="J174" t="inlineStr">
-        <is>
-          <t>埃博拉出血热</t>
-        </is>
-      </c>
-      <c r="K174" t="inlineStr">
-        <is>
-          <t>Viral</t>
-        </is>
-      </c>
-      <c r="L174" t="inlineStr">
-        <is>
-          <t>2014-12-01</t>
-        </is>
-      </c>
-      <c r="M174" t="inlineStr">
-        <is>
-          <t>2014-12</t>
-        </is>
-      </c>
-      <c r="N174" t="n">
-        <v>0</v>
-      </c>
-      <c r="O174" t="n">
-        <v>0</v>
-      </c>
-      <c r="R174" t="n">
-        <v>0</v>
-      </c>
-      <c r="S174" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="AA174" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AO174" t="inlineStr">
-        <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AP174" t="inlineStr">
-        <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR174" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS174" t="inlineStr"/>
-      <c r="AT174" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU174" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
-      <c r="AV174" t="inlineStr">
-        <is>
-          <t>kdca_open_api</t>
-        </is>
-      </c>
-      <c r="AW174" t="inlineStr">
-        <is>
-          <t>Korea KDCA EID</t>
-        </is>
-      </c>
-      <c r="AX174" t="inlineStr">
-        <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
-        </is>
-      </c>
-      <c r="AY174" t="inlineStr">
-        <is>
-          <t>open_api_or_portal_download</t>
-        </is>
-      </c>
-      <c r="AZ174" t="inlineStr">
-        <is>
-          <t>kdca_open_api</t>
-        </is>
-      </c>
-      <c r="BA174" t="inlineStr">
-        <is>
-          <t>Korea KDCA EID</t>
-        </is>
-      </c>
-      <c r="BB174" t="inlineStr">
-        <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
-        </is>
-      </c>
-      <c r="BC174" t="inlineStr">
-        <is>
-          <t>open_api_or_portal_download</t>
-        </is>
-      </c>
-    </row>
-    <row r="175">
-      <c r="A175" t="inlineStr">
-        <is>
-          <t>disease</t>
-        </is>
-      </c>
-      <c r="B175" t="inlineStr">
-        <is>
-          <t>D050</t>
-        </is>
-      </c>
-      <c r="C175" t="inlineStr">
-        <is>
-          <t>ebola</t>
-        </is>
-      </c>
-      <c r="D175" t="inlineStr">
-        <is>
-          <t>Ebola</t>
-        </is>
-      </c>
-      <c r="E175" t="inlineStr">
-        <is>
-          <t>public_projection</t>
-        </is>
-      </c>
-      <c r="F175" t="inlineStr">
-        <is>
-          <t>JP</t>
-        </is>
-      </c>
-      <c r="G175" t="inlineStr">
-        <is>
-          <t>Japan</t>
-        </is>
-      </c>
-      <c r="H175" t="inlineStr">
-        <is>
-          <t>D050</t>
-        </is>
-      </c>
-      <c r="I175" t="inlineStr">
-        <is>
-          <t>Ebola</t>
-        </is>
-      </c>
-      <c r="J175" t="inlineStr">
-        <is>
-          <t>埃博拉出血热</t>
-        </is>
-      </c>
-      <c r="K175" t="inlineStr">
-        <is>
-          <t>Viral</t>
-        </is>
-      </c>
-      <c r="L175" t="inlineStr">
-        <is>
-          <t>2014-12-05</t>
-        </is>
-      </c>
-      <c r="M175" t="inlineStr">
-        <is>
-          <t>2014-12</t>
-        </is>
-      </c>
-      <c r="N175" t="n">
-        <v>0</v>
-      </c>
-      <c r="O175" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q175" t="n">
-        <v>0</v>
-      </c>
-      <c r="R175" t="n">
-        <v>0</v>
-      </c>
-      <c r="S175" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="U175" t="inlineStr">
-        <is>
-          <t>HOLD_JP_534554c6916adc005164f8ba7945</t>
-        </is>
-      </c>
-      <c r="AA175" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AO175" t="inlineStr">
-        <is>
-          <t>mixed</t>
-        </is>
-      </c>
-      <c r="AP175" t="inlineStr">
-        <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ175" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
-        </is>
-      </c>
-      <c r="AS175" t="inlineStr">
-        <is>
-          <t>HOLD_JP_534554c6916adc005164f8ba7945</t>
-        </is>
-      </c>
-      <c r="AT175" t="n">
-        <v>1</v>
-      </c>
-      <c r="AU175" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
-      </c>
-      <c r="AV175" t="inlineStr">
-        <is>
-          <t>jp_weekly</t>
-        </is>
-      </c>
-      <c r="AW175" t="inlineStr">
-        <is>
-          <t>JP NIID Weekly</t>
-        </is>
-      </c>
-      <c r="AX175" t="inlineStr">
-        <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
-        </is>
-      </c>
-      <c r="AY175" t="inlineStr">
-        <is>
-          <t>web</t>
-        </is>
-      </c>
-      <c r="AZ175" t="inlineStr">
-        <is>
-          <t>jp_weekly</t>
-        </is>
-      </c>
-      <c r="BA175" t="inlineStr">
-        <is>
-          <t>JP NIID Weekly</t>
-        </is>
-      </c>
-      <c r="BB175" t="inlineStr">
-        <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
-        </is>
-      </c>
-      <c r="BC175" t="inlineStr">
-        <is>
-          <t>web</t>
-        </is>
-      </c>
-    </row>
-    <row r="176">
-      <c r="A176" t="inlineStr">
-        <is>
-          <t>disease</t>
-        </is>
-      </c>
-      <c r="B176" t="inlineStr">
-        <is>
-          <t>D050</t>
-        </is>
-      </c>
-      <c r="C176" t="inlineStr">
-        <is>
-          <t>ebola</t>
-        </is>
-      </c>
-      <c r="D176" t="inlineStr">
-        <is>
-          <t>Ebola</t>
-        </is>
-      </c>
-      <c r="E176" t="inlineStr">
-        <is>
-          <t>public_projection</t>
-        </is>
-      </c>
-      <c r="F176" t="inlineStr">
-        <is>
-          <t>JP</t>
-        </is>
-      </c>
-      <c r="G176" t="inlineStr">
-        <is>
-          <t>Japan</t>
-        </is>
-      </c>
-      <c r="H176" t="inlineStr">
-        <is>
-          <t>D050</t>
-        </is>
-      </c>
-      <c r="I176" t="inlineStr">
-        <is>
-          <t>Ebola</t>
-        </is>
-      </c>
-      <c r="J176" t="inlineStr">
-        <is>
-          <t>埃博拉出血热</t>
-        </is>
-      </c>
-      <c r="K176" t="inlineStr">
-        <is>
-          <t>Viral</t>
-        </is>
-      </c>
-      <c r="L176" t="inlineStr">
-        <is>
-          <t>2014-12-12</t>
-        </is>
-      </c>
-      <c r="M176" t="inlineStr">
-        <is>
-          <t>2014-12</t>
-        </is>
-      </c>
-      <c r="N176" t="n">
-        <v>0</v>
-      </c>
-      <c r="O176" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q176" t="n">
-        <v>0</v>
-      </c>
-      <c r="R176" t="n">
-        <v>0</v>
-      </c>
-      <c r="S176" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="U176" t="inlineStr">
-        <is>
-          <t>HOLD_JP_534554c6916adc005164f8ba7945</t>
-        </is>
-      </c>
-      <c r="AA176" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AO176" t="inlineStr">
-        <is>
-          <t>mixed</t>
-        </is>
-      </c>
-      <c r="AP176" t="inlineStr">
-        <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ176" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
-        </is>
-      </c>
-      <c r="AS176" t="inlineStr">
-        <is>
-          <t>HOLD_JP_534554c6916adc005164f8ba7945</t>
-        </is>
-      </c>
-      <c r="AT176" t="n">
-        <v>1</v>
-      </c>
-      <c r="AU176" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
-      </c>
-      <c r="AV176" t="inlineStr">
-        <is>
-          <t>jp_weekly</t>
-        </is>
-      </c>
-      <c r="AW176" t="inlineStr">
-        <is>
-          <t>JP NIID Weekly</t>
-        </is>
-      </c>
-      <c r="AX176" t="inlineStr">
-        <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
-        </is>
-      </c>
-      <c r="AY176" t="inlineStr">
-        <is>
-          <t>web</t>
-        </is>
-      </c>
-      <c r="AZ176" t="inlineStr">
-        <is>
-          <t>jp_weekly</t>
-        </is>
-      </c>
-      <c r="BA176" t="inlineStr">
-        <is>
-          <t>JP NIID Weekly</t>
-        </is>
-      </c>
-      <c r="BB176" t="inlineStr">
-        <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
-        </is>
-      </c>
-      <c r="BC176" t="inlineStr">
-        <is>
-          <t>web</t>
-        </is>
-      </c>
-    </row>
-    <row r="177">
-      <c r="A177" t="inlineStr">
-        <is>
-          <t>disease</t>
-        </is>
-      </c>
-      <c r="B177" t="inlineStr">
-        <is>
-          <t>D050</t>
-        </is>
-      </c>
-      <c r="C177" t="inlineStr">
-        <is>
-          <t>ebola</t>
-        </is>
-      </c>
-      <c r="D177" t="inlineStr">
-        <is>
-          <t>Ebola</t>
-        </is>
-      </c>
-      <c r="E177" t="inlineStr">
-        <is>
-          <t>public_projection</t>
-        </is>
-      </c>
-      <c r="F177" t="inlineStr">
-        <is>
-          <t>JP</t>
-        </is>
-      </c>
-      <c r="G177" t="inlineStr">
-        <is>
-          <t>Japan</t>
-        </is>
-      </c>
-      <c r="H177" t="inlineStr">
-        <is>
-          <t>D050</t>
-        </is>
-      </c>
-      <c r="I177" t="inlineStr">
-        <is>
-          <t>Ebola</t>
-        </is>
-      </c>
-      <c r="J177" t="inlineStr">
-        <is>
-          <t>埃博拉出血热</t>
-        </is>
-      </c>
-      <c r="K177" t="inlineStr">
-        <is>
-          <t>Viral</t>
-        </is>
-      </c>
-      <c r="L177" t="inlineStr">
-        <is>
-          <t>2014-12-19</t>
-        </is>
-      </c>
-      <c r="M177" t="inlineStr">
-        <is>
-          <t>2014-12</t>
-        </is>
-      </c>
-      <c r="N177" t="n">
-        <v>0</v>
-      </c>
-      <c r="O177" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q177" t="n">
-        <v>0</v>
-      </c>
-      <c r="R177" t="n">
-        <v>0</v>
-      </c>
-      <c r="S177" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="U177" t="inlineStr">
-        <is>
-          <t>HOLD_JP_534554c6916adc005164f8ba7945</t>
-        </is>
-      </c>
-      <c r="AA177" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AO177" t="inlineStr">
-        <is>
-          <t>mixed</t>
-        </is>
-      </c>
-      <c r="AP177" t="inlineStr">
-        <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ177" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
-        </is>
-      </c>
-      <c r="AS177" t="inlineStr">
-        <is>
-          <t>HOLD_JP_534554c6916adc005164f8ba7945</t>
-        </is>
-      </c>
-      <c r="AT177" t="n">
-        <v>1</v>
-      </c>
-      <c r="AU177" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
-      </c>
-      <c r="AV177" t="inlineStr">
-        <is>
-          <t>jp_weekly</t>
-        </is>
-      </c>
-      <c r="AW177" t="inlineStr">
-        <is>
-          <t>JP NIID Weekly</t>
-        </is>
-      </c>
-      <c r="AX177" t="inlineStr">
-        <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
-        </is>
-      </c>
-      <c r="AY177" t="inlineStr">
-        <is>
-          <t>web</t>
-        </is>
-      </c>
-      <c r="AZ177" t="inlineStr">
-        <is>
-          <t>jp_weekly</t>
-        </is>
-      </c>
-      <c r="BA177" t="inlineStr">
-        <is>
-          <t>JP NIID Weekly</t>
-        </is>
-      </c>
-      <c r="BB177" t="inlineStr">
-        <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
-        </is>
-      </c>
-      <c r="BC177" t="inlineStr">
-        <is>
-          <t>web</t>
-        </is>
-      </c>
-    </row>
-    <row r="178">
-      <c r="A178" t="inlineStr">
-        <is>
-          <t>disease</t>
-        </is>
-      </c>
-      <c r="B178" t="inlineStr">
-        <is>
-          <t>D050</t>
-        </is>
-      </c>
-      <c r="C178" t="inlineStr">
-        <is>
-          <t>ebola</t>
-        </is>
-      </c>
-      <c r="D178" t="inlineStr">
-        <is>
-          <t>Ebola</t>
-        </is>
-      </c>
-      <c r="E178" t="inlineStr">
-        <is>
-          <t>public_projection</t>
-        </is>
-      </c>
-      <c r="F178" t="inlineStr">
-        <is>
-          <t>JP</t>
-        </is>
-      </c>
-      <c r="G178" t="inlineStr">
-        <is>
-          <t>Japan</t>
-        </is>
-      </c>
-      <c r="H178" t="inlineStr">
-        <is>
-          <t>D050</t>
-        </is>
-      </c>
-      <c r="I178" t="inlineStr">
-        <is>
-          <t>Ebola</t>
-        </is>
-      </c>
-      <c r="J178" t="inlineStr">
-        <is>
-          <t>埃博拉出血热</t>
-        </is>
-      </c>
-      <c r="K178" t="inlineStr">
-        <is>
-          <t>Viral</t>
-        </is>
-      </c>
-      <c r="L178" t="inlineStr">
-        <is>
-          <t>2014-12-26</t>
-        </is>
-      </c>
-      <c r="M178" t="inlineStr">
-        <is>
-          <t>2014-12</t>
-        </is>
-      </c>
-      <c r="N178" t="n">
-        <v>0</v>
-      </c>
-      <c r="O178" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q178" t="n">
-        <v>0</v>
-      </c>
-      <c r="R178" t="n">
-        <v>0</v>
-      </c>
-      <c r="S178" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="U178" t="inlineStr">
-        <is>
-          <t>HOLD_JP_534554c6916adc005164f8ba7945</t>
-        </is>
-      </c>
-      <c r="AA178" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AO178" t="inlineStr">
-        <is>
-          <t>mixed</t>
-        </is>
-      </c>
-      <c r="AP178" t="inlineStr">
-        <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ178" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
-        </is>
-      </c>
-      <c r="AS178" t="inlineStr">
-        <is>
-          <t>HOLD_JP_534554c6916adc005164f8ba7945</t>
-        </is>
-      </c>
-      <c r="AT178" t="n">
-        <v>1</v>
-      </c>
-      <c r="AU178" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
-      </c>
-      <c r="AV178" t="inlineStr">
-        <is>
-          <t>jp_weekly</t>
-        </is>
-      </c>
-      <c r="AW178" t="inlineStr">
-        <is>
-          <t>JP NIID Weekly</t>
-        </is>
-      </c>
-      <c r="AX178" t="inlineStr">
-        <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
-        </is>
-      </c>
-      <c r="AY178" t="inlineStr">
-        <is>
-          <t>web</t>
-        </is>
-      </c>
-      <c r="AZ178" t="inlineStr">
-        <is>
-          <t>jp_weekly</t>
-        </is>
-      </c>
-      <c r="BA178" t="inlineStr">
-        <is>
-          <t>JP NIID Weekly</t>
-        </is>
-      </c>
-      <c r="BB178" t="inlineStr">
-        <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
-        </is>
-      </c>
-      <c r="BC178" t="inlineStr">
         <is>
           <t>web</t>
         </is>
@@ -29328,7 +27162,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>177</v>
+        <v>171</v>
       </c>
     </row>
     <row r="11">
@@ -29348,7 +27182,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -29358,7 +27192,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">

--- a/diseases/d050/2010-2014.xlsx
+++ b/diseases/d050/2010-2014.xlsx
@@ -3600,17 +3600,15 @@
       <c r="O23" t="n">
         <v>0</v>
       </c>
+      <c r="P23" t="n">
+        <v>0</v>
+      </c>
       <c r="Q23" t="n">
         <v>0</v>
       </c>
       <c r="R23" t="n">
         <v>0</v>
       </c>
-      <c r="S23" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U23" t="inlineStr">
         <is>
           <t>HOLD_JP_534554c6916adc005164f8ba7945</t>
@@ -3618,7 +3616,7 @@
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
@@ -3628,12 +3626,7 @@
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ23" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr">
@@ -3643,11 +3636,6 @@
       </c>
       <c r="AT23" t="n">
         <v>1</v>
-      </c>
-      <c r="AU23" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV23" t="inlineStr">
         <is>
@@ -3762,17 +3750,15 @@
       <c r="O24" t="n">
         <v>0</v>
       </c>
+      <c r="P24" t="n">
+        <v>0</v>
+      </c>
       <c r="Q24" t="n">
         <v>0</v>
       </c>
       <c r="R24" t="n">
         <v>0</v>
       </c>
-      <c r="S24" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U24" t="inlineStr">
         <is>
           <t>HOLD_JP_534554c6916adc005164f8ba7945</t>
@@ -3780,7 +3766,7 @@
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO24" t="inlineStr">
@@ -3790,12 +3776,7 @@
       </c>
       <c r="AP24" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ24" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS24" t="inlineStr">
@@ -3805,11 +3786,6 @@
       </c>
       <c r="AT24" t="n">
         <v>1</v>
-      </c>
-      <c r="AU24" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV24" t="inlineStr">
         <is>
@@ -3924,17 +3900,15 @@
       <c r="O25" t="n">
         <v>0</v>
       </c>
+      <c r="P25" t="n">
+        <v>0</v>
+      </c>
       <c r="Q25" t="n">
         <v>0</v>
       </c>
       <c r="R25" t="n">
         <v>0</v>
       </c>
-      <c r="S25" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U25" t="inlineStr">
         <is>
           <t>HOLD_JP_534554c6916adc005164f8ba7945</t>
@@ -3942,7 +3916,7 @@
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO25" t="inlineStr">
@@ -3952,12 +3926,7 @@
       </c>
       <c r="AP25" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ25" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS25" t="inlineStr">
@@ -3967,11 +3936,6 @@
       </c>
       <c r="AT25" t="n">
         <v>1</v>
-      </c>
-      <c r="AU25" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV25" t="inlineStr">
         <is>
@@ -4221,17 +4185,15 @@
       <c r="O27" t="n">
         <v>0</v>
       </c>
+      <c r="P27" t="n">
+        <v>0</v>
+      </c>
       <c r="Q27" t="n">
         <v>0</v>
       </c>
       <c r="R27" t="n">
         <v>0</v>
       </c>
-      <c r="S27" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U27" t="inlineStr">
         <is>
           <t>HOLD_JP_534554c6916adc005164f8ba7945</t>
@@ -4239,7 +4201,7 @@
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO27" t="inlineStr">
@@ -4249,12 +4211,7 @@
       </c>
       <c r="AP27" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ27" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS27" t="inlineStr">
@@ -4264,11 +4221,6 @@
       </c>
       <c r="AT27" t="n">
         <v>1</v>
-      </c>
-      <c r="AU27" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV27" t="inlineStr">
         <is>
@@ -4383,17 +4335,15 @@
       <c r="O28" t="n">
         <v>0</v>
       </c>
+      <c r="P28" t="n">
+        <v>0</v>
+      </c>
       <c r="Q28" t="n">
         <v>0</v>
       </c>
       <c r="R28" t="n">
         <v>0</v>
       </c>
-      <c r="S28" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U28" t="inlineStr">
         <is>
           <t>HOLD_JP_534554c6916adc005164f8ba7945</t>
@@ -4401,7 +4351,7 @@
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO28" t="inlineStr">
@@ -4411,12 +4361,7 @@
       </c>
       <c r="AP28" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ28" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS28" t="inlineStr">
@@ -4426,11 +4371,6 @@
       </c>
       <c r="AT28" t="n">
         <v>1</v>
-      </c>
-      <c r="AU28" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV28" t="inlineStr">
         <is>
@@ -4545,17 +4485,15 @@
       <c r="O29" t="n">
         <v>0</v>
       </c>
+      <c r="P29" t="n">
+        <v>0</v>
+      </c>
       <c r="Q29" t="n">
         <v>0</v>
       </c>
       <c r="R29" t="n">
         <v>0</v>
       </c>
-      <c r="S29" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U29" t="inlineStr">
         <is>
           <t>HOLD_JP_534554c6916adc005164f8ba7945</t>
@@ -4563,7 +4501,7 @@
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO29" t="inlineStr">
@@ -4573,12 +4511,7 @@
       </c>
       <c r="AP29" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ29" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS29" t="inlineStr">
@@ -4588,11 +4521,6 @@
       </c>
       <c r="AT29" t="n">
         <v>1</v>
-      </c>
-      <c r="AU29" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV29" t="inlineStr">
         <is>
@@ -4707,17 +4635,15 @@
       <c r="O30" t="n">
         <v>0</v>
       </c>
+      <c r="P30" t="n">
+        <v>0</v>
+      </c>
       <c r="Q30" t="n">
         <v>0</v>
       </c>
       <c r="R30" t="n">
         <v>0</v>
       </c>
-      <c r="S30" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U30" t="inlineStr">
         <is>
           <t>HOLD_JP_534554c6916adc005164f8ba7945</t>
@@ -4725,7 +4651,7 @@
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO30" t="inlineStr">
@@ -4735,12 +4661,7 @@
       </c>
       <c r="AP30" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ30" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS30" t="inlineStr">
@@ -4750,11 +4671,6 @@
       </c>
       <c r="AT30" t="n">
         <v>1</v>
-      </c>
-      <c r="AU30" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV30" t="inlineStr">
         <is>
@@ -5004,17 +4920,15 @@
       <c r="O32" t="n">
         <v>0</v>
       </c>
+      <c r="P32" t="n">
+        <v>0</v>
+      </c>
       <c r="Q32" t="n">
         <v>0</v>
       </c>
       <c r="R32" t="n">
         <v>0</v>
       </c>
-      <c r="S32" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U32" t="inlineStr">
         <is>
           <t>HOLD_JP_534554c6916adc005164f8ba7945</t>
@@ -5022,7 +4936,7 @@
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO32" t="inlineStr">
@@ -5032,12 +4946,7 @@
       </c>
       <c r="AP32" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ32" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS32" t="inlineStr">
@@ -5047,11 +4956,6 @@
       </c>
       <c r="AT32" t="n">
         <v>1</v>
-      </c>
-      <c r="AU32" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV32" t="inlineStr">
         <is>
@@ -5166,17 +5070,15 @@
       <c r="O33" t="n">
         <v>0</v>
       </c>
+      <c r="P33" t="n">
+        <v>0</v>
+      </c>
       <c r="Q33" t="n">
         <v>0</v>
       </c>
       <c r="R33" t="n">
         <v>0</v>
       </c>
-      <c r="S33" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U33" t="inlineStr">
         <is>
           <t>HOLD_JP_534554c6916adc005164f8ba7945</t>
@@ -5184,7 +5086,7 @@
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO33" t="inlineStr">
@@ -5194,12 +5096,7 @@
       </c>
       <c r="AP33" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ33" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS33" t="inlineStr">
@@ -5209,11 +5106,6 @@
       </c>
       <c r="AT33" t="n">
         <v>1</v>
-      </c>
-      <c r="AU33" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV33" t="inlineStr">
         <is>
@@ -5328,17 +5220,15 @@
       <c r="O34" t="n">
         <v>0</v>
       </c>
+      <c r="P34" t="n">
+        <v>0</v>
+      </c>
       <c r="Q34" t="n">
         <v>0</v>
       </c>
       <c r="R34" t="n">
         <v>0</v>
       </c>
-      <c r="S34" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U34" t="inlineStr">
         <is>
           <t>HOLD_JP_534554c6916adc005164f8ba7945</t>
@@ -5346,7 +5236,7 @@
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO34" t="inlineStr">
@@ -5356,12 +5246,7 @@
       </c>
       <c r="AP34" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ34" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS34" t="inlineStr">
@@ -5371,11 +5256,6 @@
       </c>
       <c r="AT34" t="n">
         <v>1</v>
-      </c>
-      <c r="AU34" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV34" t="inlineStr">
         <is>
@@ -5490,17 +5370,15 @@
       <c r="O35" t="n">
         <v>0</v>
       </c>
+      <c r="P35" t="n">
+        <v>0</v>
+      </c>
       <c r="Q35" t="n">
         <v>0</v>
       </c>
       <c r="R35" t="n">
         <v>0</v>
       </c>
-      <c r="S35" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U35" t="inlineStr">
         <is>
           <t>HOLD_JP_534554c6916adc005164f8ba7945</t>
@@ -5508,7 +5386,7 @@
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO35" t="inlineStr">
@@ -5518,12 +5396,7 @@
       </c>
       <c r="AP35" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ35" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS35" t="inlineStr">
@@ -5533,11 +5406,6 @@
       </c>
       <c r="AT35" t="n">
         <v>1</v>
-      </c>
-      <c r="AU35" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV35" t="inlineStr">
         <is>
@@ -5652,17 +5520,15 @@
       <c r="O36" t="n">
         <v>0</v>
       </c>
+      <c r="P36" t="n">
+        <v>0</v>
+      </c>
       <c r="Q36" t="n">
         <v>0</v>
       </c>
       <c r="R36" t="n">
         <v>0</v>
       </c>
-      <c r="S36" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U36" t="inlineStr">
         <is>
           <t>HOLD_JP_534554c6916adc005164f8ba7945</t>
@@ -5670,7 +5536,7 @@
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO36" t="inlineStr">
@@ -5680,12 +5546,7 @@
       </c>
       <c r="AP36" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ36" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS36" t="inlineStr">
@@ -5695,11 +5556,6 @@
       </c>
       <c r="AT36" t="n">
         <v>1</v>
-      </c>
-      <c r="AU36" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV36" t="inlineStr">
         <is>
@@ -5949,17 +5805,15 @@
       <c r="O38" t="n">
         <v>0</v>
       </c>
+      <c r="P38" t="n">
+        <v>0</v>
+      </c>
       <c r="Q38" t="n">
         <v>0</v>
       </c>
       <c r="R38" t="n">
         <v>0</v>
       </c>
-      <c r="S38" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U38" t="inlineStr">
         <is>
           <t>HOLD_JP_534554c6916adc005164f8ba7945</t>
@@ -5967,7 +5821,7 @@
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO38" t="inlineStr">
@@ -5977,12 +5831,7 @@
       </c>
       <c r="AP38" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ38" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS38" t="inlineStr">
@@ -5992,11 +5841,6 @@
       </c>
       <c r="AT38" t="n">
         <v>1</v>
-      </c>
-      <c r="AU38" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV38" t="inlineStr">
         <is>
@@ -6111,17 +5955,15 @@
       <c r="O39" t="n">
         <v>0</v>
       </c>
+      <c r="P39" t="n">
+        <v>0</v>
+      </c>
       <c r="Q39" t="n">
         <v>0</v>
       </c>
       <c r="R39" t="n">
         <v>0</v>
       </c>
-      <c r="S39" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U39" t="inlineStr">
         <is>
           <t>HOLD_JP_534554c6916adc005164f8ba7945</t>
@@ -6129,7 +5971,7 @@
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO39" t="inlineStr">
@@ -6139,12 +5981,7 @@
       </c>
       <c r="AP39" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ39" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS39" t="inlineStr">
@@ -6154,11 +5991,6 @@
       </c>
       <c r="AT39" t="n">
         <v>1</v>
-      </c>
-      <c r="AU39" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV39" t="inlineStr">
         <is>
@@ -6273,17 +6105,15 @@
       <c r="O40" t="n">
         <v>0</v>
       </c>
+      <c r="P40" t="n">
+        <v>0</v>
+      </c>
       <c r="Q40" t="n">
         <v>0</v>
       </c>
       <c r="R40" t="n">
         <v>0</v>
       </c>
-      <c r="S40" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U40" t="inlineStr">
         <is>
           <t>HOLD_JP_534554c6916adc005164f8ba7945</t>
@@ -6291,7 +6121,7 @@
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO40" t="inlineStr">
@@ -6301,12 +6131,7 @@
       </c>
       <c r="AP40" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ40" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS40" t="inlineStr">
@@ -6316,11 +6141,6 @@
       </c>
       <c r="AT40" t="n">
         <v>1</v>
-      </c>
-      <c r="AU40" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV40" t="inlineStr">
         <is>
@@ -6435,17 +6255,15 @@
       <c r="O41" t="n">
         <v>0</v>
       </c>
+      <c r="P41" t="n">
+        <v>0</v>
+      </c>
       <c r="Q41" t="n">
         <v>0</v>
       </c>
       <c r="R41" t="n">
         <v>0</v>
       </c>
-      <c r="S41" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U41" t="inlineStr">
         <is>
           <t>HOLD_JP_534554c6916adc005164f8ba7945</t>
@@ -6453,7 +6271,7 @@
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO41" t="inlineStr">
@@ -6463,12 +6281,7 @@
       </c>
       <c r="AP41" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ41" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS41" t="inlineStr">
@@ -6478,11 +6291,6 @@
       </c>
       <c r="AT41" t="n">
         <v>1</v>
-      </c>
-      <c r="AU41" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV41" t="inlineStr">
         <is>
@@ -6732,17 +6540,15 @@
       <c r="O43" t="n">
         <v>0</v>
       </c>
+      <c r="P43" t="n">
+        <v>0</v>
+      </c>
       <c r="Q43" t="n">
         <v>0</v>
       </c>
       <c r="R43" t="n">
         <v>0</v>
       </c>
-      <c r="S43" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U43" t="inlineStr">
         <is>
           <t>HOLD_JP_534554c6916adc005164f8ba7945</t>
@@ -6750,7 +6556,7 @@
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO43" t="inlineStr">
@@ -6760,12 +6566,7 @@
       </c>
       <c r="AP43" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ43" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS43" t="inlineStr">
@@ -6775,11 +6576,6 @@
       </c>
       <c r="AT43" t="n">
         <v>1</v>
-      </c>
-      <c r="AU43" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV43" t="inlineStr">
         <is>
@@ -6894,17 +6690,15 @@
       <c r="O44" t="n">
         <v>0</v>
       </c>
+      <c r="P44" t="n">
+        <v>0</v>
+      </c>
       <c r="Q44" t="n">
         <v>0</v>
       </c>
       <c r="R44" t="n">
         <v>0</v>
       </c>
-      <c r="S44" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U44" t="inlineStr">
         <is>
           <t>HOLD_JP_534554c6916adc005164f8ba7945</t>
@@ -6912,7 +6706,7 @@
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO44" t="inlineStr">
@@ -6922,12 +6716,7 @@
       </c>
       <c r="AP44" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ44" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS44" t="inlineStr">
@@ -6937,11 +6726,6 @@
       </c>
       <c r="AT44" t="n">
         <v>1</v>
-      </c>
-      <c r="AU44" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV44" t="inlineStr">
         <is>
@@ -7056,17 +6840,15 @@
       <c r="O45" t="n">
         <v>0</v>
       </c>
+      <c r="P45" t="n">
+        <v>0</v>
+      </c>
       <c r="Q45" t="n">
         <v>0</v>
       </c>
       <c r="R45" t="n">
         <v>0</v>
       </c>
-      <c r="S45" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U45" t="inlineStr">
         <is>
           <t>HOLD_JP_534554c6916adc005164f8ba7945</t>
@@ -7074,7 +6856,7 @@
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO45" t="inlineStr">
@@ -7084,12 +6866,7 @@
       </c>
       <c r="AP45" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ45" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS45" t="inlineStr">
@@ -7099,11 +6876,6 @@
       </c>
       <c r="AT45" t="n">
         <v>1</v>
-      </c>
-      <c r="AU45" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV45" t="inlineStr">
         <is>
@@ -7218,17 +6990,15 @@
       <c r="O46" t="n">
         <v>0</v>
       </c>
+      <c r="P46" t="n">
+        <v>0</v>
+      </c>
       <c r="Q46" t="n">
         <v>0</v>
       </c>
       <c r="R46" t="n">
         <v>0</v>
       </c>
-      <c r="S46" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U46" t="inlineStr">
         <is>
           <t>HOLD_JP_534554c6916adc005164f8ba7945</t>
@@ -7236,7 +7006,7 @@
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO46" t="inlineStr">
@@ -7246,12 +7016,7 @@
       </c>
       <c r="AP46" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ46" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS46" t="inlineStr">
@@ -7261,11 +7026,6 @@
       </c>
       <c r="AT46" t="n">
         <v>1</v>
-      </c>
-      <c r="AU46" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV46" t="inlineStr">
         <is>
@@ -7380,17 +7140,15 @@
       <c r="O47" t="n">
         <v>0</v>
       </c>
+      <c r="P47" t="n">
+        <v>0</v>
+      </c>
       <c r="Q47" t="n">
         <v>0</v>
       </c>
       <c r="R47" t="n">
         <v>0</v>
       </c>
-      <c r="S47" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U47" t="inlineStr">
         <is>
           <t>HOLD_JP_534554c6916adc005164f8ba7945</t>
@@ -7398,7 +7156,7 @@
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO47" t="inlineStr">
@@ -7408,12 +7166,7 @@
       </c>
       <c r="AP47" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ47" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS47" t="inlineStr">
@@ -7423,11 +7176,6 @@
       </c>
       <c r="AT47" t="n">
         <v>1</v>
-      </c>
-      <c r="AU47" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV47" t="inlineStr">
         <is>
@@ -7677,17 +7425,15 @@
       <c r="O49" t="n">
         <v>0</v>
       </c>
+      <c r="P49" t="n">
+        <v>0</v>
+      </c>
       <c r="Q49" t="n">
         <v>0</v>
       </c>
       <c r="R49" t="n">
         <v>0</v>
       </c>
-      <c r="S49" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U49" t="inlineStr">
         <is>
           <t>HOLD_JP_534554c6916adc005164f8ba7945</t>
@@ -7695,7 +7441,7 @@
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO49" t="inlineStr">
@@ -7705,12 +7451,7 @@
       </c>
       <c r="AP49" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ49" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS49" t="inlineStr">
@@ -7720,11 +7461,6 @@
       </c>
       <c r="AT49" t="n">
         <v>1</v>
-      </c>
-      <c r="AU49" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV49" t="inlineStr">
         <is>
@@ -7839,17 +7575,15 @@
       <c r="O50" t="n">
         <v>0</v>
       </c>
+      <c r="P50" t="n">
+        <v>0</v>
+      </c>
       <c r="Q50" t="n">
         <v>0</v>
       </c>
       <c r="R50" t="n">
         <v>0</v>
       </c>
-      <c r="S50" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U50" t="inlineStr">
         <is>
           <t>HOLD_JP_534554c6916adc005164f8ba7945</t>
@@ -7857,7 +7591,7 @@
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO50" t="inlineStr">
@@ -7867,12 +7601,7 @@
       </c>
       <c r="AP50" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ50" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS50" t="inlineStr">
@@ -7882,11 +7611,6 @@
       </c>
       <c r="AT50" t="n">
         <v>1</v>
-      </c>
-      <c r="AU50" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV50" t="inlineStr">
         <is>
@@ -8001,17 +7725,15 @@
       <c r="O51" t="n">
         <v>0</v>
       </c>
+      <c r="P51" t="n">
+        <v>0</v>
+      </c>
       <c r="Q51" t="n">
         <v>0</v>
       </c>
       <c r="R51" t="n">
         <v>0</v>
       </c>
-      <c r="S51" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U51" t="inlineStr">
         <is>
           <t>HOLD_JP_534554c6916adc005164f8ba7945</t>
@@ -8019,7 +7741,7 @@
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO51" t="inlineStr">
@@ -8029,12 +7751,7 @@
       </c>
       <c r="AP51" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ51" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS51" t="inlineStr">
@@ -8044,11 +7761,6 @@
       </c>
       <c r="AT51" t="n">
         <v>1</v>
-      </c>
-      <c r="AU51" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV51" t="inlineStr">
         <is>
@@ -8163,17 +7875,15 @@
       <c r="O52" t="n">
         <v>0</v>
       </c>
+      <c r="P52" t="n">
+        <v>0</v>
+      </c>
       <c r="Q52" t="n">
         <v>0</v>
       </c>
       <c r="R52" t="n">
         <v>0</v>
       </c>
-      <c r="S52" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U52" t="inlineStr">
         <is>
           <t>HOLD_JP_534554c6916adc005164f8ba7945</t>
@@ -8181,7 +7891,7 @@
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO52" t="inlineStr">
@@ -8191,12 +7901,7 @@
       </c>
       <c r="AP52" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ52" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS52" t="inlineStr">
@@ -8206,11 +7911,6 @@
       </c>
       <c r="AT52" t="n">
         <v>1</v>
-      </c>
-      <c r="AU52" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV52" t="inlineStr">
         <is>
@@ -8460,17 +8160,15 @@
       <c r="O54" t="n">
         <v>0</v>
       </c>
+      <c r="P54" t="n">
+        <v>0</v>
+      </c>
       <c r="Q54" t="n">
         <v>0</v>
       </c>
       <c r="R54" t="n">
         <v>0</v>
       </c>
-      <c r="S54" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U54" t="inlineStr">
         <is>
           <t>HOLD_JP_534554c6916adc005164f8ba7945</t>
@@ -8478,7 +8176,7 @@
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO54" t="inlineStr">
@@ -8488,12 +8186,7 @@
       </c>
       <c r="AP54" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ54" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS54" t="inlineStr">
@@ -8503,11 +8196,6 @@
       </c>
       <c r="AT54" t="n">
         <v>1</v>
-      </c>
-      <c r="AU54" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV54" t="inlineStr">
         <is>
@@ -8622,17 +8310,15 @@
       <c r="O55" t="n">
         <v>0</v>
       </c>
+      <c r="P55" t="n">
+        <v>0</v>
+      </c>
       <c r="Q55" t="n">
         <v>0</v>
       </c>
       <c r="R55" t="n">
         <v>0</v>
       </c>
-      <c r="S55" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U55" t="inlineStr">
         <is>
           <t>HOLD_JP_534554c6916adc005164f8ba7945</t>
@@ -8640,7 +8326,7 @@
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO55" t="inlineStr">
@@ -8650,12 +8336,7 @@
       </c>
       <c r="AP55" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ55" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS55" t="inlineStr">
@@ -8665,11 +8346,6 @@
       </c>
       <c r="AT55" t="n">
         <v>1</v>
-      </c>
-      <c r="AU55" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV55" t="inlineStr">
         <is>
@@ -8784,17 +8460,15 @@
       <c r="O56" t="n">
         <v>0</v>
       </c>
+      <c r="P56" t="n">
+        <v>0</v>
+      </c>
       <c r="Q56" t="n">
         <v>0</v>
       </c>
       <c r="R56" t="n">
         <v>0</v>
       </c>
-      <c r="S56" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U56" t="inlineStr">
         <is>
           <t>HOLD_JP_534554c6916adc005164f8ba7945</t>
@@ -8802,7 +8476,7 @@
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO56" t="inlineStr">
@@ -8812,12 +8486,7 @@
       </c>
       <c r="AP56" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ56" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS56" t="inlineStr">
@@ -8827,11 +8496,6 @@
       </c>
       <c r="AT56" t="n">
         <v>1</v>
-      </c>
-      <c r="AU56" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV56" t="inlineStr">
         <is>
@@ -8946,17 +8610,15 @@
       <c r="O57" t="n">
         <v>0</v>
       </c>
+      <c r="P57" t="n">
+        <v>0</v>
+      </c>
       <c r="Q57" t="n">
         <v>0</v>
       </c>
       <c r="R57" t="n">
         <v>0</v>
       </c>
-      <c r="S57" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U57" t="inlineStr">
         <is>
           <t>HOLD_JP_534554c6916adc005164f8ba7945</t>
@@ -8964,7 +8626,7 @@
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO57" t="inlineStr">
@@ -8974,12 +8636,7 @@
       </c>
       <c r="AP57" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ57" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS57" t="inlineStr">
@@ -8989,11 +8646,6 @@
       </c>
       <c r="AT57" t="n">
         <v>1</v>
-      </c>
-      <c r="AU57" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV57" t="inlineStr">
         <is>
@@ -9243,17 +8895,15 @@
       <c r="O59" t="n">
         <v>0</v>
       </c>
+      <c r="P59" t="n">
+        <v>0</v>
+      </c>
       <c r="Q59" t="n">
         <v>0</v>
       </c>
       <c r="R59" t="n">
         <v>0</v>
       </c>
-      <c r="S59" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U59" t="inlineStr">
         <is>
           <t>HOLD_JP_534554c6916adc005164f8ba7945</t>
@@ -9261,7 +8911,7 @@
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO59" t="inlineStr">
@@ -9271,12 +8921,7 @@
       </c>
       <c r="AP59" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ59" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS59" t="inlineStr">
@@ -9286,11 +8931,6 @@
       </c>
       <c r="AT59" t="n">
         <v>1</v>
-      </c>
-      <c r="AU59" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV59" t="inlineStr">
         <is>
@@ -9405,17 +9045,15 @@
       <c r="O60" t="n">
         <v>0</v>
       </c>
+      <c r="P60" t="n">
+        <v>0</v>
+      </c>
       <c r="Q60" t="n">
         <v>0</v>
       </c>
       <c r="R60" t="n">
         <v>0</v>
       </c>
-      <c r="S60" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U60" t="inlineStr">
         <is>
           <t>HOLD_JP_534554c6916adc005164f8ba7945</t>
@@ -9423,7 +9061,7 @@
       </c>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO60" t="inlineStr">
@@ -9433,12 +9071,7 @@
       </c>
       <c r="AP60" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ60" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS60" t="inlineStr">
@@ -9448,11 +9081,6 @@
       </c>
       <c r="AT60" t="n">
         <v>1</v>
-      </c>
-      <c r="AU60" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV60" t="inlineStr">
         <is>
@@ -9567,17 +9195,15 @@
       <c r="O61" t="n">
         <v>0</v>
       </c>
+      <c r="P61" t="n">
+        <v>0</v>
+      </c>
       <c r="Q61" t="n">
         <v>0</v>
       </c>
       <c r="R61" t="n">
         <v>0</v>
       </c>
-      <c r="S61" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U61" t="inlineStr">
         <is>
           <t>HOLD_JP_534554c6916adc005164f8ba7945</t>
@@ -9585,7 +9211,7 @@
       </c>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO61" t="inlineStr">
@@ -9595,12 +9221,7 @@
       </c>
       <c r="AP61" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ61" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS61" t="inlineStr">
@@ -9610,11 +9231,6 @@
       </c>
       <c r="AT61" t="n">
         <v>1</v>
-      </c>
-      <c r="AU61" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV61" t="inlineStr">
         <is>
@@ -9729,17 +9345,15 @@
       <c r="O62" t="n">
         <v>0</v>
       </c>
+      <c r="P62" t="n">
+        <v>0</v>
+      </c>
       <c r="Q62" t="n">
         <v>0</v>
       </c>
       <c r="R62" t="n">
         <v>0</v>
       </c>
-      <c r="S62" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U62" t="inlineStr">
         <is>
           <t>HOLD_JP_534554c6916adc005164f8ba7945</t>
@@ -9747,7 +9361,7 @@
       </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO62" t="inlineStr">
@@ -9757,12 +9371,7 @@
       </c>
       <c r="AP62" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ62" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS62" t="inlineStr">
@@ -9772,11 +9381,6 @@
       </c>
       <c r="AT62" t="n">
         <v>1</v>
-      </c>
-      <c r="AU62" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV62" t="inlineStr">
         <is>
@@ -10026,17 +9630,15 @@
       <c r="O64" t="n">
         <v>0</v>
       </c>
+      <c r="P64" t="n">
+        <v>0</v>
+      </c>
       <c r="Q64" t="n">
         <v>0</v>
       </c>
       <c r="R64" t="n">
         <v>0</v>
       </c>
-      <c r="S64" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U64" t="inlineStr">
         <is>
           <t>HOLD_JP_534554c6916adc005164f8ba7945</t>
@@ -10044,7 +9646,7 @@
       </c>
       <c r="AA64" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO64" t="inlineStr">
@@ -10054,12 +9656,7 @@
       </c>
       <c r="AP64" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ64" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS64" t="inlineStr">
@@ -10069,11 +9666,6 @@
       </c>
       <c r="AT64" t="n">
         <v>1</v>
-      </c>
-      <c r="AU64" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV64" t="inlineStr">
         <is>
@@ -10188,17 +9780,15 @@
       <c r="O65" t="n">
         <v>0</v>
       </c>
+      <c r="P65" t="n">
+        <v>0</v>
+      </c>
       <c r="Q65" t="n">
         <v>0</v>
       </c>
       <c r="R65" t="n">
         <v>0</v>
       </c>
-      <c r="S65" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U65" t="inlineStr">
         <is>
           <t>HOLD_JP_534554c6916adc005164f8ba7945</t>
@@ -10206,7 +9796,7 @@
       </c>
       <c r="AA65" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO65" t="inlineStr">
@@ -10216,12 +9806,7 @@
       </c>
       <c r="AP65" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ65" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS65" t="inlineStr">
@@ -10231,11 +9816,6 @@
       </c>
       <c r="AT65" t="n">
         <v>1</v>
-      </c>
-      <c r="AU65" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV65" t="inlineStr">
         <is>
@@ -10350,17 +9930,15 @@
       <c r="O66" t="n">
         <v>0</v>
       </c>
+      <c r="P66" t="n">
+        <v>0</v>
+      </c>
       <c r="Q66" t="n">
         <v>0</v>
       </c>
       <c r="R66" t="n">
         <v>0</v>
       </c>
-      <c r="S66" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U66" t="inlineStr">
         <is>
           <t>HOLD_JP_534554c6916adc005164f8ba7945</t>
@@ -10368,7 +9946,7 @@
       </c>
       <c r="AA66" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO66" t="inlineStr">
@@ -10378,12 +9956,7 @@
       </c>
       <c r="AP66" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ66" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS66" t="inlineStr">
@@ -10393,11 +9966,6 @@
       </c>
       <c r="AT66" t="n">
         <v>1</v>
-      </c>
-      <c r="AU66" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV66" t="inlineStr">
         <is>
@@ -10512,17 +10080,15 @@
       <c r="O67" t="n">
         <v>0</v>
       </c>
+      <c r="P67" t="n">
+        <v>0</v>
+      </c>
       <c r="Q67" t="n">
         <v>0</v>
       </c>
       <c r="R67" t="n">
         <v>0</v>
       </c>
-      <c r="S67" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U67" t="inlineStr">
         <is>
           <t>HOLD_JP_534554c6916adc005164f8ba7945</t>
@@ -10530,7 +10096,7 @@
       </c>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO67" t="inlineStr">
@@ -10540,12 +10106,7 @@
       </c>
       <c r="AP67" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ67" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS67" t="inlineStr">
@@ -10555,11 +10116,6 @@
       </c>
       <c r="AT67" t="n">
         <v>1</v>
-      </c>
-      <c r="AU67" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV67" t="inlineStr">
         <is>
@@ -10674,17 +10230,15 @@
       <c r="O68" t="n">
         <v>0</v>
       </c>
+      <c r="P68" t="n">
+        <v>0</v>
+      </c>
       <c r="Q68" t="n">
         <v>0</v>
       </c>
       <c r="R68" t="n">
         <v>0</v>
       </c>
-      <c r="S68" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U68" t="inlineStr">
         <is>
           <t>HOLD_JP_534554c6916adc005164f8ba7945</t>
@@ -10692,7 +10246,7 @@
       </c>
       <c r="AA68" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO68" t="inlineStr">
@@ -10702,12 +10256,7 @@
       </c>
       <c r="AP68" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ68" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS68" t="inlineStr">
@@ -10717,11 +10266,6 @@
       </c>
       <c r="AT68" t="n">
         <v>1</v>
-      </c>
-      <c r="AU68" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV68" t="inlineStr">
         <is>
@@ -10971,17 +10515,15 @@
       <c r="O70" t="n">
         <v>0</v>
       </c>
+      <c r="P70" t="n">
+        <v>0</v>
+      </c>
       <c r="Q70" t="n">
         <v>0</v>
       </c>
       <c r="R70" t="n">
         <v>0</v>
       </c>
-      <c r="S70" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U70" t="inlineStr">
         <is>
           <t>HOLD_JP_534554c6916adc005164f8ba7945</t>
@@ -10989,7 +10531,7 @@
       </c>
       <c r="AA70" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO70" t="inlineStr">
@@ -10999,12 +10541,7 @@
       </c>
       <c r="AP70" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ70" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS70" t="inlineStr">
@@ -11014,11 +10551,6 @@
       </c>
       <c r="AT70" t="n">
         <v>1</v>
-      </c>
-      <c r="AU70" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV70" t="inlineStr">
         <is>
@@ -11133,17 +10665,15 @@
       <c r="O71" t="n">
         <v>0</v>
       </c>
+      <c r="P71" t="n">
+        <v>0</v>
+      </c>
       <c r="Q71" t="n">
         <v>0</v>
       </c>
       <c r="R71" t="n">
         <v>0</v>
       </c>
-      <c r="S71" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U71" t="inlineStr">
         <is>
           <t>HOLD_JP_534554c6916adc005164f8ba7945</t>
@@ -11151,7 +10681,7 @@
       </c>
       <c r="AA71" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO71" t="inlineStr">
@@ -11161,12 +10691,7 @@
       </c>
       <c r="AP71" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ71" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS71" t="inlineStr">
@@ -11176,11 +10701,6 @@
       </c>
       <c r="AT71" t="n">
         <v>1</v>
-      </c>
-      <c r="AU71" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV71" t="inlineStr">
         <is>
@@ -11295,17 +10815,15 @@
       <c r="O72" t="n">
         <v>0</v>
       </c>
+      <c r="P72" t="n">
+        <v>0</v>
+      </c>
       <c r="Q72" t="n">
         <v>0</v>
       </c>
       <c r="R72" t="n">
         <v>0</v>
       </c>
-      <c r="S72" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U72" t="inlineStr">
         <is>
           <t>HOLD_JP_534554c6916adc005164f8ba7945</t>
@@ -11313,7 +10831,7 @@
       </c>
       <c r="AA72" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO72" t="inlineStr">
@@ -11323,12 +10841,7 @@
       </c>
       <c r="AP72" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ72" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS72" t="inlineStr">
@@ -11338,11 +10851,6 @@
       </c>
       <c r="AT72" t="n">
         <v>1</v>
-      </c>
-      <c r="AU72" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV72" t="inlineStr">
         <is>
@@ -11457,17 +10965,15 @@
       <c r="O73" t="n">
         <v>0</v>
       </c>
+      <c r="P73" t="n">
+        <v>0</v>
+      </c>
       <c r="Q73" t="n">
         <v>0</v>
       </c>
       <c r="R73" t="n">
         <v>0</v>
       </c>
-      <c r="S73" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U73" t="inlineStr">
         <is>
           <t>HOLD_JP_534554c6916adc005164f8ba7945</t>
@@ -11475,7 +10981,7 @@
       </c>
       <c r="AA73" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO73" t="inlineStr">
@@ -11485,12 +10991,7 @@
       </c>
       <c r="AP73" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ73" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS73" t="inlineStr">
@@ -11500,11 +11001,6 @@
       </c>
       <c r="AT73" t="n">
         <v>1</v>
-      </c>
-      <c r="AU73" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV73" t="inlineStr">
         <is>
@@ -11754,17 +11250,15 @@
       <c r="O75" t="n">
         <v>0</v>
       </c>
+      <c r="P75" t="n">
+        <v>0</v>
+      </c>
       <c r="Q75" t="n">
         <v>0</v>
       </c>
       <c r="R75" t="n">
         <v>0</v>
       </c>
-      <c r="S75" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U75" t="inlineStr">
         <is>
           <t>HOLD_JP_534554c6916adc005164f8ba7945</t>
@@ -11772,7 +11266,7 @@
       </c>
       <c r="AA75" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO75" t="inlineStr">
@@ -11782,12 +11276,7 @@
       </c>
       <c r="AP75" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ75" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS75" t="inlineStr">
@@ -11797,11 +11286,6 @@
       </c>
       <c r="AT75" t="n">
         <v>1</v>
-      </c>
-      <c r="AU75" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV75" t="inlineStr">
         <is>
@@ -11916,17 +11400,15 @@
       <c r="O76" t="n">
         <v>0</v>
       </c>
+      <c r="P76" t="n">
+        <v>0</v>
+      </c>
       <c r="Q76" t="n">
         <v>0</v>
       </c>
       <c r="R76" t="n">
         <v>0</v>
       </c>
-      <c r="S76" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U76" t="inlineStr">
         <is>
           <t>HOLD_JP_534554c6916adc005164f8ba7945</t>
@@ -11934,7 +11416,7 @@
       </c>
       <c r="AA76" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO76" t="inlineStr">
@@ -11944,12 +11426,7 @@
       </c>
       <c r="AP76" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ76" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS76" t="inlineStr">
@@ -11959,11 +11436,6 @@
       </c>
       <c r="AT76" t="n">
         <v>1</v>
-      </c>
-      <c r="AU76" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV76" t="inlineStr">
         <is>
@@ -12078,17 +11550,15 @@
       <c r="O77" t="n">
         <v>0</v>
       </c>
+      <c r="P77" t="n">
+        <v>0</v>
+      </c>
       <c r="Q77" t="n">
         <v>0</v>
       </c>
       <c r="R77" t="n">
         <v>0</v>
       </c>
-      <c r="S77" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U77" t="inlineStr">
         <is>
           <t>HOLD_JP_534554c6916adc005164f8ba7945</t>
@@ -12096,7 +11566,7 @@
       </c>
       <c r="AA77" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO77" t="inlineStr">
@@ -12106,12 +11576,7 @@
       </c>
       <c r="AP77" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ77" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS77" t="inlineStr">
@@ -12121,11 +11586,6 @@
       </c>
       <c r="AT77" t="n">
         <v>1</v>
-      </c>
-      <c r="AU77" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV77" t="inlineStr">
         <is>
@@ -12240,17 +11700,15 @@
       <c r="O78" t="n">
         <v>0</v>
       </c>
+      <c r="P78" t="n">
+        <v>0</v>
+      </c>
       <c r="Q78" t="n">
         <v>0</v>
       </c>
       <c r="R78" t="n">
         <v>0</v>
       </c>
-      <c r="S78" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U78" t="inlineStr">
         <is>
           <t>HOLD_JP_534554c6916adc005164f8ba7945</t>
@@ -12258,7 +11716,7 @@
       </c>
       <c r="AA78" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO78" t="inlineStr">
@@ -12268,12 +11726,7 @@
       </c>
       <c r="AP78" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ78" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS78" t="inlineStr">
@@ -12283,11 +11736,6 @@
       </c>
       <c r="AT78" t="n">
         <v>1</v>
-      </c>
-      <c r="AU78" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV78" t="inlineStr">
         <is>
@@ -12537,17 +11985,15 @@
       <c r="O80" t="n">
         <v>0</v>
       </c>
+      <c r="P80" t="n">
+        <v>0</v>
+      </c>
       <c r="Q80" t="n">
         <v>0</v>
       </c>
       <c r="R80" t="n">
         <v>0</v>
       </c>
-      <c r="S80" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U80" t="inlineStr">
         <is>
           <t>HOLD_JP_534554c6916adc005164f8ba7945</t>
@@ -12555,7 +12001,7 @@
       </c>
       <c r="AA80" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO80" t="inlineStr">
@@ -12565,12 +12011,7 @@
       </c>
       <c r="AP80" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ80" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS80" t="inlineStr">
@@ -12580,11 +12021,6 @@
       </c>
       <c r="AT80" t="n">
         <v>1</v>
-      </c>
-      <c r="AU80" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV80" t="inlineStr">
         <is>
@@ -12699,17 +12135,15 @@
       <c r="O81" t="n">
         <v>0</v>
       </c>
+      <c r="P81" t="n">
+        <v>0</v>
+      </c>
       <c r="Q81" t="n">
         <v>0</v>
       </c>
       <c r="R81" t="n">
         <v>0</v>
       </c>
-      <c r="S81" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U81" t="inlineStr">
         <is>
           <t>HOLD_JP_534554c6916adc005164f8ba7945</t>
@@ -12717,7 +12151,7 @@
       </c>
       <c r="AA81" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO81" t="inlineStr">
@@ -12727,12 +12161,7 @@
       </c>
       <c r="AP81" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ81" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS81" t="inlineStr">
@@ -12742,11 +12171,6 @@
       </c>
       <c r="AT81" t="n">
         <v>1</v>
-      </c>
-      <c r="AU81" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV81" t="inlineStr">
         <is>
@@ -12861,17 +12285,15 @@
       <c r="O82" t="n">
         <v>0</v>
       </c>
+      <c r="P82" t="n">
+        <v>0</v>
+      </c>
       <c r="Q82" t="n">
         <v>0</v>
       </c>
       <c r="R82" t="n">
         <v>0</v>
       </c>
-      <c r="S82" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U82" t="inlineStr">
         <is>
           <t>HOLD_JP_534554c6916adc005164f8ba7945</t>
@@ -12879,7 +12301,7 @@
       </c>
       <c r="AA82" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO82" t="inlineStr">
@@ -12889,12 +12311,7 @@
       </c>
       <c r="AP82" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ82" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS82" t="inlineStr">
@@ -12904,11 +12321,6 @@
       </c>
       <c r="AT82" t="n">
         <v>1</v>
-      </c>
-      <c r="AU82" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV82" t="inlineStr">
         <is>
@@ -13023,17 +12435,15 @@
       <c r="O83" t="n">
         <v>0</v>
       </c>
+      <c r="P83" t="n">
+        <v>0</v>
+      </c>
       <c r="Q83" t="n">
         <v>0</v>
       </c>
       <c r="R83" t="n">
         <v>0</v>
       </c>
-      <c r="S83" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U83" t="inlineStr">
         <is>
           <t>HOLD_JP_534554c6916adc005164f8ba7945</t>
@@ -13041,7 +12451,7 @@
       </c>
       <c r="AA83" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO83" t="inlineStr">
@@ -13051,12 +12461,7 @@
       </c>
       <c r="AP83" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ83" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS83" t="inlineStr">
@@ -13066,11 +12471,6 @@
       </c>
       <c r="AT83" t="n">
         <v>1</v>
-      </c>
-      <c r="AU83" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV83" t="inlineStr">
         <is>
@@ -13185,17 +12585,15 @@
       <c r="O84" t="n">
         <v>0</v>
       </c>
+      <c r="P84" t="n">
+        <v>0</v>
+      </c>
       <c r="Q84" t="n">
         <v>0</v>
       </c>
       <c r="R84" t="n">
         <v>0</v>
       </c>
-      <c r="S84" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U84" t="inlineStr">
         <is>
           <t>HOLD_JP_534554c6916adc005164f8ba7945</t>
@@ -13203,7 +12601,7 @@
       </c>
       <c r="AA84" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO84" t="inlineStr">
@@ -13213,12 +12611,7 @@
       </c>
       <c r="AP84" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ84" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS84" t="inlineStr">
@@ -13228,11 +12621,6 @@
       </c>
       <c r="AT84" t="n">
         <v>1</v>
-      </c>
-      <c r="AU84" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV84" t="inlineStr">
         <is>
@@ -13482,17 +12870,15 @@
       <c r="O86" t="n">
         <v>0</v>
       </c>
+      <c r="P86" t="n">
+        <v>0</v>
+      </c>
       <c r="Q86" t="n">
         <v>0</v>
       </c>
       <c r="R86" t="n">
         <v>0</v>
       </c>
-      <c r="S86" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U86" t="inlineStr">
         <is>
           <t>HOLD_JP_534554c6916adc005164f8ba7945</t>
@@ -13500,7 +12886,7 @@
       </c>
       <c r="AA86" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO86" t="inlineStr">
@@ -13510,12 +12896,7 @@
       </c>
       <c r="AP86" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ86" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS86" t="inlineStr">
@@ -13525,11 +12906,6 @@
       </c>
       <c r="AT86" t="n">
         <v>1</v>
-      </c>
-      <c r="AU86" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV86" t="inlineStr">
         <is>
@@ -13644,17 +13020,15 @@
       <c r="O87" t="n">
         <v>0</v>
       </c>
+      <c r="P87" t="n">
+        <v>0</v>
+      </c>
       <c r="Q87" t="n">
         <v>0</v>
       </c>
       <c r="R87" t="n">
         <v>0</v>
       </c>
-      <c r="S87" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U87" t="inlineStr">
         <is>
           <t>HOLD_JP_534554c6916adc005164f8ba7945</t>
@@ -13662,7 +13036,7 @@
       </c>
       <c r="AA87" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO87" t="inlineStr">
@@ -13672,12 +13046,7 @@
       </c>
       <c r="AP87" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ87" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS87" t="inlineStr">
@@ -13687,11 +13056,6 @@
       </c>
       <c r="AT87" t="n">
         <v>1</v>
-      </c>
-      <c r="AU87" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV87" t="inlineStr">
         <is>
@@ -13806,17 +13170,15 @@
       <c r="O88" t="n">
         <v>0</v>
       </c>
+      <c r="P88" t="n">
+        <v>0</v>
+      </c>
       <c r="Q88" t="n">
         <v>0</v>
       </c>
       <c r="R88" t="n">
         <v>0</v>
       </c>
-      <c r="S88" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U88" t="inlineStr">
         <is>
           <t>HOLD_JP_534554c6916adc005164f8ba7945</t>
@@ -13824,7 +13186,7 @@
       </c>
       <c r="AA88" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO88" t="inlineStr">
@@ -13834,12 +13196,7 @@
       </c>
       <c r="AP88" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ88" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS88" t="inlineStr">
@@ -13849,11 +13206,6 @@
       </c>
       <c r="AT88" t="n">
         <v>1</v>
-      </c>
-      <c r="AU88" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV88" t="inlineStr">
         <is>
@@ -13968,17 +13320,15 @@
       <c r="O89" t="n">
         <v>0</v>
       </c>
+      <c r="P89" t="n">
+        <v>0</v>
+      </c>
       <c r="Q89" t="n">
         <v>0</v>
       </c>
       <c r="R89" t="n">
         <v>0</v>
       </c>
-      <c r="S89" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U89" t="inlineStr">
         <is>
           <t>HOLD_JP_534554c6916adc005164f8ba7945</t>
@@ -13986,7 +13336,7 @@
       </c>
       <c r="AA89" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO89" t="inlineStr">
@@ -13996,12 +13346,7 @@
       </c>
       <c r="AP89" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ89" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS89" t="inlineStr">
@@ -14011,11 +13356,6 @@
       </c>
       <c r="AT89" t="n">
         <v>1</v>
-      </c>
-      <c r="AU89" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV89" t="inlineStr">
         <is>
@@ -14265,17 +13605,15 @@
       <c r="O91" t="n">
         <v>0</v>
       </c>
+      <c r="P91" t="n">
+        <v>0</v>
+      </c>
       <c r="Q91" t="n">
         <v>0</v>
       </c>
       <c r="R91" t="n">
         <v>0</v>
       </c>
-      <c r="S91" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U91" t="inlineStr">
         <is>
           <t>HOLD_JP_534554c6916adc005164f8ba7945</t>
@@ -14283,7 +13621,7 @@
       </c>
       <c r="AA91" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO91" t="inlineStr">
@@ -14293,12 +13631,7 @@
       </c>
       <c r="AP91" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ91" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS91" t="inlineStr">
@@ -14308,11 +13641,6 @@
       </c>
       <c r="AT91" t="n">
         <v>1</v>
-      </c>
-      <c r="AU91" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV91" t="inlineStr">
         <is>
@@ -14427,17 +13755,15 @@
       <c r="O92" t="n">
         <v>0</v>
       </c>
+      <c r="P92" t="n">
+        <v>0</v>
+      </c>
       <c r="Q92" t="n">
         <v>0</v>
       </c>
       <c r="R92" t="n">
         <v>0</v>
       </c>
-      <c r="S92" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U92" t="inlineStr">
         <is>
           <t>HOLD_JP_534554c6916adc005164f8ba7945</t>
@@ -14445,7 +13771,7 @@
       </c>
       <c r="AA92" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO92" t="inlineStr">
@@ -14455,12 +13781,7 @@
       </c>
       <c r="AP92" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ92" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS92" t="inlineStr">
@@ -14470,11 +13791,6 @@
       </c>
       <c r="AT92" t="n">
         <v>1</v>
-      </c>
-      <c r="AU92" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV92" t="inlineStr">
         <is>
@@ -14589,17 +13905,15 @@
       <c r="O93" t="n">
         <v>0</v>
       </c>
+      <c r="P93" t="n">
+        <v>0</v>
+      </c>
       <c r="Q93" t="n">
         <v>0</v>
       </c>
       <c r="R93" t="n">
         <v>0</v>
       </c>
-      <c r="S93" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U93" t="inlineStr">
         <is>
           <t>HOLD_JP_534554c6916adc005164f8ba7945</t>
@@ -14607,7 +13921,7 @@
       </c>
       <c r="AA93" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO93" t="inlineStr">
@@ -14617,12 +13931,7 @@
       </c>
       <c r="AP93" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ93" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS93" t="inlineStr">
@@ -14632,11 +13941,6 @@
       </c>
       <c r="AT93" t="n">
         <v>1</v>
-      </c>
-      <c r="AU93" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV93" t="inlineStr">
         <is>
@@ -14751,17 +14055,15 @@
       <c r="O94" t="n">
         <v>0</v>
       </c>
+      <c r="P94" t="n">
+        <v>0</v>
+      </c>
       <c r="Q94" t="n">
         <v>0</v>
       </c>
       <c r="R94" t="n">
         <v>0</v>
       </c>
-      <c r="S94" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U94" t="inlineStr">
         <is>
           <t>HOLD_JP_534554c6916adc005164f8ba7945</t>
@@ -14769,7 +14071,7 @@
       </c>
       <c r="AA94" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO94" t="inlineStr">
@@ -14779,12 +14081,7 @@
       </c>
       <c r="AP94" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ94" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS94" t="inlineStr">
@@ -14794,11 +14091,6 @@
       </c>
       <c r="AT94" t="n">
         <v>1</v>
-      </c>
-      <c r="AU94" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV94" t="inlineStr">
         <is>
@@ -14913,17 +14205,15 @@
       <c r="O95" t="n">
         <v>0</v>
       </c>
+      <c r="P95" t="n">
+        <v>0</v>
+      </c>
       <c r="Q95" t="n">
         <v>0</v>
       </c>
       <c r="R95" t="n">
         <v>0</v>
       </c>
-      <c r="S95" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U95" t="inlineStr">
         <is>
           <t>HOLD_JP_534554c6916adc005164f8ba7945</t>
@@ -14931,7 +14221,7 @@
       </c>
       <c r="AA95" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO95" t="inlineStr">
@@ -14941,12 +14231,7 @@
       </c>
       <c r="AP95" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ95" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS95" t="inlineStr">
@@ -14956,11 +14241,6 @@
       </c>
       <c r="AT95" t="n">
         <v>1</v>
-      </c>
-      <c r="AU95" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV95" t="inlineStr">
         <is>
@@ -15210,17 +14490,15 @@
       <c r="O97" t="n">
         <v>0</v>
       </c>
+      <c r="P97" t="n">
+        <v>0</v>
+      </c>
       <c r="Q97" t="n">
         <v>0</v>
       </c>
       <c r="R97" t="n">
         <v>0</v>
       </c>
-      <c r="S97" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U97" t="inlineStr">
         <is>
           <t>HOLD_JP_534554c6916adc005164f8ba7945</t>
@@ -15228,7 +14506,7 @@
       </c>
       <c r="AA97" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO97" t="inlineStr">
@@ -15238,12 +14516,7 @@
       </c>
       <c r="AP97" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ97" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS97" t="inlineStr">
@@ -15253,11 +14526,6 @@
       </c>
       <c r="AT97" t="n">
         <v>1</v>
-      </c>
-      <c r="AU97" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV97" t="inlineStr">
         <is>
@@ -15372,17 +14640,15 @@
       <c r="O98" t="n">
         <v>0</v>
       </c>
+      <c r="P98" t="n">
+        <v>0</v>
+      </c>
       <c r="Q98" t="n">
         <v>0</v>
       </c>
       <c r="R98" t="n">
         <v>0</v>
       </c>
-      <c r="S98" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U98" t="inlineStr">
         <is>
           <t>HOLD_JP_534554c6916adc005164f8ba7945</t>
@@ -15390,7 +14656,7 @@
       </c>
       <c r="AA98" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO98" t="inlineStr">
@@ -15400,12 +14666,7 @@
       </c>
       <c r="AP98" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ98" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS98" t="inlineStr">
@@ -15415,11 +14676,6 @@
       </c>
       <c r="AT98" t="n">
         <v>1</v>
-      </c>
-      <c r="AU98" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV98" t="inlineStr">
         <is>
@@ -15534,17 +14790,15 @@
       <c r="O99" t="n">
         <v>0</v>
       </c>
+      <c r="P99" t="n">
+        <v>0</v>
+      </c>
       <c r="Q99" t="n">
         <v>0</v>
       </c>
       <c r="R99" t="n">
         <v>0</v>
       </c>
-      <c r="S99" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U99" t="inlineStr">
         <is>
           <t>HOLD_JP_534554c6916adc005164f8ba7945</t>
@@ -15552,7 +14806,7 @@
       </c>
       <c r="AA99" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO99" t="inlineStr">
@@ -15562,12 +14816,7 @@
       </c>
       <c r="AP99" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ99" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS99" t="inlineStr">
@@ -15577,11 +14826,6 @@
       </c>
       <c r="AT99" t="n">
         <v>1</v>
-      </c>
-      <c r="AU99" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV99" t="inlineStr">
         <is>
@@ -15696,17 +14940,15 @@
       <c r="O100" t="n">
         <v>0</v>
       </c>
+      <c r="P100" t="n">
+        <v>0</v>
+      </c>
       <c r="Q100" t="n">
         <v>0</v>
       </c>
       <c r="R100" t="n">
         <v>0</v>
       </c>
-      <c r="S100" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U100" t="inlineStr">
         <is>
           <t>HOLD_JP_534554c6916adc005164f8ba7945</t>
@@ -15714,7 +14956,7 @@
       </c>
       <c r="AA100" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO100" t="inlineStr">
@@ -15724,12 +14966,7 @@
       </c>
       <c r="AP100" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ100" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS100" t="inlineStr">
@@ -15739,11 +14976,6 @@
       </c>
       <c r="AT100" t="n">
         <v>1</v>
-      </c>
-      <c r="AU100" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV100" t="inlineStr">
         <is>
@@ -15993,17 +15225,15 @@
       <c r="O102" t="n">
         <v>0</v>
       </c>
+      <c r="P102" t="n">
+        <v>0</v>
+      </c>
       <c r="Q102" t="n">
         <v>0</v>
       </c>
       <c r="R102" t="n">
         <v>0</v>
       </c>
-      <c r="S102" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U102" t="inlineStr">
         <is>
           <t>HOLD_JP_534554c6916adc005164f8ba7945</t>
@@ -16011,7 +15241,7 @@
       </c>
       <c r="AA102" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO102" t="inlineStr">
@@ -16021,12 +15251,7 @@
       </c>
       <c r="AP102" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ102" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS102" t="inlineStr">
@@ -16036,11 +15261,6 @@
       </c>
       <c r="AT102" t="n">
         <v>1</v>
-      </c>
-      <c r="AU102" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV102" t="inlineStr">
         <is>
@@ -16155,17 +15375,15 @@
       <c r="O103" t="n">
         <v>0</v>
       </c>
+      <c r="P103" t="n">
+        <v>0</v>
+      </c>
       <c r="Q103" t="n">
         <v>0</v>
       </c>
       <c r="R103" t="n">
         <v>0</v>
       </c>
-      <c r="S103" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U103" t="inlineStr">
         <is>
           <t>HOLD_JP_534554c6916adc005164f8ba7945</t>
@@ -16173,7 +15391,7 @@
       </c>
       <c r="AA103" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO103" t="inlineStr">
@@ -16183,12 +15401,7 @@
       </c>
       <c r="AP103" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ103" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS103" t="inlineStr">
@@ -16198,11 +15411,6 @@
       </c>
       <c r="AT103" t="n">
         <v>1</v>
-      </c>
-      <c r="AU103" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV103" t="inlineStr">
         <is>
@@ -16317,17 +15525,15 @@
       <c r="O104" t="n">
         <v>0</v>
       </c>
+      <c r="P104" t="n">
+        <v>0</v>
+      </c>
       <c r="Q104" t="n">
         <v>0</v>
       </c>
       <c r="R104" t="n">
         <v>0</v>
       </c>
-      <c r="S104" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U104" t="inlineStr">
         <is>
           <t>HOLD_JP_534554c6916adc005164f8ba7945</t>
@@ -16335,7 +15541,7 @@
       </c>
       <c r="AA104" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO104" t="inlineStr">
@@ -16345,12 +15551,7 @@
       </c>
       <c r="AP104" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ104" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS104" t="inlineStr">
@@ -16360,11 +15561,6 @@
       </c>
       <c r="AT104" t="n">
         <v>1</v>
-      </c>
-      <c r="AU104" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV104" t="inlineStr">
         <is>
@@ -16479,17 +15675,15 @@
       <c r="O105" t="n">
         <v>0</v>
       </c>
+      <c r="P105" t="n">
+        <v>0</v>
+      </c>
       <c r="Q105" t="n">
         <v>0</v>
       </c>
       <c r="R105" t="n">
         <v>0</v>
       </c>
-      <c r="S105" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U105" t="inlineStr">
         <is>
           <t>HOLD_JP_534554c6916adc005164f8ba7945</t>
@@ -16497,7 +15691,7 @@
       </c>
       <c r="AA105" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO105" t="inlineStr">
@@ -16507,12 +15701,7 @@
       </c>
       <c r="AP105" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ105" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS105" t="inlineStr">
@@ -16522,11 +15711,6 @@
       </c>
       <c r="AT105" t="n">
         <v>1</v>
-      </c>
-      <c r="AU105" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV105" t="inlineStr">
         <is>
@@ -16776,17 +15960,15 @@
       <c r="O107" t="n">
         <v>0</v>
       </c>
+      <c r="P107" t="n">
+        <v>0</v>
+      </c>
       <c r="Q107" t="n">
         <v>0</v>
       </c>
       <c r="R107" t="n">
         <v>0</v>
       </c>
-      <c r="S107" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U107" t="inlineStr">
         <is>
           <t>HOLD_JP_534554c6916adc005164f8ba7945</t>
@@ -16794,7 +15976,7 @@
       </c>
       <c r="AA107" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO107" t="inlineStr">
@@ -16804,12 +15986,7 @@
       </c>
       <c r="AP107" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ107" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS107" t="inlineStr">
@@ -16819,11 +15996,6 @@
       </c>
       <c r="AT107" t="n">
         <v>1</v>
-      </c>
-      <c r="AU107" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV107" t="inlineStr">
         <is>
@@ -16938,17 +16110,15 @@
       <c r="O108" t="n">
         <v>0</v>
       </c>
+      <c r="P108" t="n">
+        <v>0</v>
+      </c>
       <c r="Q108" t="n">
         <v>0</v>
       </c>
       <c r="R108" t="n">
         <v>0</v>
       </c>
-      <c r="S108" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U108" t="inlineStr">
         <is>
           <t>HOLD_JP_534554c6916adc005164f8ba7945</t>
@@ -16956,7 +16126,7 @@
       </c>
       <c r="AA108" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO108" t="inlineStr">
@@ -16966,12 +16136,7 @@
       </c>
       <c r="AP108" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ108" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS108" t="inlineStr">
@@ -16981,11 +16146,6 @@
       </c>
       <c r="AT108" t="n">
         <v>1</v>
-      </c>
-      <c r="AU108" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV108" t="inlineStr">
         <is>
@@ -17100,17 +16260,15 @@
       <c r="O109" t="n">
         <v>0</v>
       </c>
+      <c r="P109" t="n">
+        <v>0</v>
+      </c>
       <c r="Q109" t="n">
         <v>0</v>
       </c>
       <c r="R109" t="n">
         <v>0</v>
       </c>
-      <c r="S109" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U109" t="inlineStr">
         <is>
           <t>HOLD_JP_534554c6916adc005164f8ba7945</t>
@@ -17118,7 +16276,7 @@
       </c>
       <c r="AA109" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO109" t="inlineStr">
@@ -17128,12 +16286,7 @@
       </c>
       <c r="AP109" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ109" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS109" t="inlineStr">
@@ -17143,11 +16296,6 @@
       </c>
       <c r="AT109" t="n">
         <v>1</v>
-      </c>
-      <c r="AU109" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV109" t="inlineStr">
         <is>
@@ -17262,17 +16410,15 @@
       <c r="O110" t="n">
         <v>0</v>
       </c>
+      <c r="P110" t="n">
+        <v>0</v>
+      </c>
       <c r="Q110" t="n">
         <v>0</v>
       </c>
       <c r="R110" t="n">
         <v>0</v>
       </c>
-      <c r="S110" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U110" t="inlineStr">
         <is>
           <t>HOLD_JP_534554c6916adc005164f8ba7945</t>
@@ -17280,7 +16426,7 @@
       </c>
       <c r="AA110" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO110" t="inlineStr">
@@ -17290,12 +16436,7 @@
       </c>
       <c r="AP110" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ110" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS110" t="inlineStr">
@@ -17305,11 +16446,6 @@
       </c>
       <c r="AT110" t="n">
         <v>1</v>
-      </c>
-      <c r="AU110" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV110" t="inlineStr">
         <is>
@@ -17424,17 +16560,15 @@
       <c r="O111" t="n">
         <v>0</v>
       </c>
+      <c r="P111" t="n">
+        <v>0</v>
+      </c>
       <c r="Q111" t="n">
         <v>0</v>
       </c>
       <c r="R111" t="n">
         <v>0</v>
       </c>
-      <c r="S111" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U111" t="inlineStr">
         <is>
           <t>HOLD_JP_534554c6916adc005164f8ba7945</t>
@@ -17442,7 +16576,7 @@
       </c>
       <c r="AA111" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO111" t="inlineStr">
@@ -17452,12 +16586,7 @@
       </c>
       <c r="AP111" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ111" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS111" t="inlineStr">
@@ -17467,11 +16596,6 @@
       </c>
       <c r="AT111" t="n">
         <v>1</v>
-      </c>
-      <c r="AU111" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV111" t="inlineStr">
         <is>
@@ -17721,17 +16845,15 @@
       <c r="O113" t="n">
         <v>0</v>
       </c>
+      <c r="P113" t="n">
+        <v>0</v>
+      </c>
       <c r="Q113" t="n">
         <v>0</v>
       </c>
       <c r="R113" t="n">
         <v>0</v>
       </c>
-      <c r="S113" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U113" t="inlineStr">
         <is>
           <t>HOLD_JP_534554c6916adc005164f8ba7945</t>
@@ -17739,7 +16861,7 @@
       </c>
       <c r="AA113" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO113" t="inlineStr">
@@ -17749,12 +16871,7 @@
       </c>
       <c r="AP113" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ113" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS113" t="inlineStr">
@@ -17764,11 +16881,6 @@
       </c>
       <c r="AT113" t="n">
         <v>1</v>
-      </c>
-      <c r="AU113" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV113" t="inlineStr">
         <is>
@@ -17883,17 +16995,15 @@
       <c r="O114" t="n">
         <v>0</v>
       </c>
+      <c r="P114" t="n">
+        <v>0</v>
+      </c>
       <c r="Q114" t="n">
         <v>0</v>
       </c>
       <c r="R114" t="n">
         <v>0</v>
       </c>
-      <c r="S114" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U114" t="inlineStr">
         <is>
           <t>HOLD_JP_534554c6916adc005164f8ba7945</t>
@@ -17901,7 +17011,7 @@
       </c>
       <c r="AA114" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO114" t="inlineStr">
@@ -17911,12 +17021,7 @@
       </c>
       <c r="AP114" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ114" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS114" t="inlineStr">
@@ -17926,11 +17031,6 @@
       </c>
       <c r="AT114" t="n">
         <v>1</v>
-      </c>
-      <c r="AU114" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV114" t="inlineStr">
         <is>
@@ -18045,17 +17145,15 @@
       <c r="O115" t="n">
         <v>0</v>
       </c>
+      <c r="P115" t="n">
+        <v>0</v>
+      </c>
       <c r="Q115" t="n">
         <v>0</v>
       </c>
       <c r="R115" t="n">
         <v>0</v>
       </c>
-      <c r="S115" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U115" t="inlineStr">
         <is>
           <t>HOLD_JP_534554c6916adc005164f8ba7945</t>
@@ -18063,7 +17161,7 @@
       </c>
       <c r="AA115" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO115" t="inlineStr">
@@ -18073,12 +17171,7 @@
       </c>
       <c r="AP115" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ115" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS115" t="inlineStr">
@@ -18088,11 +17181,6 @@
       </c>
       <c r="AT115" t="n">
         <v>1</v>
-      </c>
-      <c r="AU115" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV115" t="inlineStr">
         <is>
@@ -18207,17 +17295,15 @@
       <c r="O116" t="n">
         <v>0</v>
       </c>
+      <c r="P116" t="n">
+        <v>0</v>
+      </c>
       <c r="Q116" t="n">
         <v>0</v>
       </c>
       <c r="R116" t="n">
         <v>0</v>
       </c>
-      <c r="S116" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U116" t="inlineStr">
         <is>
           <t>HOLD_JP_534554c6916adc005164f8ba7945</t>
@@ -18225,7 +17311,7 @@
       </c>
       <c r="AA116" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO116" t="inlineStr">
@@ -18235,12 +17321,7 @@
       </c>
       <c r="AP116" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ116" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS116" t="inlineStr">
@@ -18250,11 +17331,6 @@
       </c>
       <c r="AT116" t="n">
         <v>1</v>
-      </c>
-      <c r="AU116" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV116" t="inlineStr">
         <is>
@@ -18504,17 +17580,15 @@
       <c r="O118" t="n">
         <v>0</v>
       </c>
+      <c r="P118" t="n">
+        <v>0</v>
+      </c>
       <c r="Q118" t="n">
         <v>0</v>
       </c>
       <c r="R118" t="n">
         <v>0</v>
       </c>
-      <c r="S118" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U118" t="inlineStr">
         <is>
           <t>HOLD_JP_534554c6916adc005164f8ba7945</t>
@@ -18522,7 +17596,7 @@
       </c>
       <c r="AA118" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO118" t="inlineStr">
@@ -18532,12 +17606,7 @@
       </c>
       <c r="AP118" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ118" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS118" t="inlineStr">
@@ -18547,11 +17616,6 @@
       </c>
       <c r="AT118" t="n">
         <v>1</v>
-      </c>
-      <c r="AU118" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV118" t="inlineStr">
         <is>
@@ -18666,17 +17730,15 @@
       <c r="O119" t="n">
         <v>0</v>
       </c>
+      <c r="P119" t="n">
+        <v>0</v>
+      </c>
       <c r="Q119" t="n">
         <v>0</v>
       </c>
       <c r="R119" t="n">
         <v>0</v>
       </c>
-      <c r="S119" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U119" t="inlineStr">
         <is>
           <t>HOLD_JP_534554c6916adc005164f8ba7945</t>
@@ -18684,7 +17746,7 @@
       </c>
       <c r="AA119" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO119" t="inlineStr">
@@ -18694,12 +17756,7 @@
       </c>
       <c r="AP119" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ119" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS119" t="inlineStr">
@@ -18709,11 +17766,6 @@
       </c>
       <c r="AT119" t="n">
         <v>1</v>
-      </c>
-      <c r="AU119" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV119" t="inlineStr">
         <is>
@@ -18828,17 +17880,15 @@
       <c r="O120" t="n">
         <v>0</v>
       </c>
+      <c r="P120" t="n">
+        <v>0</v>
+      </c>
       <c r="Q120" t="n">
         <v>0</v>
       </c>
       <c r="R120" t="n">
         <v>0</v>
       </c>
-      <c r="S120" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U120" t="inlineStr">
         <is>
           <t>HOLD_JP_534554c6916adc005164f8ba7945</t>
@@ -18846,7 +17896,7 @@
       </c>
       <c r="AA120" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO120" t="inlineStr">
@@ -18856,12 +17906,7 @@
       </c>
       <c r="AP120" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ120" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS120" t="inlineStr">
@@ -18871,11 +17916,6 @@
       </c>
       <c r="AT120" t="n">
         <v>1</v>
-      </c>
-      <c r="AU120" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV120" t="inlineStr">
         <is>
@@ -18990,17 +18030,15 @@
       <c r="O121" t="n">
         <v>0</v>
       </c>
+      <c r="P121" t="n">
+        <v>0</v>
+      </c>
       <c r="Q121" t="n">
         <v>0</v>
       </c>
       <c r="R121" t="n">
         <v>0</v>
       </c>
-      <c r="S121" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U121" t="inlineStr">
         <is>
           <t>HOLD_JP_534554c6916adc005164f8ba7945</t>
@@ -19008,7 +18046,7 @@
       </c>
       <c r="AA121" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO121" t="inlineStr">
@@ -19018,12 +18056,7 @@
       </c>
       <c r="AP121" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ121" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS121" t="inlineStr">
@@ -19033,11 +18066,6 @@
       </c>
       <c r="AT121" t="n">
         <v>1</v>
-      </c>
-      <c r="AU121" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV121" t="inlineStr">
         <is>
@@ -19287,17 +18315,15 @@
       <c r="O123" t="n">
         <v>0</v>
       </c>
+      <c r="P123" t="n">
+        <v>0</v>
+      </c>
       <c r="Q123" t="n">
         <v>0</v>
       </c>
       <c r="R123" t="n">
         <v>0</v>
       </c>
-      <c r="S123" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U123" t="inlineStr">
         <is>
           <t>HOLD_JP_534554c6916adc005164f8ba7945</t>
@@ -19305,7 +18331,7 @@
       </c>
       <c r="AA123" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO123" t="inlineStr">
@@ -19315,12 +18341,7 @@
       </c>
       <c r="AP123" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ123" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS123" t="inlineStr">
@@ -19330,11 +18351,6 @@
       </c>
       <c r="AT123" t="n">
         <v>1</v>
-      </c>
-      <c r="AU123" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV123" t="inlineStr">
         <is>
@@ -19449,17 +18465,15 @@
       <c r="O124" t="n">
         <v>0</v>
       </c>
+      <c r="P124" t="n">
+        <v>0</v>
+      </c>
       <c r="Q124" t="n">
         <v>0</v>
       </c>
       <c r="R124" t="n">
         <v>0</v>
       </c>
-      <c r="S124" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U124" t="inlineStr">
         <is>
           <t>HOLD_JP_534554c6916adc005164f8ba7945</t>
@@ -19467,7 +18481,7 @@
       </c>
       <c r="AA124" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO124" t="inlineStr">
@@ -19477,12 +18491,7 @@
       </c>
       <c r="AP124" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ124" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS124" t="inlineStr">
@@ -19492,11 +18501,6 @@
       </c>
       <c r="AT124" t="n">
         <v>1</v>
-      </c>
-      <c r="AU124" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV124" t="inlineStr">
         <is>
@@ -19611,17 +18615,15 @@
       <c r="O125" t="n">
         <v>0</v>
       </c>
+      <c r="P125" t="n">
+        <v>0</v>
+      </c>
       <c r="Q125" t="n">
         <v>0</v>
       </c>
       <c r="R125" t="n">
         <v>0</v>
       </c>
-      <c r="S125" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U125" t="inlineStr">
         <is>
           <t>HOLD_JP_534554c6916adc005164f8ba7945</t>
@@ -19629,7 +18631,7 @@
       </c>
       <c r="AA125" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO125" t="inlineStr">
@@ -19639,12 +18641,7 @@
       </c>
       <c r="AP125" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ125" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS125" t="inlineStr">
@@ -19654,11 +18651,6 @@
       </c>
       <c r="AT125" t="n">
         <v>1</v>
-      </c>
-      <c r="AU125" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV125" t="inlineStr">
         <is>
@@ -19773,17 +18765,15 @@
       <c r="O126" t="n">
         <v>0</v>
       </c>
+      <c r="P126" t="n">
+        <v>0</v>
+      </c>
       <c r="Q126" t="n">
         <v>0</v>
       </c>
       <c r="R126" t="n">
         <v>0</v>
       </c>
-      <c r="S126" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U126" t="inlineStr">
         <is>
           <t>HOLD_JP_534554c6916adc005164f8ba7945</t>
@@ -19791,7 +18781,7 @@
       </c>
       <c r="AA126" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO126" t="inlineStr">
@@ -19801,12 +18791,7 @@
       </c>
       <c r="AP126" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ126" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS126" t="inlineStr">
@@ -19816,11 +18801,6 @@
       </c>
       <c r="AT126" t="n">
         <v>1</v>
-      </c>
-      <c r="AU126" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV126" t="inlineStr">
         <is>
@@ -20070,17 +19050,15 @@
       <c r="O128" t="n">
         <v>0</v>
       </c>
+      <c r="P128" t="n">
+        <v>0</v>
+      </c>
       <c r="Q128" t="n">
         <v>0</v>
       </c>
       <c r="R128" t="n">
         <v>0</v>
       </c>
-      <c r="S128" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U128" t="inlineStr">
         <is>
           <t>HOLD_JP_534554c6916adc005164f8ba7945</t>
@@ -20088,7 +19066,7 @@
       </c>
       <c r="AA128" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO128" t="inlineStr">
@@ -20098,12 +19076,7 @@
       </c>
       <c r="AP128" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ128" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS128" t="inlineStr">
@@ -20113,11 +19086,6 @@
       </c>
       <c r="AT128" t="n">
         <v>1</v>
-      </c>
-      <c r="AU128" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV128" t="inlineStr">
         <is>
@@ -20232,17 +19200,15 @@
       <c r="O129" t="n">
         <v>0</v>
       </c>
+      <c r="P129" t="n">
+        <v>0</v>
+      </c>
       <c r="Q129" t="n">
         <v>0</v>
       </c>
       <c r="R129" t="n">
         <v>0</v>
       </c>
-      <c r="S129" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U129" t="inlineStr">
         <is>
           <t>HOLD_JP_534554c6916adc005164f8ba7945</t>
@@ -20250,7 +19216,7 @@
       </c>
       <c r="AA129" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO129" t="inlineStr">
@@ -20260,12 +19226,7 @@
       </c>
       <c r="AP129" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ129" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS129" t="inlineStr">
@@ -20275,11 +19236,6 @@
       </c>
       <c r="AT129" t="n">
         <v>1</v>
-      </c>
-      <c r="AU129" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV129" t="inlineStr">
         <is>
@@ -20394,17 +19350,15 @@
       <c r="O130" t="n">
         <v>0</v>
       </c>
+      <c r="P130" t="n">
+        <v>0</v>
+      </c>
       <c r="Q130" t="n">
         <v>0</v>
       </c>
       <c r="R130" t="n">
         <v>0</v>
       </c>
-      <c r="S130" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U130" t="inlineStr">
         <is>
           <t>HOLD_JP_534554c6916adc005164f8ba7945</t>
@@ -20412,7 +19366,7 @@
       </c>
       <c r="AA130" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO130" t="inlineStr">
@@ -20422,12 +19376,7 @@
       </c>
       <c r="AP130" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ130" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS130" t="inlineStr">
@@ -20437,11 +19386,6 @@
       </c>
       <c r="AT130" t="n">
         <v>1</v>
-      </c>
-      <c r="AU130" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV130" t="inlineStr">
         <is>
@@ -20556,17 +19500,15 @@
       <c r="O131" t="n">
         <v>0</v>
       </c>
+      <c r="P131" t="n">
+        <v>0</v>
+      </c>
       <c r="Q131" t="n">
         <v>0</v>
       </c>
       <c r="R131" t="n">
         <v>0</v>
       </c>
-      <c r="S131" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U131" t="inlineStr">
         <is>
           <t>HOLD_JP_534554c6916adc005164f8ba7945</t>
@@ -20574,7 +19516,7 @@
       </c>
       <c r="AA131" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO131" t="inlineStr">
@@ -20584,12 +19526,7 @@
       </c>
       <c r="AP131" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ131" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS131" t="inlineStr">
@@ -20599,11 +19536,6 @@
       </c>
       <c r="AT131" t="n">
         <v>1</v>
-      </c>
-      <c r="AU131" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV131" t="inlineStr">
         <is>
@@ -20718,17 +19650,15 @@
       <c r="O132" t="n">
         <v>0</v>
       </c>
+      <c r="P132" t="n">
+        <v>0</v>
+      </c>
       <c r="Q132" t="n">
         <v>0</v>
       </c>
       <c r="R132" t="n">
         <v>0</v>
       </c>
-      <c r="S132" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U132" t="inlineStr">
         <is>
           <t>HOLD_JP_534554c6916adc005164f8ba7945</t>
@@ -20736,7 +19666,7 @@
       </c>
       <c r="AA132" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO132" t="inlineStr">
@@ -20746,12 +19676,7 @@
       </c>
       <c r="AP132" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ132" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS132" t="inlineStr">
@@ -20761,11 +19686,6 @@
       </c>
       <c r="AT132" t="n">
         <v>1</v>
-      </c>
-      <c r="AU132" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV132" t="inlineStr">
         <is>
@@ -21015,17 +19935,15 @@
       <c r="O134" t="n">
         <v>0</v>
       </c>
+      <c r="P134" t="n">
+        <v>0</v>
+      </c>
       <c r="Q134" t="n">
         <v>0</v>
       </c>
       <c r="R134" t="n">
         <v>0</v>
       </c>
-      <c r="S134" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U134" t="inlineStr">
         <is>
           <t>HOLD_JP_534554c6916adc005164f8ba7945</t>
@@ -21033,7 +19951,7 @@
       </c>
       <c r="AA134" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO134" t="inlineStr">
@@ -21043,12 +19961,7 @@
       </c>
       <c r="AP134" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ134" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS134" t="inlineStr">
@@ -21058,11 +19971,6 @@
       </c>
       <c r="AT134" t="n">
         <v>1</v>
-      </c>
-      <c r="AU134" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV134" t="inlineStr">
         <is>
@@ -21177,17 +20085,15 @@
       <c r="O135" t="n">
         <v>0</v>
       </c>
+      <c r="P135" t="n">
+        <v>0</v>
+      </c>
       <c r="Q135" t="n">
         <v>0</v>
       </c>
       <c r="R135" t="n">
         <v>0</v>
       </c>
-      <c r="S135" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U135" t="inlineStr">
         <is>
           <t>HOLD_JP_534554c6916adc005164f8ba7945</t>
@@ -21195,7 +20101,7 @@
       </c>
       <c r="AA135" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO135" t="inlineStr">
@@ -21205,12 +20111,7 @@
       </c>
       <c r="AP135" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ135" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS135" t="inlineStr">
@@ -21220,11 +20121,6 @@
       </c>
       <c r="AT135" t="n">
         <v>1</v>
-      </c>
-      <c r="AU135" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV135" t="inlineStr">
         <is>
@@ -21339,17 +20235,15 @@
       <c r="O136" t="n">
         <v>0</v>
       </c>
+      <c r="P136" t="n">
+        <v>0</v>
+      </c>
       <c r="Q136" t="n">
         <v>0</v>
       </c>
       <c r="R136" t="n">
         <v>0</v>
       </c>
-      <c r="S136" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U136" t="inlineStr">
         <is>
           <t>HOLD_JP_534554c6916adc005164f8ba7945</t>
@@ -21357,7 +20251,7 @@
       </c>
       <c r="AA136" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO136" t="inlineStr">
@@ -21367,12 +20261,7 @@
       </c>
       <c r="AP136" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ136" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS136" t="inlineStr">
@@ -21382,11 +20271,6 @@
       </c>
       <c r="AT136" t="n">
         <v>1</v>
-      </c>
-      <c r="AU136" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV136" t="inlineStr">
         <is>
@@ -21501,17 +20385,15 @@
       <c r="O137" t="n">
         <v>0</v>
       </c>
+      <c r="P137" t="n">
+        <v>0</v>
+      </c>
       <c r="Q137" t="n">
         <v>0</v>
       </c>
       <c r="R137" t="n">
         <v>0</v>
       </c>
-      <c r="S137" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U137" t="inlineStr">
         <is>
           <t>HOLD_JP_534554c6916adc005164f8ba7945</t>
@@ -21519,7 +20401,7 @@
       </c>
       <c r="AA137" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO137" t="inlineStr">
@@ -21529,12 +20411,7 @@
       </c>
       <c r="AP137" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ137" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS137" t="inlineStr">
@@ -21544,11 +20421,6 @@
       </c>
       <c r="AT137" t="n">
         <v>1</v>
-      </c>
-      <c r="AU137" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV137" t="inlineStr">
         <is>
@@ -21798,17 +20670,15 @@
       <c r="O139" t="n">
         <v>0</v>
       </c>
+      <c r="P139" t="n">
+        <v>0</v>
+      </c>
       <c r="Q139" t="n">
         <v>0</v>
       </c>
       <c r="R139" t="n">
         <v>0</v>
       </c>
-      <c r="S139" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U139" t="inlineStr">
         <is>
           <t>HOLD_JP_534554c6916adc005164f8ba7945</t>
@@ -21816,7 +20686,7 @@
       </c>
       <c r="AA139" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO139" t="inlineStr">
@@ -21826,12 +20696,7 @@
       </c>
       <c r="AP139" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ139" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS139" t="inlineStr">
@@ -21841,11 +20706,6 @@
       </c>
       <c r="AT139" t="n">
         <v>1</v>
-      </c>
-      <c r="AU139" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV139" t="inlineStr">
         <is>
@@ -21960,17 +20820,15 @@
       <c r="O140" t="n">
         <v>0</v>
       </c>
+      <c r="P140" t="n">
+        <v>0</v>
+      </c>
       <c r="Q140" t="n">
         <v>0</v>
       </c>
       <c r="R140" t="n">
         <v>0</v>
       </c>
-      <c r="S140" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U140" t="inlineStr">
         <is>
           <t>HOLD_JP_534554c6916adc005164f8ba7945</t>
@@ -21978,7 +20836,7 @@
       </c>
       <c r="AA140" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO140" t="inlineStr">
@@ -21988,12 +20846,7 @@
       </c>
       <c r="AP140" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ140" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS140" t="inlineStr">
@@ -22003,11 +20856,6 @@
       </c>
       <c r="AT140" t="n">
         <v>1</v>
-      </c>
-      <c r="AU140" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV140" t="inlineStr">
         <is>
@@ -22122,17 +20970,15 @@
       <c r="O141" t="n">
         <v>0</v>
       </c>
+      <c r="P141" t="n">
+        <v>0</v>
+      </c>
       <c r="Q141" t="n">
         <v>0</v>
       </c>
       <c r="R141" t="n">
         <v>0</v>
       </c>
-      <c r="S141" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U141" t="inlineStr">
         <is>
           <t>HOLD_JP_534554c6916adc005164f8ba7945</t>
@@ -22140,7 +20986,7 @@
       </c>
       <c r="AA141" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO141" t="inlineStr">
@@ -22150,12 +20996,7 @@
       </c>
       <c r="AP141" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ141" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS141" t="inlineStr">
@@ -22165,11 +21006,6 @@
       </c>
       <c r="AT141" t="n">
         <v>1</v>
-      </c>
-      <c r="AU141" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV141" t="inlineStr">
         <is>
@@ -22284,17 +21120,15 @@
       <c r="O142" t="n">
         <v>0</v>
       </c>
+      <c r="P142" t="n">
+        <v>0</v>
+      </c>
       <c r="Q142" t="n">
         <v>0</v>
       </c>
       <c r="R142" t="n">
         <v>0</v>
       </c>
-      <c r="S142" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U142" t="inlineStr">
         <is>
           <t>HOLD_JP_534554c6916adc005164f8ba7945</t>
@@ -22302,7 +21136,7 @@
       </c>
       <c r="AA142" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO142" t="inlineStr">
@@ -22312,12 +21146,7 @@
       </c>
       <c r="AP142" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ142" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS142" t="inlineStr">
@@ -22327,11 +21156,6 @@
       </c>
       <c r="AT142" t="n">
         <v>1</v>
-      </c>
-      <c r="AU142" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV142" t="inlineStr">
         <is>
@@ -22446,17 +21270,15 @@
       <c r="O143" t="n">
         <v>0</v>
       </c>
+      <c r="P143" t="n">
+        <v>0</v>
+      </c>
       <c r="Q143" t="n">
         <v>0</v>
       </c>
       <c r="R143" t="n">
         <v>0</v>
       </c>
-      <c r="S143" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U143" t="inlineStr">
         <is>
           <t>HOLD_JP_534554c6916adc005164f8ba7945</t>
@@ -22464,7 +21286,7 @@
       </c>
       <c r="AA143" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO143" t="inlineStr">
@@ -22474,12 +21296,7 @@
       </c>
       <c r="AP143" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ143" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS143" t="inlineStr">
@@ -22489,11 +21306,6 @@
       </c>
       <c r="AT143" t="n">
         <v>1</v>
-      </c>
-      <c r="AU143" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV143" t="inlineStr">
         <is>
@@ -22743,17 +21555,15 @@
       <c r="O145" t="n">
         <v>0</v>
       </c>
+      <c r="P145" t="n">
+        <v>0</v>
+      </c>
       <c r="Q145" t="n">
         <v>0</v>
       </c>
       <c r="R145" t="n">
         <v>0</v>
       </c>
-      <c r="S145" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U145" t="inlineStr">
         <is>
           <t>HOLD_JP_534554c6916adc005164f8ba7945</t>
@@ -22761,7 +21571,7 @@
       </c>
       <c r="AA145" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO145" t="inlineStr">
@@ -22771,12 +21581,7 @@
       </c>
       <c r="AP145" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ145" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS145" t="inlineStr">
@@ -22786,11 +21591,6 @@
       </c>
       <c r="AT145" t="n">
         <v>1</v>
-      </c>
-      <c r="AU145" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV145" t="inlineStr">
         <is>
@@ -22905,17 +21705,15 @@
       <c r="O146" t="n">
         <v>0</v>
       </c>
+      <c r="P146" t="n">
+        <v>0</v>
+      </c>
       <c r="Q146" t="n">
         <v>0</v>
       </c>
       <c r="R146" t="n">
         <v>0</v>
       </c>
-      <c r="S146" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U146" t="inlineStr">
         <is>
           <t>HOLD_JP_534554c6916adc005164f8ba7945</t>
@@ -22923,7 +21721,7 @@
       </c>
       <c r="AA146" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO146" t="inlineStr">
@@ -22933,12 +21731,7 @@
       </c>
       <c r="AP146" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ146" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS146" t="inlineStr">
@@ -22948,11 +21741,6 @@
       </c>
       <c r="AT146" t="n">
         <v>1</v>
-      </c>
-      <c r="AU146" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV146" t="inlineStr">
         <is>
@@ -23067,17 +21855,15 @@
       <c r="O147" t="n">
         <v>0</v>
       </c>
+      <c r="P147" t="n">
+        <v>0</v>
+      </c>
       <c r="Q147" t="n">
         <v>0</v>
       </c>
       <c r="R147" t="n">
         <v>0</v>
       </c>
-      <c r="S147" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U147" t="inlineStr">
         <is>
           <t>HOLD_JP_534554c6916adc005164f8ba7945</t>
@@ -23085,7 +21871,7 @@
       </c>
       <c r="AA147" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO147" t="inlineStr">
@@ -23095,12 +21881,7 @@
       </c>
       <c r="AP147" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ147" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS147" t="inlineStr">
@@ -23110,11 +21891,6 @@
       </c>
       <c r="AT147" t="n">
         <v>1</v>
-      </c>
-      <c r="AU147" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV147" t="inlineStr">
         <is>
@@ -23229,17 +22005,15 @@
       <c r="O148" t="n">
         <v>0</v>
       </c>
+      <c r="P148" t="n">
+        <v>0</v>
+      </c>
       <c r="Q148" t="n">
         <v>0</v>
       </c>
       <c r="R148" t="n">
         <v>0</v>
       </c>
-      <c r="S148" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U148" t="inlineStr">
         <is>
           <t>HOLD_JP_534554c6916adc005164f8ba7945</t>
@@ -23247,7 +22021,7 @@
       </c>
       <c r="AA148" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO148" t="inlineStr">
@@ -23257,12 +22031,7 @@
       </c>
       <c r="AP148" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ148" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS148" t="inlineStr">
@@ -23272,11 +22041,6 @@
       </c>
       <c r="AT148" t="n">
         <v>1</v>
-      </c>
-      <c r="AU148" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV148" t="inlineStr">
         <is>
@@ -23526,17 +22290,15 @@
       <c r="O150" t="n">
         <v>0</v>
       </c>
+      <c r="P150" t="n">
+        <v>0</v>
+      </c>
       <c r="Q150" t="n">
         <v>0</v>
       </c>
       <c r="R150" t="n">
         <v>0</v>
       </c>
-      <c r="S150" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U150" t="inlineStr">
         <is>
           <t>HOLD_JP_534554c6916adc005164f8ba7945</t>
@@ -23544,7 +22306,7 @@
       </c>
       <c r="AA150" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO150" t="inlineStr">
@@ -23554,12 +22316,7 @@
       </c>
       <c r="AP150" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ150" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS150" t="inlineStr">
@@ -23569,11 +22326,6 @@
       </c>
       <c r="AT150" t="n">
         <v>1</v>
-      </c>
-      <c r="AU150" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV150" t="inlineStr">
         <is>
@@ -23829,17 +22581,15 @@
       <c r="O152" t="n">
         <v>0</v>
       </c>
+      <c r="P152" t="n">
+        <v>0</v>
+      </c>
       <c r="Q152" t="n">
         <v>0</v>
       </c>
       <c r="R152" t="n">
         <v>0</v>
       </c>
-      <c r="S152" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U152" t="inlineStr">
         <is>
           <t>HOLD_JP_534554c6916adc005164f8ba7945</t>
@@ -23847,7 +22597,7 @@
       </c>
       <c r="AA152" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO152" t="inlineStr">
@@ -23857,12 +22607,7 @@
       </c>
       <c r="AP152" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ152" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS152" t="inlineStr">
@@ -23872,11 +22617,6 @@
       </c>
       <c r="AT152" t="n">
         <v>1</v>
-      </c>
-      <c r="AU152" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV152" t="inlineStr">
         <is>
@@ -23991,17 +22731,15 @@
       <c r="O153" t="n">
         <v>0</v>
       </c>
+      <c r="P153" t="n">
+        <v>0</v>
+      </c>
       <c r="Q153" t="n">
         <v>0</v>
       </c>
       <c r="R153" t="n">
         <v>0</v>
       </c>
-      <c r="S153" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U153" t="inlineStr">
         <is>
           <t>HOLD_JP_534554c6916adc005164f8ba7945</t>
@@ -24009,7 +22747,7 @@
       </c>
       <c r="AA153" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO153" t="inlineStr">
@@ -24019,12 +22757,7 @@
       </c>
       <c r="AP153" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ153" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS153" t="inlineStr">
@@ -24034,11 +22767,6 @@
       </c>
       <c r="AT153" t="n">
         <v>1</v>
-      </c>
-      <c r="AU153" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV153" t="inlineStr">
         <is>
@@ -24153,17 +22881,15 @@
       <c r="O154" t="n">
         <v>0</v>
       </c>
+      <c r="P154" t="n">
+        <v>0</v>
+      </c>
       <c r="Q154" t="n">
         <v>0</v>
       </c>
       <c r="R154" t="n">
         <v>0</v>
       </c>
-      <c r="S154" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U154" t="inlineStr">
         <is>
           <t>HOLD_JP_534554c6916adc005164f8ba7945</t>
@@ -24171,7 +22897,7 @@
       </c>
       <c r="AA154" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO154" t="inlineStr">
@@ -24181,12 +22907,7 @@
       </c>
       <c r="AP154" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ154" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS154" t="inlineStr">
@@ -24196,11 +22917,6 @@
       </c>
       <c r="AT154" t="n">
         <v>1</v>
-      </c>
-      <c r="AU154" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV154" t="inlineStr">
         <is>
@@ -24591,17 +23307,15 @@
       <c r="O157" t="n">
         <v>0</v>
       </c>
+      <c r="P157" t="n">
+        <v>0</v>
+      </c>
       <c r="Q157" t="n">
         <v>0</v>
       </c>
       <c r="R157" t="n">
         <v>0</v>
       </c>
-      <c r="S157" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U157" t="inlineStr">
         <is>
           <t>HOLD_JP_534554c6916adc005164f8ba7945</t>
@@ -24609,7 +23323,7 @@
       </c>
       <c r="AA157" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO157" t="inlineStr">
@@ -24619,12 +23333,7 @@
       </c>
       <c r="AP157" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ157" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS157" t="inlineStr">
@@ -24634,11 +23343,6 @@
       </c>
       <c r="AT157" t="n">
         <v>1</v>
-      </c>
-      <c r="AU157" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV157" t="inlineStr">
         <is>
@@ -24894,17 +23598,15 @@
       <c r="O159" t="n">
         <v>0</v>
       </c>
+      <c r="P159" t="n">
+        <v>0</v>
+      </c>
       <c r="Q159" t="n">
         <v>0</v>
       </c>
       <c r="R159" t="n">
         <v>0</v>
       </c>
-      <c r="S159" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U159" t="inlineStr">
         <is>
           <t>HOLD_JP_534554c6916adc005164f8ba7945</t>
@@ -24912,7 +23614,7 @@
       </c>
       <c r="AA159" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO159" t="inlineStr">
@@ -24922,12 +23624,7 @@
       </c>
       <c r="AP159" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ159" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS159" t="inlineStr">
@@ -24937,11 +23634,6 @@
       </c>
       <c r="AT159" t="n">
         <v>1</v>
-      </c>
-      <c r="AU159" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV159" t="inlineStr">
         <is>
@@ -25056,17 +23748,15 @@
       <c r="O160" t="n">
         <v>0</v>
       </c>
+      <c r="P160" t="n">
+        <v>0</v>
+      </c>
       <c r="Q160" t="n">
         <v>0</v>
       </c>
       <c r="R160" t="n">
         <v>0</v>
       </c>
-      <c r="S160" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U160" t="inlineStr">
         <is>
           <t>HOLD_JP_534554c6916adc005164f8ba7945</t>
@@ -25074,7 +23764,7 @@
       </c>
       <c r="AA160" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO160" t="inlineStr">
@@ -25084,12 +23774,7 @@
       </c>
       <c r="AP160" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ160" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS160" t="inlineStr">
@@ -25099,11 +23784,6 @@
       </c>
       <c r="AT160" t="n">
         <v>1</v>
-      </c>
-      <c r="AU160" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV160" t="inlineStr">
         <is>
@@ -25218,17 +23898,15 @@
       <c r="O161" t="n">
         <v>0</v>
       </c>
+      <c r="P161" t="n">
+        <v>0</v>
+      </c>
       <c r="Q161" t="n">
         <v>0</v>
       </c>
       <c r="R161" t="n">
         <v>0</v>
       </c>
-      <c r="S161" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U161" t="inlineStr">
         <is>
           <t>HOLD_JP_534554c6916adc005164f8ba7945</t>
@@ -25236,7 +23914,7 @@
       </c>
       <c r="AA161" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO161" t="inlineStr">
@@ -25246,12 +23924,7 @@
       </c>
       <c r="AP161" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ161" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS161" t="inlineStr">
@@ -25261,11 +23934,6 @@
       </c>
       <c r="AT161" t="n">
         <v>1</v>
-      </c>
-      <c r="AU161" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV161" t="inlineStr">
         <is>
@@ -25380,17 +24048,15 @@
       <c r="O162" t="n">
         <v>0</v>
       </c>
+      <c r="P162" t="n">
+        <v>0</v>
+      </c>
       <c r="Q162" t="n">
         <v>0</v>
       </c>
       <c r="R162" t="n">
         <v>0</v>
       </c>
-      <c r="S162" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U162" t="inlineStr">
         <is>
           <t>HOLD_JP_534554c6916adc005164f8ba7945</t>
@@ -25398,7 +24064,7 @@
       </c>
       <c r="AA162" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO162" t="inlineStr">
@@ -25408,12 +24074,7 @@
       </c>
       <c r="AP162" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ162" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS162" t="inlineStr">
@@ -25423,11 +24084,6 @@
       </c>
       <c r="AT162" t="n">
         <v>1</v>
-      </c>
-      <c r="AU162" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV162" t="inlineStr">
         <is>
@@ -25677,17 +24333,15 @@
       <c r="O164" t="n">
         <v>0</v>
       </c>
+      <c r="P164" t="n">
+        <v>0</v>
+      </c>
       <c r="Q164" t="n">
         <v>0</v>
       </c>
       <c r="R164" t="n">
         <v>0</v>
       </c>
-      <c r="S164" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U164" t="inlineStr">
         <is>
           <t>HOLD_JP_534554c6916adc005164f8ba7945</t>
@@ -25695,7 +24349,7 @@
       </c>
       <c r="AA164" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO164" t="inlineStr">
@@ -25705,12 +24359,7 @@
       </c>
       <c r="AP164" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ164" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS164" t="inlineStr">
@@ -25720,11 +24369,6 @@
       </c>
       <c r="AT164" t="n">
         <v>1</v>
-      </c>
-      <c r="AU164" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV164" t="inlineStr">
         <is>
@@ -25839,17 +24483,15 @@
       <c r="O165" t="n">
         <v>0</v>
       </c>
+      <c r="P165" t="n">
+        <v>0</v>
+      </c>
       <c r="Q165" t="n">
         <v>0</v>
       </c>
       <c r="R165" t="n">
         <v>0</v>
       </c>
-      <c r="S165" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U165" t="inlineStr">
         <is>
           <t>HOLD_JP_534554c6916adc005164f8ba7945</t>
@@ -25857,7 +24499,7 @@
       </c>
       <c r="AA165" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO165" t="inlineStr">
@@ -25867,12 +24509,7 @@
       </c>
       <c r="AP165" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ165" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS165" t="inlineStr">
@@ -25882,11 +24519,6 @@
       </c>
       <c r="AT165" t="n">
         <v>1</v>
-      </c>
-      <c r="AU165" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV165" t="inlineStr">
         <is>
@@ -26001,17 +24633,15 @@
       <c r="O166" t="n">
         <v>0</v>
       </c>
+      <c r="P166" t="n">
+        <v>0</v>
+      </c>
       <c r="Q166" t="n">
         <v>0</v>
       </c>
       <c r="R166" t="n">
         <v>0</v>
       </c>
-      <c r="S166" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U166" t="inlineStr">
         <is>
           <t>HOLD_JP_534554c6916adc005164f8ba7945</t>
@@ -26019,7 +24649,7 @@
       </c>
       <c r="AA166" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO166" t="inlineStr">
@@ -26029,12 +24659,7 @@
       </c>
       <c r="AP166" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ166" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS166" t="inlineStr">
@@ -26044,11 +24669,6 @@
       </c>
       <c r="AT166" t="n">
         <v>1</v>
-      </c>
-      <c r="AU166" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV166" t="inlineStr">
         <is>
@@ -26163,17 +24783,15 @@
       <c r="O167" t="n">
         <v>0</v>
       </c>
+      <c r="P167" t="n">
+        <v>0</v>
+      </c>
       <c r="Q167" t="n">
         <v>0</v>
       </c>
       <c r="R167" t="n">
         <v>0</v>
       </c>
-      <c r="S167" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U167" t="inlineStr">
         <is>
           <t>HOLD_JP_534554c6916adc005164f8ba7945</t>
@@ -26181,7 +24799,7 @@
       </c>
       <c r="AA167" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO167" t="inlineStr">
@@ -26191,12 +24809,7 @@
       </c>
       <c r="AP167" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ167" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS167" t="inlineStr">
@@ -26206,11 +24819,6 @@
       </c>
       <c r="AT167" t="n">
         <v>1</v>
-      </c>
-      <c r="AU167" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV167" t="inlineStr">
         <is>
@@ -26460,17 +25068,15 @@
       <c r="O169" t="n">
         <v>0</v>
       </c>
+      <c r="P169" t="n">
+        <v>0</v>
+      </c>
       <c r="Q169" t="n">
         <v>0</v>
       </c>
       <c r="R169" t="n">
         <v>0</v>
       </c>
-      <c r="S169" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U169" t="inlineStr">
         <is>
           <t>HOLD_JP_534554c6916adc005164f8ba7945</t>
@@ -26478,7 +25084,7 @@
       </c>
       <c r="AA169" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO169" t="inlineStr">
@@ -26488,12 +25094,7 @@
       </c>
       <c r="AP169" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ169" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS169" t="inlineStr">
@@ -26503,11 +25104,6 @@
       </c>
       <c r="AT169" t="n">
         <v>1</v>
-      </c>
-      <c r="AU169" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV169" t="inlineStr">
         <is>
@@ -26622,17 +25218,15 @@
       <c r="O170" t="n">
         <v>0</v>
       </c>
+      <c r="P170" t="n">
+        <v>0</v>
+      </c>
       <c r="Q170" t="n">
         <v>0</v>
       </c>
       <c r="R170" t="n">
         <v>0</v>
       </c>
-      <c r="S170" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U170" t="inlineStr">
         <is>
           <t>HOLD_JP_534554c6916adc005164f8ba7945</t>
@@ -26640,7 +25234,7 @@
       </c>
       <c r="AA170" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO170" t="inlineStr">
@@ -26650,12 +25244,7 @@
       </c>
       <c r="AP170" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ170" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS170" t="inlineStr">
@@ -26665,11 +25254,6 @@
       </c>
       <c r="AT170" t="n">
         <v>1</v>
-      </c>
-      <c r="AU170" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV170" t="inlineStr">
         <is>
@@ -26784,17 +25368,15 @@
       <c r="O171" t="n">
         <v>0</v>
       </c>
+      <c r="P171" t="n">
+        <v>0</v>
+      </c>
       <c r="Q171" t="n">
         <v>0</v>
       </c>
       <c r="R171" t="n">
         <v>0</v>
       </c>
-      <c r="S171" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U171" t="inlineStr">
         <is>
           <t>HOLD_JP_534554c6916adc005164f8ba7945</t>
@@ -26802,7 +25384,7 @@
       </c>
       <c r="AA171" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO171" t="inlineStr">
@@ -26812,12 +25394,7 @@
       </c>
       <c r="AP171" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ171" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS171" t="inlineStr">
@@ -26827,11 +25404,6 @@
       </c>
       <c r="AT171" t="n">
         <v>1</v>
-      </c>
-      <c r="AU171" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV171" t="inlineStr">
         <is>
@@ -26946,17 +25518,15 @@
       <c r="O172" t="n">
         <v>0</v>
       </c>
+      <c r="P172" t="n">
+        <v>0</v>
+      </c>
       <c r="Q172" t="n">
         <v>0</v>
       </c>
       <c r="R172" t="n">
         <v>0</v>
       </c>
-      <c r="S172" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U172" t="inlineStr">
         <is>
           <t>HOLD_JP_534554c6916adc005164f8ba7945</t>
@@ -26964,7 +25534,7 @@
       </c>
       <c r="AA172" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO172" t="inlineStr">
@@ -26974,12 +25544,7 @@
       </c>
       <c r="AP172" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ172" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS172" t="inlineStr">
@@ -26989,11 +25554,6 @@
       </c>
       <c r="AT172" t="n">
         <v>1</v>
-      </c>
-      <c r="AU172" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV172" t="inlineStr">
         <is>

--- a/diseases/d050/2010-2014.xlsx
+++ b/diseases/d050/2010-2014.xlsx
@@ -22391,17 +22391,17 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>DE-HH</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Hamburg, Germany</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
@@ -22440,33 +22440,125 @@
       <c r="O151" t="n">
         <v>1</v>
       </c>
+      <c r="P151" t="n">
+        <v>1</v>
+      </c>
       <c r="U151" t="inlineStr">
         <is>
-          <t>HOLD_DE_a46d3e1400ce8c779c6fd41d7e0c</t>
+          <t>SER_DE_RKI_SURVSTAT_SOURCE_NATIVE</t>
+        </is>
+      </c>
+      <c r="V151" t="inlineStr">
+        <is>
+          <t>SER_DE_RKI_SURVSTAT_SOURCE_NATIVE</t>
+        </is>
+      </c>
+      <c r="W151" t="inlineStr">
+        <is>
+          <t>SRC_DE_RKI_SURVSTAT</t>
+        </is>
+      </c>
+      <c r="X151" t="inlineStr">
+        <is>
+          <t>__source_native__</t>
+        </is>
+      </c>
+      <c r="Y151" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z151" t="inlineStr">
+        <is>
+          <t>national_ifsG_notification_registry</t>
         </is>
       </c>
       <c r="AA151" t="inlineStr">
         <is>
-          <t>unknown</t>
-        </is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB151" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC151" t="inlineStr">
+        <is>
+          <t>country:DE:national</t>
+        </is>
+      </c>
+      <c r="AD151" t="inlineStr">
+        <is>
+          <t>sha256:d93dc9dc4f6141dbe5cd43d9314d102c906ca0e9ca38d971733bac05e6076158</t>
+        </is>
+      </c>
+      <c r="AE151" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF151" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG151" t="inlineStr">
+        <is>
+          <t>direct_only</t>
+        </is>
+      </c>
+      <c r="AH151" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI151" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ151" t="inlineStr">
+        <is>
+          <t>DE_RKI_SURVSTAT_source_native</t>
+        </is>
+      </c>
+      <c r="AK151" t="inlineStr">
+        <is>
+          <t>Source-native RKI SurvStat category. The original pathogen/category is retained in dimensions and is not automatically rolled up.</t>
+        </is>
+      </c>
+      <c r="AM151" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN151" t="b">
+        <v>0</v>
       </c>
       <c r="AO151" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>source_observations_only</t>
         </is>
       </c>
       <c r="AP151" t="inlineStr">
         <is>
-          <t>published_series</t>
-        </is>
-      </c>
-      <c r="AS151" t="inlineStr">
-        <is>
-          <t>HOLD_DE_a46d3e1400ce8c779c6fd41d7e0c</t>
-        </is>
-      </c>
+          <t>no_eligible_public_projection</t>
+        </is>
+      </c>
+      <c r="AQ151" t="inlineStr">
+        <is>
+          <t>source_observations_only</t>
+        </is>
+      </c>
+      <c r="AS151" t="inlineStr"/>
       <c r="AT151" t="n">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="AU151" t="inlineStr">
+        <is>
+          <t>Registered source observations are retained for provenance and downloads, but their measure is not eligible for the public cases curve.</t>
+        </is>
       </c>
       <c r="AV151" t="inlineStr">
         <is>
@@ -22480,12 +22572,12 @@
       </c>
       <c r="AX151" t="inlineStr">
         <is>
-          <t>https://survstat.rki.de/Content/Query/Main.aspx</t>
+          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
         </is>
       </c>
       <c r="AY151" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_webforms_csv_export</t>
         </is>
       </c>
       <c r="AZ151" t="inlineStr">
@@ -22500,12 +22592,12 @@
       </c>
       <c r="BB151" t="inlineStr">
         <is>
-          <t>https://survstat.rki.de/Content/Query/Main.aspx</t>
+          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
         </is>
       </c>
       <c r="BC151" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_webforms_csv_export</t>
         </is>
       </c>
     </row>
@@ -22537,12 +22629,12 @@
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>DE-HH</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Hamburg, Germany</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
@@ -22567,7 +22659,7 @@
       </c>
       <c r="L152" t="inlineStr">
         <is>
-          <t>2014-09-12</t>
+          <t>2014-09-08</t>
         </is>
       </c>
       <c r="M152" t="inlineStr">
@@ -22576,61 +22668,67 @@
         </is>
       </c>
       <c r="N152" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O152" t="n">
-        <v>0</v>
-      </c>
-      <c r="P152" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q152" t="n">
-        <v>0</v>
-      </c>
-      <c r="R152" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="S152" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
       </c>
       <c r="U152" t="inlineStr">
         <is>
-          <t>HOLD_JP_534554c6916adc005164f8ba7945</t>
+          <t>HOLD_DE_a46d3e1400ce8c779c6fd41d7e0c</t>
         </is>
       </c>
       <c r="AA152" t="inlineStr">
         <is>
-          <t>weekly</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="AO152" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP152" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ152" t="inlineStr">
+        <is>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS152" t="inlineStr">
         <is>
-          <t>HOLD_JP_534554c6916adc005164f8ba7945</t>
+          <t>HOLD_DE_a46d3e1400ce8c779c6fd41d7e0c</t>
         </is>
       </c>
       <c r="AT152" t="n">
         <v>1</v>
       </c>
+      <c r="AU152" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
       <c r="AV152" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>rki_survstat</t>
         </is>
       </c>
       <c r="AW152" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Germany RKI SurvStat 2.0</t>
         </is>
       </c>
       <c r="AX152" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://survstat.rki.de/Content/Query/Main.aspx</t>
         </is>
       </c>
       <c r="AY152" t="inlineStr">
@@ -22640,17 +22738,17 @@
       </c>
       <c r="AZ152" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>rki_survstat</t>
         </is>
       </c>
       <c r="BA152" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Germany RKI SurvStat 2.0</t>
         </is>
       </c>
       <c r="BB152" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://survstat.rki.de/Content/Query/Main.aspx</t>
         </is>
       </c>
       <c r="BC152" t="inlineStr">
@@ -22682,17 +22780,17 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>DE-HH</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Hamburg, Germany</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
@@ -22717,7 +22815,7 @@
       </c>
       <c r="L153" t="inlineStr">
         <is>
-          <t>2014-09-19</t>
+          <t>2014-09-08</t>
         </is>
       </c>
       <c r="M153" t="inlineStr">
@@ -22726,61 +22824,145 @@
         </is>
       </c>
       <c r="N153" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O153" t="n">
-        <v>0</v>
-      </c>
-      <c r="P153" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q153" t="n">
-        <v>0</v>
-      </c>
-      <c r="R153" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U153" t="inlineStr">
         <is>
-          <t>HOLD_JP_534554c6916adc005164f8ba7945</t>
+          <t>HOLD_DE_a46d3e1400ce8c779c6fd41d7e0c</t>
+        </is>
+      </c>
+      <c r="V153" t="inlineStr">
+        <is>
+          <t>ebolafieber</t>
+        </is>
+      </c>
+      <c r="W153" t="inlineStr">
+        <is>
+          <t>SRC_DE_RKI_SURVSTAT</t>
+        </is>
+      </c>
+      <c r="X153" t="inlineStr">
+        <is>
+          <t>Ebolafieber</t>
+        </is>
+      </c>
+      <c r="Y153" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z153" t="inlineStr">
+        <is>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA153" t="inlineStr">
         <is>
-          <t>weekly</t>
-        </is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AB153" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC153" t="inlineStr">
+        <is>
+          <t>country:DE-HH:national</t>
+        </is>
+      </c>
+      <c r="AD153" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE153" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF153" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG153" t="inlineStr">
+        <is>
+          <t>direct_only</t>
+        </is>
+      </c>
+      <c r="AH153" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI153" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ153" t="inlineStr">
+        <is>
+          <t>source-current</t>
+        </is>
+      </c>
+      <c r="AL153" t="inlineStr">
+        <is>
+          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
+        </is>
+      </c>
+      <c r="AM153" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN153" t="b">
+        <v>1</v>
       </c>
       <c r="AO153" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP153" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ153" t="inlineStr">
+        <is>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS153" t="inlineStr">
         <is>
-          <t>HOLD_JP_534554c6916adc005164f8ba7945</t>
+          <t>HOLD_DE_a46d3e1400ce8c779c6fd41d7e0c</t>
         </is>
       </c>
       <c r="AT153" t="n">
         <v>1</v>
       </c>
+      <c r="AU153" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
       <c r="AV153" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>rki_survstat</t>
         </is>
       </c>
       <c r="AW153" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Germany RKI SurvStat 2.0</t>
         </is>
       </c>
       <c r="AX153" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://survstat.rki.de/Content/Query/Main.aspx</t>
         </is>
       </c>
       <c r="AY153" t="inlineStr">
@@ -22790,17 +22972,17 @@
       </c>
       <c r="AZ153" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>rki_survstat</t>
         </is>
       </c>
       <c r="BA153" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Germany RKI SurvStat 2.0</t>
         </is>
       </c>
       <c r="BB153" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://survstat.rki.de/Content/Query/Main.aspx</t>
         </is>
       </c>
       <c r="BC153" t="inlineStr">
@@ -22867,7 +23049,7 @@
       </c>
       <c r="L154" t="inlineStr">
         <is>
-          <t>2014-09-26</t>
+          <t>2014-09-12</t>
         </is>
       </c>
       <c r="M154" t="inlineStr">
@@ -22987,12 +23169,12 @@
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>DE-HE</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Hessen, Germany</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
@@ -23017,7 +23199,7 @@
       </c>
       <c r="L155" t="inlineStr">
         <is>
-          <t>2014-09-29</t>
+          <t>2014-09-19</t>
         </is>
       </c>
       <c r="M155" t="inlineStr">
@@ -23026,24 +23208,33 @@
         </is>
       </c>
       <c r="N155" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O155" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="P155" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q155" t="n">
+        <v>0</v>
+      </c>
+      <c r="R155" t="n">
+        <v>0</v>
       </c>
       <c r="U155" t="inlineStr">
         <is>
-          <t>HOLD_DE_a46d3e1400ce8c779c6fd41d7e0c</t>
+          <t>HOLD_JP_534554c6916adc005164f8ba7945</t>
         </is>
       </c>
       <c r="AA155" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO155" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP155" t="inlineStr">
@@ -23053,7 +23244,7 @@
       </c>
       <c r="AS155" t="inlineStr">
         <is>
-          <t>HOLD_DE_a46d3e1400ce8c779c6fd41d7e0c</t>
+          <t>HOLD_JP_534554c6916adc005164f8ba7945</t>
         </is>
       </c>
       <c r="AT155" t="n">
@@ -23061,17 +23252,17 @@
       </c>
       <c r="AV155" t="inlineStr">
         <is>
-          <t>rki_survstat</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW155" t="inlineStr">
         <is>
-          <t>Germany RKI SurvStat 2.0</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX155" t="inlineStr">
         <is>
-          <t>https://survstat.rki.de/Content/Query/Main.aspx</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY155" t="inlineStr">
@@ -23081,17 +23272,17 @@
       </c>
       <c r="AZ155" t="inlineStr">
         <is>
-          <t>rki_survstat</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA155" t="inlineStr">
         <is>
-          <t>Germany RKI SurvStat 2.0</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB155" t="inlineStr">
         <is>
-          <t>https://survstat.rki.de/Content/Query/Main.aspx</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC155" t="inlineStr">
@@ -23128,12 +23319,12 @@
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
@@ -23158,12 +23349,12 @@
       </c>
       <c r="L156" t="inlineStr">
         <is>
-          <t>2014-10-01</t>
+          <t>2014-09-26</t>
         </is>
       </c>
       <c r="M156" t="inlineStr">
         <is>
-          <t>2014-10</t>
+          <t>2014-09</t>
         </is>
       </c>
       <c r="N156" t="n">
@@ -23172,17 +23363,28 @@
       <c r="O156" t="n">
         <v>0</v>
       </c>
+      <c r="P156" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q156" t="n">
+        <v>0</v>
+      </c>
       <c r="R156" t="n">
         <v>0</v>
       </c>
+      <c r="U156" t="inlineStr">
+        <is>
+          <t>HOLD_JP_534554c6916adc005164f8ba7945</t>
+        </is>
+      </c>
       <c r="AA156" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO156" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP156" t="inlineStr">
@@ -23190,48 +23392,52 @@
           <t>published_series</t>
         </is>
       </c>
-      <c r="AS156" t="inlineStr"/>
+      <c r="AS156" t="inlineStr">
+        <is>
+          <t>HOLD_JP_534554c6916adc005164f8ba7945</t>
+        </is>
+      </c>
       <c r="AT156" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AV156" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW156" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX156" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY156" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ156" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA156" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB156" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC156" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -23258,17 +23464,17 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
@@ -23293,32 +23499,51 @@
       </c>
       <c r="L157" t="inlineStr">
         <is>
-          <t>2014-10-03</t>
+          <t>2014-09-29</t>
         </is>
       </c>
       <c r="M157" t="inlineStr">
         <is>
-          <t>2014-10</t>
+          <t>2014-09</t>
         </is>
       </c>
       <c r="N157" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O157" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P157" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q157" t="n">
-        <v>0</v>
-      </c>
-      <c r="R157" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U157" t="inlineStr">
         <is>
-          <t>HOLD_JP_534554c6916adc005164f8ba7945</t>
+          <t>SER_DE_RKI_SURVSTAT_SOURCE_NATIVE</t>
+        </is>
+      </c>
+      <c r="V157" t="inlineStr">
+        <is>
+          <t>SER_DE_RKI_SURVSTAT_SOURCE_NATIVE</t>
+        </is>
+      </c>
+      <c r="W157" t="inlineStr">
+        <is>
+          <t>SRC_DE_RKI_SURVSTAT</t>
+        </is>
+      </c>
+      <c r="X157" t="inlineStr">
+        <is>
+          <t>__source_native__</t>
+        </is>
+      </c>
+      <c r="Y157" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z157" t="inlineStr">
+        <is>
+          <t>national_ifsG_notification_registry</t>
         </is>
       </c>
       <c r="AA157" t="inlineStr">
@@ -23326,62 +23551,126 @@
           <t>weekly</t>
         </is>
       </c>
+      <c r="AB157" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC157" t="inlineStr">
+        <is>
+          <t>country:DE:national</t>
+        </is>
+      </c>
+      <c r="AD157" t="inlineStr">
+        <is>
+          <t>sha256:d93dc9dc4f6141dbe5cd43d9314d102c906ca0e9ca38d971733bac05e6076158</t>
+        </is>
+      </c>
+      <c r="AE157" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF157" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG157" t="inlineStr">
+        <is>
+          <t>direct_only</t>
+        </is>
+      </c>
+      <c r="AH157" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI157" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ157" t="inlineStr">
+        <is>
+          <t>DE_RKI_SURVSTAT_source_native</t>
+        </is>
+      </c>
+      <c r="AK157" t="inlineStr">
+        <is>
+          <t>Source-native RKI SurvStat category. The original pathogen/category is retained in dimensions and is not automatically rolled up.</t>
+        </is>
+      </c>
+      <c r="AM157" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN157" t="b">
+        <v>0</v>
+      </c>
       <c r="AO157" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>source_observations_only</t>
         </is>
       </c>
       <c r="AP157" t="inlineStr">
         <is>
-          <t>published_series</t>
-        </is>
-      </c>
-      <c r="AS157" t="inlineStr">
-        <is>
-          <t>HOLD_JP_534554c6916adc005164f8ba7945</t>
-        </is>
-      </c>
+          <t>no_eligible_public_projection</t>
+        </is>
+      </c>
+      <c r="AQ157" t="inlineStr">
+        <is>
+          <t>source_observations_only</t>
+        </is>
+      </c>
+      <c r="AS157" t="inlineStr"/>
       <c r="AT157" t="n">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="AU157" t="inlineStr">
+        <is>
+          <t>Registered source observations are retained for provenance and downloads, but their measure is not eligible for the public cases curve.</t>
+        </is>
       </c>
       <c r="AV157" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>rki_survstat</t>
         </is>
       </c>
       <c r="AW157" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Germany RKI SurvStat 2.0</t>
         </is>
       </c>
       <c r="AX157" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
         </is>
       </c>
       <c r="AY157" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_webforms_csv_export</t>
         </is>
       </c>
       <c r="AZ157" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>rki_survstat</t>
         </is>
       </c>
       <c r="BA157" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Germany RKI SurvStat 2.0</t>
         </is>
       </c>
       <c r="BB157" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
         </is>
       </c>
       <c r="BC157" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_webforms_csv_export</t>
         </is>
       </c>
     </row>
@@ -23413,12 +23702,12 @@
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>DE-SN</t>
+          <t>DE-HE</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Sachsen, Germany</t>
+          <t>Hessen, Germany</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
@@ -23443,12 +23732,12 @@
       </c>
       <c r="L158" t="inlineStr">
         <is>
-          <t>2014-10-06</t>
+          <t>2014-09-29</t>
         </is>
       </c>
       <c r="M158" t="inlineStr">
         <is>
-          <t>2014-10</t>
+          <t>2014-09</t>
         </is>
       </c>
       <c r="N158" t="n">
@@ -23457,6 +23746,11 @@
       <c r="O158" t="n">
         <v>1</v>
       </c>
+      <c r="S158" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="U158" t="inlineStr">
         <is>
           <t>HOLD_DE_a46d3e1400ce8c779c6fd41d7e0c</t>
@@ -23474,7 +23768,12 @@
       </c>
       <c r="AP158" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ158" t="inlineStr">
+        <is>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS158" t="inlineStr">
@@ -23484,6 +23783,11 @@
       </c>
       <c r="AT158" t="n">
         <v>1</v>
+      </c>
+      <c r="AU158" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
       </c>
       <c r="AV158" t="inlineStr">
         <is>
@@ -23549,17 +23853,17 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>DE-HE</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Hessen, Germany</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
@@ -23584,70 +23888,154 @@
       </c>
       <c r="L159" t="inlineStr">
         <is>
-          <t>2014-10-10</t>
+          <t>2014-09-29</t>
         </is>
       </c>
       <c r="M159" t="inlineStr">
         <is>
-          <t>2014-10</t>
+          <t>2014-09</t>
         </is>
       </c>
       <c r="N159" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O159" t="n">
-        <v>0</v>
-      </c>
-      <c r="P159" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q159" t="n">
-        <v>0</v>
-      </c>
-      <c r="R159" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U159" t="inlineStr">
         <is>
-          <t>HOLD_JP_534554c6916adc005164f8ba7945</t>
+          <t>HOLD_DE_a46d3e1400ce8c779c6fd41d7e0c</t>
+        </is>
+      </c>
+      <c r="V159" t="inlineStr">
+        <is>
+          <t>ebolafieber</t>
+        </is>
+      </c>
+      <c r="W159" t="inlineStr">
+        <is>
+          <t>SRC_DE_RKI_SURVSTAT</t>
+        </is>
+      </c>
+      <c r="X159" t="inlineStr">
+        <is>
+          <t>Ebolafieber</t>
+        </is>
+      </c>
+      <c r="Y159" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z159" t="inlineStr">
+        <is>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA159" t="inlineStr">
         <is>
-          <t>weekly</t>
-        </is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AB159" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC159" t="inlineStr">
+        <is>
+          <t>country:DE-HE:national</t>
+        </is>
+      </c>
+      <c r="AD159" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE159" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF159" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG159" t="inlineStr">
+        <is>
+          <t>direct_only</t>
+        </is>
+      </c>
+      <c r="AH159" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI159" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ159" t="inlineStr">
+        <is>
+          <t>source-current</t>
+        </is>
+      </c>
+      <c r="AL159" t="inlineStr">
+        <is>
+          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
+        </is>
+      </c>
+      <c r="AM159" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN159" t="b">
+        <v>1</v>
       </c>
       <c r="AO159" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP159" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ159" t="inlineStr">
+        <is>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS159" t="inlineStr">
         <is>
-          <t>HOLD_JP_534554c6916adc005164f8ba7945</t>
+          <t>HOLD_DE_a46d3e1400ce8c779c6fd41d7e0c</t>
         </is>
       </c>
       <c r="AT159" t="n">
         <v>1</v>
       </c>
+      <c r="AU159" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
       <c r="AV159" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>rki_survstat</t>
         </is>
       </c>
       <c r="AW159" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Germany RKI SurvStat 2.0</t>
         </is>
       </c>
       <c r="AX159" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://survstat.rki.de/Content/Query/Main.aspx</t>
         </is>
       </c>
       <c r="AY159" t="inlineStr">
@@ -23657,17 +24045,17 @@
       </c>
       <c r="AZ159" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>rki_survstat</t>
         </is>
       </c>
       <c r="BA159" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Germany RKI SurvStat 2.0</t>
         </is>
       </c>
       <c r="BB159" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://survstat.rki.de/Content/Query/Main.aspx</t>
         </is>
       </c>
       <c r="BC159" t="inlineStr">
@@ -23704,12 +24092,12 @@
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
@@ -23734,7 +24122,7 @@
       </c>
       <c r="L160" t="inlineStr">
         <is>
-          <t>2014-10-17</t>
+          <t>2014-10-01</t>
         </is>
       </c>
       <c r="M160" t="inlineStr">
@@ -23748,28 +24136,17 @@
       <c r="O160" t="n">
         <v>0</v>
       </c>
-      <c r="P160" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q160" t="n">
-        <v>0</v>
-      </c>
       <c r="R160" t="n">
         <v>0</v>
       </c>
-      <c r="U160" t="inlineStr">
-        <is>
-          <t>HOLD_JP_534554c6916adc005164f8ba7945</t>
-        </is>
-      </c>
       <c r="AA160" t="inlineStr">
         <is>
-          <t>weekly</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO160" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP160" t="inlineStr">
@@ -23777,52 +24154,48 @@
           <t>published_series</t>
         </is>
       </c>
-      <c r="AS160" t="inlineStr">
-        <is>
-          <t>HOLD_JP_534554c6916adc005164f8ba7945</t>
-        </is>
-      </c>
+      <c r="AS160" t="inlineStr"/>
       <c r="AT160" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AV160" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW160" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX160" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY160" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ160" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA160" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB160" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC160" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -23884,7 +24257,7 @@
       </c>
       <c r="L161" t="inlineStr">
         <is>
-          <t>2014-10-24</t>
+          <t>2014-10-03</t>
         </is>
       </c>
       <c r="M161" t="inlineStr">
@@ -23999,17 +24372,17 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
@@ -24034,7 +24407,7 @@
       </c>
       <c r="L162" t="inlineStr">
         <is>
-          <t>2014-10-31</t>
+          <t>2014-10-06</t>
         </is>
       </c>
       <c r="M162" t="inlineStr">
@@ -24043,23 +24416,42 @@
         </is>
       </c>
       <c r="N162" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O162" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P162" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q162" t="n">
-        <v>0</v>
-      </c>
-      <c r="R162" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U162" t="inlineStr">
         <is>
-          <t>HOLD_JP_534554c6916adc005164f8ba7945</t>
+          <t>SER_DE_RKI_SURVSTAT_SOURCE_NATIVE</t>
+        </is>
+      </c>
+      <c r="V162" t="inlineStr">
+        <is>
+          <t>SER_DE_RKI_SURVSTAT_SOURCE_NATIVE</t>
+        </is>
+      </c>
+      <c r="W162" t="inlineStr">
+        <is>
+          <t>SRC_DE_RKI_SURVSTAT</t>
+        </is>
+      </c>
+      <c r="X162" t="inlineStr">
+        <is>
+          <t>__source_native__</t>
+        </is>
+      </c>
+      <c r="Y162" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z162" t="inlineStr">
+        <is>
+          <t>national_ifsG_notification_registry</t>
         </is>
       </c>
       <c r="AA162" t="inlineStr">
@@ -24067,62 +24459,126 @@
           <t>weekly</t>
         </is>
       </c>
+      <c r="AB162" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC162" t="inlineStr">
+        <is>
+          <t>country:DE:national</t>
+        </is>
+      </c>
+      <c r="AD162" t="inlineStr">
+        <is>
+          <t>sha256:d93dc9dc4f6141dbe5cd43d9314d102c906ca0e9ca38d971733bac05e6076158</t>
+        </is>
+      </c>
+      <c r="AE162" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF162" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG162" t="inlineStr">
+        <is>
+          <t>direct_only</t>
+        </is>
+      </c>
+      <c r="AH162" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI162" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ162" t="inlineStr">
+        <is>
+          <t>DE_RKI_SURVSTAT_source_native</t>
+        </is>
+      </c>
+      <c r="AK162" t="inlineStr">
+        <is>
+          <t>Source-native RKI SurvStat category. The original pathogen/category is retained in dimensions and is not automatically rolled up.</t>
+        </is>
+      </c>
+      <c r="AM162" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN162" t="b">
+        <v>0</v>
+      </c>
       <c r="AO162" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>source_observations_only</t>
         </is>
       </c>
       <c r="AP162" t="inlineStr">
         <is>
-          <t>published_series</t>
-        </is>
-      </c>
-      <c r="AS162" t="inlineStr">
-        <is>
-          <t>HOLD_JP_534554c6916adc005164f8ba7945</t>
-        </is>
-      </c>
+          <t>no_eligible_public_projection</t>
+        </is>
+      </c>
+      <c r="AQ162" t="inlineStr">
+        <is>
+          <t>source_observations_only</t>
+        </is>
+      </c>
+      <c r="AS162" t="inlineStr"/>
       <c r="AT162" t="n">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="AU162" t="inlineStr">
+        <is>
+          <t>Registered source observations are retained for provenance and downloads, but their measure is not eligible for the public cases curve.</t>
+        </is>
       </c>
       <c r="AV162" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>rki_survstat</t>
         </is>
       </c>
       <c r="AW162" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Germany RKI SurvStat 2.0</t>
         </is>
       </c>
       <c r="AX162" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
         </is>
       </c>
       <c r="AY162" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_webforms_csv_export</t>
         </is>
       </c>
       <c r="AZ162" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>rki_survstat</t>
         </is>
       </c>
       <c r="BA162" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Germany RKI SurvStat 2.0</t>
         </is>
       </c>
       <c r="BB162" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
         </is>
       </c>
       <c r="BC162" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_webforms_csv_export</t>
         </is>
       </c>
     </row>
@@ -24154,12 +24610,12 @@
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>DE-SN</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Sachsen, Germany</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
@@ -24184,80 +24640,101 @@
       </c>
       <c r="L163" t="inlineStr">
         <is>
-          <t>2014-11-01</t>
+          <t>2014-10-06</t>
         </is>
       </c>
       <c r="M163" t="inlineStr">
         <is>
-          <t>2014-11</t>
+          <t>2014-10</t>
         </is>
       </c>
       <c r="N163" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O163" t="n">
-        <v>0</v>
-      </c>
-      <c r="R163" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="S163" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="U163" t="inlineStr">
+        <is>
+          <t>HOLD_DE_a46d3e1400ce8c779c6fd41d7e0c</t>
+        </is>
       </c>
       <c r="AA163" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="AO163" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP163" t="inlineStr">
         <is>
-          <t>published_series</t>
-        </is>
-      </c>
-      <c r="AS163" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ163" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS163" t="inlineStr">
+        <is>
+          <t>HOLD_DE_a46d3e1400ce8c779c6fd41d7e0c</t>
+        </is>
+      </c>
       <c r="AT163" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="AU163" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
       </c>
       <c r="AV163" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>rki_survstat</t>
         </is>
       </c>
       <c r="AW163" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Germany RKI SurvStat 2.0</t>
         </is>
       </c>
       <c r="AX163" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://survstat.rki.de/Content/Query/Main.aspx</t>
         </is>
       </c>
       <c r="AY163" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ163" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>rki_survstat</t>
         </is>
       </c>
       <c r="BA163" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Germany RKI SurvStat 2.0</t>
         </is>
       </c>
       <c r="BB163" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://survstat.rki.de/Content/Query/Main.aspx</t>
         </is>
       </c>
       <c r="BC163" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -24284,17 +24761,17 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>DE-SN</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Sachsen, Germany</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
@@ -24319,70 +24796,154 @@
       </c>
       <c r="L164" t="inlineStr">
         <is>
-          <t>2014-11-07</t>
+          <t>2014-10-06</t>
         </is>
       </c>
       <c r="M164" t="inlineStr">
         <is>
-          <t>2014-11</t>
+          <t>2014-10</t>
         </is>
       </c>
       <c r="N164" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O164" t="n">
-        <v>0</v>
-      </c>
-      <c r="P164" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q164" t="n">
-        <v>0</v>
-      </c>
-      <c r="R164" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U164" t="inlineStr">
         <is>
-          <t>HOLD_JP_534554c6916adc005164f8ba7945</t>
+          <t>HOLD_DE_a46d3e1400ce8c779c6fd41d7e0c</t>
+        </is>
+      </c>
+      <c r="V164" t="inlineStr">
+        <is>
+          <t>ebolafieber</t>
+        </is>
+      </c>
+      <c r="W164" t="inlineStr">
+        <is>
+          <t>SRC_DE_RKI_SURVSTAT</t>
+        </is>
+      </c>
+      <c r="X164" t="inlineStr">
+        <is>
+          <t>Ebolafieber</t>
+        </is>
+      </c>
+      <c r="Y164" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z164" t="inlineStr">
+        <is>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA164" t="inlineStr">
         <is>
-          <t>weekly</t>
-        </is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AB164" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC164" t="inlineStr">
+        <is>
+          <t>country:DE-SN:national</t>
+        </is>
+      </c>
+      <c r="AD164" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE164" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF164" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG164" t="inlineStr">
+        <is>
+          <t>direct_only</t>
+        </is>
+      </c>
+      <c r="AH164" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI164" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ164" t="inlineStr">
+        <is>
+          <t>source-current</t>
+        </is>
+      </c>
+      <c r="AL164" t="inlineStr">
+        <is>
+          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
+        </is>
+      </c>
+      <c r="AM164" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN164" t="b">
+        <v>1</v>
       </c>
       <c r="AO164" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP164" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ164" t="inlineStr">
+        <is>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS164" t="inlineStr">
         <is>
-          <t>HOLD_JP_534554c6916adc005164f8ba7945</t>
+          <t>HOLD_DE_a46d3e1400ce8c779c6fd41d7e0c</t>
         </is>
       </c>
       <c r="AT164" t="n">
         <v>1</v>
       </c>
+      <c r="AU164" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
       <c r="AV164" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>rki_survstat</t>
         </is>
       </c>
       <c r="AW164" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Germany RKI SurvStat 2.0</t>
         </is>
       </c>
       <c r="AX164" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://survstat.rki.de/Content/Query/Main.aspx</t>
         </is>
       </c>
       <c r="AY164" t="inlineStr">
@@ -24392,17 +24953,17 @@
       </c>
       <c r="AZ164" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>rki_survstat</t>
         </is>
       </c>
       <c r="BA164" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Germany RKI SurvStat 2.0</t>
         </is>
       </c>
       <c r="BB164" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://survstat.rki.de/Content/Query/Main.aspx</t>
         </is>
       </c>
       <c r="BC164" t="inlineStr">
@@ -24469,12 +25030,12 @@
       </c>
       <c r="L165" t="inlineStr">
         <is>
-          <t>2014-11-14</t>
+          <t>2014-10-10</t>
         </is>
       </c>
       <c r="M165" t="inlineStr">
         <is>
-          <t>2014-11</t>
+          <t>2014-10</t>
         </is>
       </c>
       <c r="N165" t="n">
@@ -24619,12 +25180,12 @@
       </c>
       <c r="L166" t="inlineStr">
         <is>
-          <t>2014-11-21</t>
+          <t>2014-10-17</t>
         </is>
       </c>
       <c r="M166" t="inlineStr">
         <is>
-          <t>2014-11</t>
+          <t>2014-10</t>
         </is>
       </c>
       <c r="N166" t="n">
@@ -24769,12 +25330,12 @@
       </c>
       <c r="L167" t="inlineStr">
         <is>
-          <t>2014-11-28</t>
+          <t>2014-10-24</t>
         </is>
       </c>
       <c r="M167" t="inlineStr">
         <is>
-          <t>2014-11</t>
+          <t>2014-10</t>
         </is>
       </c>
       <c r="N167" t="n">
@@ -24889,12 +25450,12 @@
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
@@ -24919,12 +25480,12 @@
       </c>
       <c r="L168" t="inlineStr">
         <is>
-          <t>2014-12-01</t>
+          <t>2014-10-31</t>
         </is>
       </c>
       <c r="M168" t="inlineStr">
         <is>
-          <t>2014-12</t>
+          <t>2014-10</t>
         </is>
       </c>
       <c r="N168" t="n">
@@ -24933,17 +25494,28 @@
       <c r="O168" t="n">
         <v>0</v>
       </c>
+      <c r="P168" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q168" t="n">
+        <v>0</v>
+      </c>
       <c r="R168" t="n">
         <v>0</v>
       </c>
+      <c r="U168" t="inlineStr">
+        <is>
+          <t>HOLD_JP_534554c6916adc005164f8ba7945</t>
+        </is>
+      </c>
       <c r="AA168" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO168" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP168" t="inlineStr">
@@ -24951,48 +25523,52 @@
           <t>published_series</t>
         </is>
       </c>
-      <c r="AS168" t="inlineStr"/>
+      <c r="AS168" t="inlineStr">
+        <is>
+          <t>HOLD_JP_534554c6916adc005164f8ba7945</t>
+        </is>
+      </c>
       <c r="AT168" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AV168" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW168" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX168" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY168" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ168" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA168" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB168" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC168" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -25024,12 +25600,12 @@
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
@@ -25054,12 +25630,12 @@
       </c>
       <c r="L169" t="inlineStr">
         <is>
-          <t>2014-12-05</t>
+          <t>2014-11-01</t>
         </is>
       </c>
       <c r="M169" t="inlineStr">
         <is>
-          <t>2014-12</t>
+          <t>2014-11</t>
         </is>
       </c>
       <c r="N169" t="n">
@@ -25068,28 +25644,17 @@
       <c r="O169" t="n">
         <v>0</v>
       </c>
-      <c r="P169" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q169" t="n">
-        <v>0</v>
-      </c>
       <c r="R169" t="n">
         <v>0</v>
       </c>
-      <c r="U169" t="inlineStr">
-        <is>
-          <t>HOLD_JP_534554c6916adc005164f8ba7945</t>
-        </is>
-      </c>
       <c r="AA169" t="inlineStr">
         <is>
-          <t>weekly</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO169" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP169" t="inlineStr">
@@ -25097,52 +25662,48 @@
           <t>published_series</t>
         </is>
       </c>
-      <c r="AS169" t="inlineStr">
-        <is>
-          <t>HOLD_JP_534554c6916adc005164f8ba7945</t>
-        </is>
-      </c>
+      <c r="AS169" t="inlineStr"/>
       <c r="AT169" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AV169" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW169" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX169" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY169" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ169" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA169" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB169" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC169" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -25204,12 +25765,12 @@
       </c>
       <c r="L170" t="inlineStr">
         <is>
-          <t>2014-12-12</t>
+          <t>2014-11-07</t>
         </is>
       </c>
       <c r="M170" t="inlineStr">
         <is>
-          <t>2014-12</t>
+          <t>2014-11</t>
         </is>
       </c>
       <c r="N170" t="n">
@@ -25354,12 +25915,12 @@
       </c>
       <c r="L171" t="inlineStr">
         <is>
-          <t>2014-12-19</t>
+          <t>2014-11-14</t>
         </is>
       </c>
       <c r="M171" t="inlineStr">
         <is>
-          <t>2014-12</t>
+          <t>2014-11</t>
         </is>
       </c>
       <c r="N171" t="n">
@@ -25504,12 +26065,12 @@
       </c>
       <c r="L172" t="inlineStr">
         <is>
-          <t>2014-12-26</t>
+          <t>2014-11-21</t>
         </is>
       </c>
       <c r="M172" t="inlineStr">
         <is>
-          <t>2014-12</t>
+          <t>2014-11</t>
         </is>
       </c>
       <c r="N172" t="n">
@@ -25591,6 +26152,891 @@
         </is>
       </c>
       <c r="BC172" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>D050</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>ebola</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>Ebola</t>
+        </is>
+      </c>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F173" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G173" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H173" t="inlineStr">
+        <is>
+          <t>D050</t>
+        </is>
+      </c>
+      <c r="I173" t="inlineStr">
+        <is>
+          <t>Ebola</t>
+        </is>
+      </c>
+      <c r="J173" t="inlineStr">
+        <is>
+          <t>埃博拉出血热</t>
+        </is>
+      </c>
+      <c r="K173" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L173" t="inlineStr">
+        <is>
+          <t>2014-11-28</t>
+        </is>
+      </c>
+      <c r="M173" t="inlineStr">
+        <is>
+          <t>2014-11</t>
+        </is>
+      </c>
+      <c r="N173" t="n">
+        <v>0</v>
+      </c>
+      <c r="O173" t="n">
+        <v>0</v>
+      </c>
+      <c r="P173" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q173" t="n">
+        <v>0</v>
+      </c>
+      <c r="R173" t="n">
+        <v>0</v>
+      </c>
+      <c r="U173" t="inlineStr">
+        <is>
+          <t>HOLD_JP_534554c6916adc005164f8ba7945</t>
+        </is>
+      </c>
+      <c r="AA173" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO173" t="inlineStr">
+        <is>
+          <t>mixed</t>
+        </is>
+      </c>
+      <c r="AP173" t="inlineStr">
+        <is>
+          <t>published_series</t>
+        </is>
+      </c>
+      <c r="AS173" t="inlineStr">
+        <is>
+          <t>HOLD_JP_534554c6916adc005164f8ba7945</t>
+        </is>
+      </c>
+      <c r="AT173" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV173" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW173" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX173" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY173" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ173" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA173" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB173" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC173" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>D050</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>ebola</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>Ebola</t>
+        </is>
+      </c>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F174" t="inlineStr">
+        <is>
+          <t>KR</t>
+        </is>
+      </c>
+      <c r="G174" t="inlineStr">
+        <is>
+          <t>South Korea</t>
+        </is>
+      </c>
+      <c r="H174" t="inlineStr">
+        <is>
+          <t>D050</t>
+        </is>
+      </c>
+      <c r="I174" t="inlineStr">
+        <is>
+          <t>Ebola</t>
+        </is>
+      </c>
+      <c r="J174" t="inlineStr">
+        <is>
+          <t>埃博拉出血热</t>
+        </is>
+      </c>
+      <c r="K174" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L174" t="inlineStr">
+        <is>
+          <t>2014-12-01</t>
+        </is>
+      </c>
+      <c r="M174" t="inlineStr">
+        <is>
+          <t>2014-12</t>
+        </is>
+      </c>
+      <c r="N174" t="n">
+        <v>0</v>
+      </c>
+      <c r="O174" t="n">
+        <v>0</v>
+      </c>
+      <c r="R174" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA174" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO174" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP174" t="inlineStr">
+        <is>
+          <t>published_series</t>
+        </is>
+      </c>
+      <c r="AS174" t="inlineStr"/>
+      <c r="AT174" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV174" t="inlineStr">
+        <is>
+          <t>kdca_open_api</t>
+        </is>
+      </c>
+      <c r="AW174" t="inlineStr">
+        <is>
+          <t>Korea KDCA EID</t>
+        </is>
+      </c>
+      <c r="AX174" t="inlineStr">
+        <is>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+        </is>
+      </c>
+      <c r="AY174" t="inlineStr">
+        <is>
+          <t>open_api_or_portal_download</t>
+        </is>
+      </c>
+      <c r="AZ174" t="inlineStr">
+        <is>
+          <t>kdca_open_api</t>
+        </is>
+      </c>
+      <c r="BA174" t="inlineStr">
+        <is>
+          <t>Korea KDCA EID</t>
+        </is>
+      </c>
+      <c r="BB174" t="inlineStr">
+        <is>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+        </is>
+      </c>
+      <c r="BC174" t="inlineStr">
+        <is>
+          <t>open_api_or_portal_download</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>D050</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>ebola</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>Ebola</t>
+        </is>
+      </c>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F175" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G175" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H175" t="inlineStr">
+        <is>
+          <t>D050</t>
+        </is>
+      </c>
+      <c r="I175" t="inlineStr">
+        <is>
+          <t>Ebola</t>
+        </is>
+      </c>
+      <c r="J175" t="inlineStr">
+        <is>
+          <t>埃博拉出血热</t>
+        </is>
+      </c>
+      <c r="K175" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L175" t="inlineStr">
+        <is>
+          <t>2014-12-05</t>
+        </is>
+      </c>
+      <c r="M175" t="inlineStr">
+        <is>
+          <t>2014-12</t>
+        </is>
+      </c>
+      <c r="N175" t="n">
+        <v>0</v>
+      </c>
+      <c r="O175" t="n">
+        <v>0</v>
+      </c>
+      <c r="P175" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q175" t="n">
+        <v>0</v>
+      </c>
+      <c r="R175" t="n">
+        <v>0</v>
+      </c>
+      <c r="U175" t="inlineStr">
+        <is>
+          <t>HOLD_JP_534554c6916adc005164f8ba7945</t>
+        </is>
+      </c>
+      <c r="AA175" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO175" t="inlineStr">
+        <is>
+          <t>mixed</t>
+        </is>
+      </c>
+      <c r="AP175" t="inlineStr">
+        <is>
+          <t>published_series</t>
+        </is>
+      </c>
+      <c r="AS175" t="inlineStr">
+        <is>
+          <t>HOLD_JP_534554c6916adc005164f8ba7945</t>
+        </is>
+      </c>
+      <c r="AT175" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV175" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW175" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX175" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY175" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ175" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA175" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB175" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC175" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>D050</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>ebola</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>Ebola</t>
+        </is>
+      </c>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F176" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G176" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H176" t="inlineStr">
+        <is>
+          <t>D050</t>
+        </is>
+      </c>
+      <c r="I176" t="inlineStr">
+        <is>
+          <t>Ebola</t>
+        </is>
+      </c>
+      <c r="J176" t="inlineStr">
+        <is>
+          <t>埃博拉出血热</t>
+        </is>
+      </c>
+      <c r="K176" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L176" t="inlineStr">
+        <is>
+          <t>2014-12-12</t>
+        </is>
+      </c>
+      <c r="M176" t="inlineStr">
+        <is>
+          <t>2014-12</t>
+        </is>
+      </c>
+      <c r="N176" t="n">
+        <v>0</v>
+      </c>
+      <c r="O176" t="n">
+        <v>0</v>
+      </c>
+      <c r="P176" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q176" t="n">
+        <v>0</v>
+      </c>
+      <c r="R176" t="n">
+        <v>0</v>
+      </c>
+      <c r="U176" t="inlineStr">
+        <is>
+          <t>HOLD_JP_534554c6916adc005164f8ba7945</t>
+        </is>
+      </c>
+      <c r="AA176" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO176" t="inlineStr">
+        <is>
+          <t>mixed</t>
+        </is>
+      </c>
+      <c r="AP176" t="inlineStr">
+        <is>
+          <t>published_series</t>
+        </is>
+      </c>
+      <c r="AS176" t="inlineStr">
+        <is>
+          <t>HOLD_JP_534554c6916adc005164f8ba7945</t>
+        </is>
+      </c>
+      <c r="AT176" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV176" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW176" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX176" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY176" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ176" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA176" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB176" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC176" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>D050</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>ebola</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>Ebola</t>
+        </is>
+      </c>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F177" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G177" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H177" t="inlineStr">
+        <is>
+          <t>D050</t>
+        </is>
+      </c>
+      <c r="I177" t="inlineStr">
+        <is>
+          <t>Ebola</t>
+        </is>
+      </c>
+      <c r="J177" t="inlineStr">
+        <is>
+          <t>埃博拉出血热</t>
+        </is>
+      </c>
+      <c r="K177" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L177" t="inlineStr">
+        <is>
+          <t>2014-12-19</t>
+        </is>
+      </c>
+      <c r="M177" t="inlineStr">
+        <is>
+          <t>2014-12</t>
+        </is>
+      </c>
+      <c r="N177" t="n">
+        <v>0</v>
+      </c>
+      <c r="O177" t="n">
+        <v>0</v>
+      </c>
+      <c r="P177" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q177" t="n">
+        <v>0</v>
+      </c>
+      <c r="R177" t="n">
+        <v>0</v>
+      </c>
+      <c r="U177" t="inlineStr">
+        <is>
+          <t>HOLD_JP_534554c6916adc005164f8ba7945</t>
+        </is>
+      </c>
+      <c r="AA177" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO177" t="inlineStr">
+        <is>
+          <t>mixed</t>
+        </is>
+      </c>
+      <c r="AP177" t="inlineStr">
+        <is>
+          <t>published_series</t>
+        </is>
+      </c>
+      <c r="AS177" t="inlineStr">
+        <is>
+          <t>HOLD_JP_534554c6916adc005164f8ba7945</t>
+        </is>
+      </c>
+      <c r="AT177" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV177" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW177" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX177" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY177" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ177" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA177" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB177" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC177" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>D050</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>ebola</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>Ebola</t>
+        </is>
+      </c>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F178" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G178" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H178" t="inlineStr">
+        <is>
+          <t>D050</t>
+        </is>
+      </c>
+      <c r="I178" t="inlineStr">
+        <is>
+          <t>Ebola</t>
+        </is>
+      </c>
+      <c r="J178" t="inlineStr">
+        <is>
+          <t>埃博拉出血热</t>
+        </is>
+      </c>
+      <c r="K178" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L178" t="inlineStr">
+        <is>
+          <t>2014-12-26</t>
+        </is>
+      </c>
+      <c r="M178" t="inlineStr">
+        <is>
+          <t>2014-12</t>
+        </is>
+      </c>
+      <c r="N178" t="n">
+        <v>0</v>
+      </c>
+      <c r="O178" t="n">
+        <v>0</v>
+      </c>
+      <c r="P178" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q178" t="n">
+        <v>0</v>
+      </c>
+      <c r="R178" t="n">
+        <v>0</v>
+      </c>
+      <c r="U178" t="inlineStr">
+        <is>
+          <t>HOLD_JP_534554c6916adc005164f8ba7945</t>
+        </is>
+      </c>
+      <c r="AA178" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO178" t="inlineStr">
+        <is>
+          <t>mixed</t>
+        </is>
+      </c>
+      <c r="AP178" t="inlineStr">
+        <is>
+          <t>published_series</t>
+        </is>
+      </c>
+      <c r="AS178" t="inlineStr">
+        <is>
+          <t>HOLD_JP_534554c6916adc005164f8ba7945</t>
+        </is>
+      </c>
+      <c r="AT178" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV178" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW178" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX178" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY178" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ178" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA178" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB178" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC178" t="inlineStr">
         <is>
           <t>web</t>
         </is>
@@ -25722,7 +27168,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>171</v>
+        <v>177</v>
       </c>
     </row>
     <row r="11">
@@ -25742,7 +27188,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="13">
@@ -25752,7 +27198,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14">

--- a/diseases/d050/2010-2014.xlsx
+++ b/diseases/d050/2010-2014.xlsx
@@ -768,6 +768,11 @@
       <c r="R2" t="n">
         <v>0</v>
       </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -780,12 +785,22 @@
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR2" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr"/>
       <c r="AT2" t="n">
         <v>0</v>
+      </c>
+      <c r="AU2" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV2" t="inlineStr">
         <is>
@@ -903,6 +918,11 @@
       <c r="R3" t="n">
         <v>0</v>
       </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -915,12 +935,22 @@
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR3" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr"/>
       <c r="AT3" t="n">
         <v>0</v>
+      </c>
+      <c r="AU3" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV3" t="inlineStr">
         <is>
@@ -1038,6 +1068,11 @@
       <c r="R4" t="n">
         <v>0</v>
       </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1050,12 +1085,22 @@
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR4" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr"/>
       <c r="AT4" t="n">
         <v>0</v>
+      </c>
+      <c r="AU4" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV4" t="inlineStr">
         <is>
@@ -1173,6 +1218,11 @@
       <c r="R5" t="n">
         <v>0</v>
       </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1185,12 +1235,22 @@
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR5" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr"/>
       <c r="AT5" t="n">
         <v>0</v>
+      </c>
+      <c r="AU5" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV5" t="inlineStr">
         <is>
@@ -1308,6 +1368,11 @@
       <c r="R6" t="n">
         <v>0</v>
       </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1320,12 +1385,22 @@
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR6" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr"/>
       <c r="AT6" t="n">
         <v>0</v>
+      </c>
+      <c r="AU6" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV6" t="inlineStr">
         <is>
@@ -1443,6 +1518,11 @@
       <c r="R7" t="n">
         <v>0</v>
       </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1455,12 +1535,22 @@
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR7" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr"/>
       <c r="AT7" t="n">
         <v>0</v>
+      </c>
+      <c r="AU7" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV7" t="inlineStr">
         <is>
@@ -1578,6 +1668,11 @@
       <c r="R8" t="n">
         <v>0</v>
       </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1590,12 +1685,22 @@
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR8" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr"/>
       <c r="AT8" t="n">
         <v>0</v>
+      </c>
+      <c r="AU8" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV8" t="inlineStr">
         <is>
@@ -1713,6 +1818,11 @@
       <c r="R9" t="n">
         <v>0</v>
       </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1725,12 +1835,22 @@
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR9" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr"/>
       <c r="AT9" t="n">
         <v>0</v>
+      </c>
+      <c r="AU9" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV9" t="inlineStr">
         <is>
@@ -1848,6 +1968,11 @@
       <c r="R10" t="n">
         <v>0</v>
       </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1860,12 +1985,22 @@
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR10" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr"/>
       <c r="AT10" t="n">
         <v>0</v>
+      </c>
+      <c r="AU10" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV10" t="inlineStr">
         <is>
@@ -1983,6 +2118,11 @@
       <c r="R11" t="n">
         <v>0</v>
       </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1995,12 +2135,22 @@
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR11" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr"/>
       <c r="AT11" t="n">
         <v>0</v>
+      </c>
+      <c r="AU11" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV11" t="inlineStr">
         <is>
@@ -2118,6 +2268,11 @@
       <c r="R12" t="n">
         <v>0</v>
       </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2130,12 +2285,22 @@
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR12" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr"/>
       <c r="AT12" t="n">
         <v>0</v>
+      </c>
+      <c r="AU12" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV12" t="inlineStr">
         <is>
@@ -2253,6 +2418,11 @@
       <c r="R13" t="n">
         <v>0</v>
       </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2265,12 +2435,22 @@
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR13" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr"/>
       <c r="AT13" t="n">
         <v>0</v>
+      </c>
+      <c r="AU13" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV13" t="inlineStr">
         <is>
@@ -2388,6 +2568,11 @@
       <c r="R14" t="n">
         <v>0</v>
       </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2400,12 +2585,22 @@
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR14" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr"/>
       <c r="AT14" t="n">
         <v>0</v>
+      </c>
+      <c r="AU14" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV14" t="inlineStr">
         <is>
@@ -2523,6 +2718,11 @@
       <c r="R15" t="n">
         <v>0</v>
       </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2535,12 +2735,22 @@
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR15" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr"/>
       <c r="AT15" t="n">
         <v>0</v>
+      </c>
+      <c r="AU15" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV15" t="inlineStr">
         <is>
@@ -2658,6 +2868,11 @@
       <c r="R16" t="n">
         <v>0</v>
       </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2670,12 +2885,22 @@
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR16" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr"/>
       <c r="AT16" t="n">
         <v>0</v>
+      </c>
+      <c r="AU16" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV16" t="inlineStr">
         <is>
@@ -2793,6 +3018,11 @@
       <c r="R17" t="n">
         <v>0</v>
       </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2805,12 +3035,22 @@
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR17" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr"/>
       <c r="AT17" t="n">
         <v>0</v>
+      </c>
+      <c r="AU17" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV17" t="inlineStr">
         <is>
@@ -2928,6 +3168,11 @@
       <c r="R18" t="n">
         <v>0</v>
       </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2940,12 +3185,22 @@
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR18" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr"/>
       <c r="AT18" t="n">
         <v>0</v>
+      </c>
+      <c r="AU18" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV18" t="inlineStr">
         <is>
@@ -3063,6 +3318,11 @@
       <c r="R19" t="n">
         <v>0</v>
       </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3075,12 +3335,22 @@
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR19" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr"/>
       <c r="AT19" t="n">
         <v>0</v>
+      </c>
+      <c r="AU19" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV19" t="inlineStr">
         <is>
@@ -3198,6 +3468,11 @@
       <c r="R20" t="n">
         <v>0</v>
       </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3210,12 +3485,22 @@
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR20" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr"/>
       <c r="AT20" t="n">
         <v>0</v>
+      </c>
+      <c r="AU20" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV20" t="inlineStr">
         <is>
@@ -3333,6 +3618,11 @@
       <c r="R21" t="n">
         <v>0</v>
       </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3345,12 +3635,22 @@
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR21" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr"/>
       <c r="AT21" t="n">
         <v>0</v>
+      </c>
+      <c r="AU21" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV21" t="inlineStr">
         <is>
@@ -3468,6 +3768,11 @@
       <c r="R22" t="n">
         <v>0</v>
       </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3480,12 +3785,22 @@
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR22" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr"/>
       <c r="AT22" t="n">
         <v>0</v>
+      </c>
+      <c r="AU22" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV22" t="inlineStr">
         <is>
@@ -4053,6 +4368,11 @@
       <c r="R26" t="n">
         <v>0</v>
       </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -4065,12 +4385,22 @@
       </c>
       <c r="AP26" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR26" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS26" t="inlineStr"/>
       <c r="AT26" t="n">
         <v>0</v>
+      </c>
+      <c r="AU26" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV26" t="inlineStr">
         <is>
@@ -4788,6 +5118,11 @@
       <c r="R31" t="n">
         <v>0</v>
       </c>
+      <c r="S31" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -4800,12 +5135,22 @@
       </c>
       <c r="AP31" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR31" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS31" t="inlineStr"/>
       <c r="AT31" t="n">
         <v>0</v>
+      </c>
+      <c r="AU31" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV31" t="inlineStr">
         <is>
@@ -5673,6 +6018,11 @@
       <c r="R37" t="n">
         <v>0</v>
       </c>
+      <c r="S37" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -5685,12 +6035,22 @@
       </c>
       <c r="AP37" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR37" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS37" t="inlineStr"/>
       <c r="AT37" t="n">
         <v>0</v>
+      </c>
+      <c r="AU37" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV37" t="inlineStr">
         <is>
@@ -6408,6 +6768,11 @@
       <c r="R42" t="n">
         <v>0</v>
       </c>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -6420,12 +6785,22 @@
       </c>
       <c r="AP42" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR42" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS42" t="inlineStr"/>
       <c r="AT42" t="n">
         <v>0</v>
+      </c>
+      <c r="AU42" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV42" t="inlineStr">
         <is>
@@ -7293,6 +7668,11 @@
       <c r="R48" t="n">
         <v>0</v>
       </c>
+      <c r="S48" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA48" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -7305,12 +7685,22 @@
       </c>
       <c r="AP48" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR48" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS48" t="inlineStr"/>
       <c r="AT48" t="n">
         <v>0</v>
+      </c>
+      <c r="AU48" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV48" t="inlineStr">
         <is>
@@ -8028,6 +8418,11 @@
       <c r="R53" t="n">
         <v>0</v>
       </c>
+      <c r="S53" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA53" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -8040,12 +8435,22 @@
       </c>
       <c r="AP53" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR53" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS53" t="inlineStr"/>
       <c r="AT53" t="n">
         <v>0</v>
+      </c>
+      <c r="AU53" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV53" t="inlineStr">
         <is>
@@ -8763,6 +9168,11 @@
       <c r="R58" t="n">
         <v>0</v>
       </c>
+      <c r="S58" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA58" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -8775,12 +9185,22 @@
       </c>
       <c r="AP58" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR58" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS58" t="inlineStr"/>
       <c r="AT58" t="n">
         <v>0</v>
+      </c>
+      <c r="AU58" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV58" t="inlineStr">
         <is>
@@ -9498,6 +9918,11 @@
       <c r="R63" t="n">
         <v>0</v>
       </c>
+      <c r="S63" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA63" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -9510,12 +9935,22 @@
       </c>
       <c r="AP63" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR63" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS63" t="inlineStr"/>
       <c r="AT63" t="n">
         <v>0</v>
+      </c>
+      <c r="AU63" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV63" t="inlineStr">
         <is>
@@ -10383,6 +10818,11 @@
       <c r="R69" t="n">
         <v>0</v>
       </c>
+      <c r="S69" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA69" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -10395,12 +10835,22 @@
       </c>
       <c r="AP69" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR69" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS69" t="inlineStr"/>
       <c r="AT69" t="n">
         <v>0</v>
+      </c>
+      <c r="AU69" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV69" t="inlineStr">
         <is>
@@ -11118,6 +11568,11 @@
       <c r="R74" t="n">
         <v>0</v>
       </c>
+      <c r="S74" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA74" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -11130,12 +11585,22 @@
       </c>
       <c r="AP74" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR74" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS74" t="inlineStr"/>
       <c r="AT74" t="n">
         <v>0</v>
+      </c>
+      <c r="AU74" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV74" t="inlineStr">
         <is>
@@ -11853,6 +12318,11 @@
       <c r="R79" t="n">
         <v>0</v>
       </c>
+      <c r="S79" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA79" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -11865,12 +12335,22 @@
       </c>
       <c r="AP79" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR79" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS79" t="inlineStr"/>
       <c r="AT79" t="n">
         <v>0</v>
+      </c>
+      <c r="AU79" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV79" t="inlineStr">
         <is>
@@ -12738,6 +13218,11 @@
       <c r="R85" t="n">
         <v>0</v>
       </c>
+      <c r="S85" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA85" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -12750,12 +13235,22 @@
       </c>
       <c r="AP85" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR85" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS85" t="inlineStr"/>
       <c r="AT85" t="n">
         <v>0</v>
+      </c>
+      <c r="AU85" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV85" t="inlineStr">
         <is>
@@ -13473,6 +13968,11 @@
       <c r="R90" t="n">
         <v>0</v>
       </c>
+      <c r="S90" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA90" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -13485,12 +13985,22 @@
       </c>
       <c r="AP90" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR90" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS90" t="inlineStr"/>
       <c r="AT90" t="n">
         <v>0</v>
+      </c>
+      <c r="AU90" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV90" t="inlineStr">
         <is>
@@ -14358,6 +14868,11 @@
       <c r="R96" t="n">
         <v>0</v>
       </c>
+      <c r="S96" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA96" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -14370,12 +14885,22 @@
       </c>
       <c r="AP96" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR96" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS96" t="inlineStr"/>
       <c r="AT96" t="n">
         <v>0</v>
+      </c>
+      <c r="AU96" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV96" t="inlineStr">
         <is>
@@ -15093,6 +15618,11 @@
       <c r="R101" t="n">
         <v>0</v>
       </c>
+      <c r="S101" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA101" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -15105,12 +15635,22 @@
       </c>
       <c r="AP101" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR101" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS101" t="inlineStr"/>
       <c r="AT101" t="n">
         <v>0</v>
+      </c>
+      <c r="AU101" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV101" t="inlineStr">
         <is>
@@ -15828,6 +16368,11 @@
       <c r="R106" t="n">
         <v>0</v>
       </c>
+      <c r="S106" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA106" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -15840,12 +16385,22 @@
       </c>
       <c r="AP106" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR106" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS106" t="inlineStr"/>
       <c r="AT106" t="n">
         <v>0</v>
+      </c>
+      <c r="AU106" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV106" t="inlineStr">
         <is>
@@ -16713,6 +17268,11 @@
       <c r="R112" t="n">
         <v>0</v>
       </c>
+      <c r="S112" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA112" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -16725,12 +17285,22 @@
       </c>
       <c r="AP112" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR112" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS112" t="inlineStr"/>
       <c r="AT112" t="n">
         <v>0</v>
+      </c>
+      <c r="AU112" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV112" t="inlineStr">
         <is>
@@ -17448,6 +18018,11 @@
       <c r="R117" t="n">
         <v>0</v>
       </c>
+      <c r="S117" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA117" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -17460,12 +18035,22 @@
       </c>
       <c r="AP117" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR117" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS117" t="inlineStr"/>
       <c r="AT117" t="n">
         <v>0</v>
+      </c>
+      <c r="AU117" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV117" t="inlineStr">
         <is>
@@ -18183,6 +18768,11 @@
       <c r="R122" t="n">
         <v>0</v>
       </c>
+      <c r="S122" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA122" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -18195,12 +18785,22 @@
       </c>
       <c r="AP122" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR122" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS122" t="inlineStr"/>
       <c r="AT122" t="n">
         <v>0</v>
+      </c>
+      <c r="AU122" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV122" t="inlineStr">
         <is>
@@ -18918,6 +19518,11 @@
       <c r="R127" t="n">
         <v>0</v>
       </c>
+      <c r="S127" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA127" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -18930,12 +19535,22 @@
       </c>
       <c r="AP127" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR127" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS127" t="inlineStr"/>
       <c r="AT127" t="n">
         <v>0</v>
+      </c>
+      <c r="AU127" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV127" t="inlineStr">
         <is>
@@ -19803,6 +20418,11 @@
       <c r="R133" t="n">
         <v>0</v>
       </c>
+      <c r="S133" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA133" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -19815,12 +20435,22 @@
       </c>
       <c r="AP133" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR133" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS133" t="inlineStr"/>
       <c r="AT133" t="n">
         <v>0</v>
+      </c>
+      <c r="AU133" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV133" t="inlineStr">
         <is>
@@ -20538,6 +21168,11 @@
       <c r="R138" t="n">
         <v>0</v>
       </c>
+      <c r="S138" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA138" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -20550,12 +21185,22 @@
       </c>
       <c r="AP138" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR138" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS138" t="inlineStr"/>
       <c r="AT138" t="n">
         <v>0</v>
+      </c>
+      <c r="AU138" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV138" t="inlineStr">
         <is>
@@ -21423,6 +22068,11 @@
       <c r="R144" t="n">
         <v>0</v>
       </c>
+      <c r="S144" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA144" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -21435,12 +22085,22 @@
       </c>
       <c r="AP144" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR144" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS144" t="inlineStr"/>
       <c r="AT144" t="n">
         <v>0</v>
+      </c>
+      <c r="AU144" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV144" t="inlineStr">
         <is>
@@ -22158,6 +22818,11 @@
       <c r="R149" t="n">
         <v>0</v>
       </c>
+      <c r="S149" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA149" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -22170,12 +22835,22 @@
       </c>
       <c r="AP149" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR149" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS149" t="inlineStr"/>
       <c r="AT149" t="n">
         <v>0</v>
+      </c>
+      <c r="AU149" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV149" t="inlineStr">
         <is>
@@ -24139,6 +24814,11 @@
       <c r="R160" t="n">
         <v>0</v>
       </c>
+      <c r="S160" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA160" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -24151,12 +24831,22 @@
       </c>
       <c r="AP160" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR160" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS160" t="inlineStr"/>
       <c r="AT160" t="n">
         <v>0</v>
+      </c>
+      <c r="AU160" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV160" t="inlineStr">
         <is>
@@ -25647,6 +26337,11 @@
       <c r="R169" t="n">
         <v>0</v>
       </c>
+      <c r="S169" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA169" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -25659,12 +26354,22 @@
       </c>
       <c r="AP169" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR169" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS169" t="inlineStr"/>
       <c r="AT169" t="n">
         <v>0</v>
+      </c>
+      <c r="AU169" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV169" t="inlineStr">
         <is>
@@ -26382,6 +27087,11 @@
       <c r="R174" t="n">
         <v>0</v>
       </c>
+      <c r="S174" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA174" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -26394,12 +27104,22 @@
       </c>
       <c r="AP174" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR174" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS174" t="inlineStr"/>
       <c r="AT174" t="n">
         <v>0</v>
+      </c>
+      <c r="AU174" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV174" t="inlineStr">
         <is>
